--- a/Assets/StreamingAssets/Data.xlsx
+++ b/Assets/StreamingAssets/Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ljh\tralalero Shooter\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6C68F65-4FA4-4ACD-B13F-70DA1F3ADE3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A6D049-CE62-494B-8A1E-5BDB139B06CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="업그레이드" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="66">
   <si>
     <t>식별 순번</t>
   </si>
@@ -126,16 +126,10 @@
     <t>퉁퉁퉁 사후르</t>
   </si>
   <si>
-    <t>플레이어 현재 체력의</t>
-  </si>
-  <si>
     <t>BOOMBAR</t>
   </si>
   <si>
     <t>붐바르 딜로</t>
-  </si>
-  <si>
-    <t>플레이어 현재 공격력의</t>
   </si>
   <si>
     <t>트랄랄레오 보라 스킨</t>
@@ -220,6 +214,38 @@
   </si>
   <si>
     <t>기타 설명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격력 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>체력 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격 속도 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>투사체 속도 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보스 데미지 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>얻는 코인량 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내 현재 체력의</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내 현재 공격력의</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -668,6 +694,9 @@
       <c r="I3">
         <v>100</v>
       </c>
+      <c r="J3" t="s">
+        <v>58</v>
+      </c>
       <c r="K3" s="2"/>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.3">
@@ -695,6 +724,9 @@
       <c r="I4">
         <v>150</v>
       </c>
+      <c r="J4" t="s">
+        <v>58</v>
+      </c>
       <c r="K4" s="2"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
@@ -722,6 +754,9 @@
       <c r="I5">
         <v>200</v>
       </c>
+      <c r="J5" t="s">
+        <v>58</v>
+      </c>
       <c r="K5" s="2"/>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
@@ -749,6 +784,9 @@
       <c r="I6">
         <v>250</v>
       </c>
+      <c r="J6" t="s">
+        <v>58</v>
+      </c>
       <c r="K6" s="2"/>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.3">
@@ -776,6 +814,9 @@
       <c r="I7">
         <v>300</v>
       </c>
+      <c r="J7" t="s">
+        <v>58</v>
+      </c>
       <c r="K7" s="2"/>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
@@ -803,6 +844,9 @@
       <c r="I8">
         <v>350</v>
       </c>
+      <c r="J8" t="s">
+        <v>58</v>
+      </c>
       <c r="K8" s="2"/>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.3">
@@ -830,6 +874,9 @@
       <c r="I9">
         <v>400</v>
       </c>
+      <c r="J9" t="s">
+        <v>58</v>
+      </c>
       <c r="K9" s="2"/>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.3">
@@ -857,6 +904,9 @@
       <c r="I10">
         <v>450</v>
       </c>
+      <c r="J10" t="s">
+        <v>58</v>
+      </c>
       <c r="K10" s="2"/>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.3">
@@ -884,6 +934,9 @@
       <c r="I11">
         <v>500</v>
       </c>
+      <c r="J11" t="s">
+        <v>58</v>
+      </c>
       <c r="K11" s="2"/>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.3">
@@ -911,6 +964,9 @@
       <c r="I12">
         <v>550</v>
       </c>
+      <c r="J12" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13">
@@ -937,6 +993,9 @@
       <c r="I13">
         <v>600</v>
       </c>
+      <c r="J13" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14">
@@ -963,6 +1022,9 @@
       <c r="I14">
         <v>650</v>
       </c>
+      <c r="J14" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15">
@@ -989,6 +1051,9 @@
       <c r="I15">
         <v>700</v>
       </c>
+      <c r="J15" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16">
@@ -1015,8 +1080,11 @@
       <c r="I16">
         <v>750</v>
       </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>1</v>
       </c>
@@ -1041,8 +1109,11 @@
       <c r="I17">
         <v>800</v>
       </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J17" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>1</v>
       </c>
@@ -1067,8 +1138,11 @@
       <c r="I18">
         <v>850</v>
       </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>1</v>
       </c>
@@ -1093,8 +1167,11 @@
       <c r="I19">
         <v>900</v>
       </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>1</v>
       </c>
@@ -1119,8 +1196,11 @@
       <c r="I20">
         <v>950</v>
       </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>1</v>
       </c>
@@ -1145,8 +1225,11 @@
       <c r="I21">
         <v>1000</v>
       </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J21" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>1</v>
       </c>
@@ -1171,8 +1254,11 @@
       <c r="I22">
         <v>1050</v>
       </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J22" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>2</v>
       </c>
@@ -1197,8 +1283,11 @@
       <c r="I23">
         <v>100</v>
       </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J23" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>2</v>
       </c>
@@ -1223,8 +1312,11 @@
       <c r="I24">
         <v>150</v>
       </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J24" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>2</v>
       </c>
@@ -1249,8 +1341,11 @@
       <c r="I25">
         <v>200</v>
       </c>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J25" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>2</v>
       </c>
@@ -1275,8 +1370,11 @@
       <c r="I26">
         <v>250</v>
       </c>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J26" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>2</v>
       </c>
@@ -1301,8 +1399,11 @@
       <c r="I27">
         <v>300</v>
       </c>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J27" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>2</v>
       </c>
@@ -1327,8 +1428,11 @@
       <c r="I28">
         <v>350</v>
       </c>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J28" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>2</v>
       </c>
@@ -1353,8 +1457,11 @@
       <c r="I29">
         <v>400</v>
       </c>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J29" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30">
         <v>2</v>
       </c>
@@ -1379,8 +1486,11 @@
       <c r="I30">
         <v>450</v>
       </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J30" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>2</v>
       </c>
@@ -1405,8 +1515,11 @@
       <c r="I31">
         <v>500</v>
       </c>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J31" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>2</v>
       </c>
@@ -1431,8 +1544,11 @@
       <c r="I32">
         <v>550</v>
       </c>
-    </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J32" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>2</v>
       </c>
@@ -1457,8 +1573,11 @@
       <c r="I33">
         <v>600</v>
       </c>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J33" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>2</v>
       </c>
@@ -1483,8 +1602,11 @@
       <c r="I34">
         <v>650</v>
       </c>
-    </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J34" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B35">
         <v>2</v>
       </c>
@@ -1509,8 +1631,11 @@
       <c r="I35">
         <v>700</v>
       </c>
-    </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J35" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>2</v>
       </c>
@@ -1535,8 +1660,11 @@
       <c r="I36">
         <v>750</v>
       </c>
-    </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J36" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B37">
         <v>2</v>
       </c>
@@ -1561,8 +1689,11 @@
       <c r="I37">
         <v>800</v>
       </c>
-    </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J37" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B38">
         <v>2</v>
       </c>
@@ -1587,8 +1718,11 @@
       <c r="I38">
         <v>850</v>
       </c>
-    </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J38" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B39">
         <v>2</v>
       </c>
@@ -1613,8 +1747,11 @@
       <c r="I39">
         <v>900</v>
       </c>
-    </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J39" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B40">
         <v>2</v>
       </c>
@@ -1639,8 +1776,11 @@
       <c r="I40">
         <v>950</v>
       </c>
-    </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J40" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41">
         <v>2</v>
       </c>
@@ -1665,8 +1805,11 @@
       <c r="I41">
         <v>1000</v>
       </c>
-    </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J41" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B42">
         <v>2</v>
       </c>
@@ -1691,8 +1834,11 @@
       <c r="I42">
         <v>1050</v>
       </c>
-    </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J42" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B43">
         <v>3</v>
       </c>
@@ -1717,8 +1863,11 @@
       <c r="I43">
         <v>100</v>
       </c>
-    </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J43" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44">
         <v>3</v>
       </c>
@@ -1743,8 +1892,11 @@
       <c r="I44">
         <v>150</v>
       </c>
-    </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J44" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B45">
         <v>3</v>
       </c>
@@ -1769,8 +1921,11 @@
       <c r="I45">
         <v>200</v>
       </c>
-    </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J45" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B46">
         <v>3</v>
       </c>
@@ -1795,8 +1950,11 @@
       <c r="I46">
         <v>250</v>
       </c>
-    </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J46" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47">
         <v>3</v>
       </c>
@@ -1821,8 +1979,11 @@
       <c r="I47">
         <v>300</v>
       </c>
-    </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J47" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B48">
         <v>3</v>
       </c>
@@ -1847,8 +2008,11 @@
       <c r="I48">
         <v>350</v>
       </c>
-    </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J48" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B49">
         <v>3</v>
       </c>
@@ -1873,8 +2037,11 @@
       <c r="I49">
         <v>400</v>
       </c>
-    </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J49" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B50">
         <v>3</v>
       </c>
@@ -1899,8 +2066,11 @@
       <c r="I50">
         <v>450</v>
       </c>
-    </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J50" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B51">
         <v>3</v>
       </c>
@@ -1925,8 +2095,11 @@
       <c r="I51">
         <v>500</v>
       </c>
-    </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J51" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B52">
         <v>3</v>
       </c>
@@ -1951,8 +2124,11 @@
       <c r="I52">
         <v>550</v>
       </c>
-    </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J52" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B53">
         <v>3</v>
       </c>
@@ -1977,8 +2153,11 @@
       <c r="I53">
         <v>600</v>
       </c>
-    </row>
-    <row r="54" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J53" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B54">
         <v>3</v>
       </c>
@@ -2003,8 +2182,11 @@
       <c r="I54">
         <v>650</v>
       </c>
-    </row>
-    <row r="55" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J54" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B55">
         <v>3</v>
       </c>
@@ -2029,8 +2211,11 @@
       <c r="I55">
         <v>700</v>
       </c>
-    </row>
-    <row r="56" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J55" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B56">
         <v>3</v>
       </c>
@@ -2055,8 +2240,11 @@
       <c r="I56">
         <v>750</v>
       </c>
-    </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J56" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B57">
         <v>3</v>
       </c>
@@ -2081,8 +2269,11 @@
       <c r="I57">
         <v>800</v>
       </c>
-    </row>
-    <row r="58" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J57" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B58">
         <v>3</v>
       </c>
@@ -2107,8 +2298,11 @@
       <c r="I58">
         <v>850</v>
       </c>
-    </row>
-    <row r="59" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J58" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B59">
         <v>3</v>
       </c>
@@ -2133,8 +2327,11 @@
       <c r="I59">
         <v>900</v>
       </c>
-    </row>
-    <row r="60" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J59" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B60">
         <v>3</v>
       </c>
@@ -2159,8 +2356,11 @@
       <c r="I60">
         <v>950</v>
       </c>
-    </row>
-    <row r="61" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J60" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B61">
         <v>3</v>
       </c>
@@ -2185,8 +2385,11 @@
       <c r="I61">
         <v>1000</v>
       </c>
-    </row>
-    <row r="62" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J61" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B62">
         <v>3</v>
       </c>
@@ -2211,8 +2414,11 @@
       <c r="I62">
         <v>1050</v>
       </c>
-    </row>
-    <row r="63" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J62" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B63">
         <v>4</v>
       </c>
@@ -2237,8 +2443,11 @@
       <c r="I63">
         <v>100</v>
       </c>
-    </row>
-    <row r="64" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J63" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B64">
         <v>4</v>
       </c>
@@ -2263,8 +2472,11 @@
       <c r="I64">
         <v>150</v>
       </c>
-    </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J64" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B65">
         <v>4</v>
       </c>
@@ -2289,8 +2501,11 @@
       <c r="I65">
         <v>200</v>
       </c>
-    </row>
-    <row r="66" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J65" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B66">
         <v>4</v>
       </c>
@@ -2315,8 +2530,11 @@
       <c r="I66">
         <v>250</v>
       </c>
-    </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J66" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B67">
         <v>4</v>
       </c>
@@ -2341,8 +2559,11 @@
       <c r="I67">
         <v>300</v>
       </c>
-    </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J67" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B68">
         <v>4</v>
       </c>
@@ -2367,8 +2588,11 @@
       <c r="I68">
         <v>350</v>
       </c>
-    </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J68" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B69">
         <v>4</v>
       </c>
@@ -2393,8 +2617,11 @@
       <c r="I69">
         <v>400</v>
       </c>
-    </row>
-    <row r="70" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J69" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B70">
         <v>4</v>
       </c>
@@ -2419,8 +2646,11 @@
       <c r="I70">
         <v>450</v>
       </c>
-    </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J70" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B71">
         <v>4</v>
       </c>
@@ -2445,8 +2675,11 @@
       <c r="I71">
         <v>500</v>
       </c>
-    </row>
-    <row r="72" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J71" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B72">
         <v>4</v>
       </c>
@@ -2471,8 +2704,11 @@
       <c r="I72">
         <v>550</v>
       </c>
-    </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J72" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B73">
         <v>4</v>
       </c>
@@ -2497,8 +2733,11 @@
       <c r="I73">
         <v>600</v>
       </c>
-    </row>
-    <row r="74" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J73" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B74">
         <v>4</v>
       </c>
@@ -2523,8 +2762,11 @@
       <c r="I74">
         <v>650</v>
       </c>
-    </row>
-    <row r="75" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J74" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B75">
         <v>4</v>
       </c>
@@ -2549,8 +2791,11 @@
       <c r="I75">
         <v>700</v>
       </c>
-    </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J75" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B76">
         <v>4</v>
       </c>
@@ -2575,8 +2820,11 @@
       <c r="I76">
         <v>750</v>
       </c>
-    </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J76" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B77">
         <v>4</v>
       </c>
@@ -2601,8 +2849,11 @@
       <c r="I77">
         <v>800</v>
       </c>
-    </row>
-    <row r="78" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J77" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B78">
         <v>4</v>
       </c>
@@ -2627,8 +2878,11 @@
       <c r="I78">
         <v>850</v>
       </c>
-    </row>
-    <row r="79" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J78" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B79">
         <v>4</v>
       </c>
@@ -2653,8 +2907,11 @@
       <c r="I79">
         <v>900</v>
       </c>
-    </row>
-    <row r="80" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J79" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B80">
         <v>4</v>
       </c>
@@ -2679,8 +2936,11 @@
       <c r="I80">
         <v>950</v>
       </c>
-    </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J80" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B81">
         <v>4</v>
       </c>
@@ -2705,8 +2965,11 @@
       <c r="I81">
         <v>1000</v>
       </c>
-    </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J81" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="82" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B82">
         <v>4</v>
       </c>
@@ -2731,8 +2994,11 @@
       <c r="I82">
         <v>1050</v>
       </c>
-    </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J82" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B83">
         <v>5</v>
       </c>
@@ -2757,8 +3023,11 @@
       <c r="I83">
         <v>100</v>
       </c>
-    </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J83" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B84">
         <v>5</v>
       </c>
@@ -2783,8 +3052,11 @@
       <c r="I84">
         <v>150</v>
       </c>
-    </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J84" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="85" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B85">
         <v>5</v>
       </c>
@@ -2809,8 +3081,11 @@
       <c r="I85">
         <v>200</v>
       </c>
-    </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J85" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B86">
         <v>5</v>
       </c>
@@ -2835,8 +3110,11 @@
       <c r="I86">
         <v>250</v>
       </c>
-    </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J86" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B87">
         <v>5</v>
       </c>
@@ -2861,8 +3139,11 @@
       <c r="I87">
         <v>300</v>
       </c>
-    </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J87" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="88" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B88">
         <v>5</v>
       </c>
@@ -2887,8 +3168,11 @@
       <c r="I88">
         <v>350</v>
       </c>
-    </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J88" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="89" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B89">
         <v>5</v>
       </c>
@@ -2913,8 +3197,11 @@
       <c r="I89">
         <v>400</v>
       </c>
-    </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J89" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="90" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B90">
         <v>5</v>
       </c>
@@ -2939,8 +3226,11 @@
       <c r="I90">
         <v>450</v>
       </c>
-    </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J90" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="91" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B91">
         <v>5</v>
       </c>
@@ -2965,8 +3255,11 @@
       <c r="I91">
         <v>500</v>
       </c>
-    </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J91" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="92" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B92">
         <v>5</v>
       </c>
@@ -2991,8 +3284,11 @@
       <c r="I92">
         <v>550</v>
       </c>
-    </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J92" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="93" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B93">
         <v>5</v>
       </c>
@@ -3017,8 +3313,11 @@
       <c r="I93">
         <v>600</v>
       </c>
-    </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J93" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="94" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B94">
         <v>5</v>
       </c>
@@ -3043,8 +3342,11 @@
       <c r="I94">
         <v>650</v>
       </c>
-    </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J94" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="95" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B95">
         <v>5</v>
       </c>
@@ -3069,8 +3371,11 @@
       <c r="I95">
         <v>700</v>
       </c>
-    </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J95" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="96" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B96">
         <v>5</v>
       </c>
@@ -3095,8 +3400,11 @@
       <c r="I96">
         <v>750</v>
       </c>
-    </row>
-    <row r="97" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J96" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97">
         <v>5</v>
       </c>
@@ -3121,8 +3429,11 @@
       <c r="I97">
         <v>800</v>
       </c>
-    </row>
-    <row r="98" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J97" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98">
         <v>5</v>
       </c>
@@ -3147,8 +3458,11 @@
       <c r="I98">
         <v>850</v>
       </c>
-    </row>
-    <row r="99" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J98" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="99" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B99">
         <v>5</v>
       </c>
@@ -3173,8 +3487,11 @@
       <c r="I99">
         <v>900</v>
       </c>
-    </row>
-    <row r="100" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J99" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="100" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B100">
         <v>5</v>
       </c>
@@ -3199,8 +3516,11 @@
       <c r="I100">
         <v>950</v>
       </c>
-    </row>
-    <row r="101" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J100" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="101" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B101">
         <v>5</v>
       </c>
@@ -3225,8 +3545,11 @@
       <c r="I101">
         <v>1000</v>
       </c>
-    </row>
-    <row r="102" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J101" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="102" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B102">
         <v>5</v>
       </c>
@@ -3251,8 +3574,11 @@
       <c r="I102">
         <v>1050</v>
       </c>
-    </row>
-    <row r="103" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J102" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="103" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B103">
         <v>6</v>
       </c>
@@ -3277,8 +3603,11 @@
       <c r="I103">
         <v>100</v>
       </c>
-    </row>
-    <row r="104" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J103" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="104" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B104">
         <v>6</v>
       </c>
@@ -3303,8 +3632,11 @@
       <c r="I104">
         <v>150</v>
       </c>
-    </row>
-    <row r="105" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J104" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="105" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B105">
         <v>6</v>
       </c>
@@ -3329,8 +3661,11 @@
       <c r="I105">
         <v>200</v>
       </c>
-    </row>
-    <row r="106" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J105" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="106" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B106">
         <v>6</v>
       </c>
@@ -3355,8 +3690,11 @@
       <c r="I106">
         <v>250</v>
       </c>
-    </row>
-    <row r="107" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J106" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="107" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B107">
         <v>6</v>
       </c>
@@ -3381,8 +3719,11 @@
       <c r="I107">
         <v>300</v>
       </c>
-    </row>
-    <row r="108" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J107" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="108" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B108">
         <v>6</v>
       </c>
@@ -3407,8 +3748,11 @@
       <c r="I108">
         <v>350</v>
       </c>
-    </row>
-    <row r="109" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J108" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="109" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B109">
         <v>6</v>
       </c>
@@ -3433,8 +3777,11 @@
       <c r="I109">
         <v>400</v>
       </c>
-    </row>
-    <row r="110" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J109" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="110" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B110">
         <v>6</v>
       </c>
@@ -3459,8 +3806,11 @@
       <c r="I110">
         <v>450</v>
       </c>
-    </row>
-    <row r="111" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J110" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="111" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B111">
         <v>6</v>
       </c>
@@ -3485,8 +3835,11 @@
       <c r="I111">
         <v>500</v>
       </c>
-    </row>
-    <row r="112" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J111" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="112" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B112">
         <v>6</v>
       </c>
@@ -3510,6 +3863,9 @@
       </c>
       <c r="I112">
         <v>550</v>
+      </c>
+      <c r="J112" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
@@ -3537,6 +3893,9 @@
       <c r="I113">
         <v>600</v>
       </c>
+      <c r="J113" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="114" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B114">
@@ -3563,6 +3922,9 @@
       <c r="I114">
         <v>650</v>
       </c>
+      <c r="J114" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="115" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B115">
@@ -3589,6 +3951,9 @@
       <c r="I115">
         <v>700</v>
       </c>
+      <c r="J115" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="116" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B116">
@@ -3615,6 +3980,9 @@
       <c r="I116">
         <v>750</v>
       </c>
+      <c r="J116" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="117" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B117">
@@ -3641,6 +4009,9 @@
       <c r="I117">
         <v>800</v>
       </c>
+      <c r="J117" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="118" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B118">
@@ -3667,6 +4038,9 @@
       <c r="I118">
         <v>850</v>
       </c>
+      <c r="J118" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B119">
@@ -3693,6 +4067,9 @@
       <c r="I119">
         <v>900</v>
       </c>
+      <c r="J119" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="120" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B120">
@@ -3719,6 +4096,9 @@
       <c r="I120">
         <v>950</v>
       </c>
+      <c r="J120" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="121" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B121">
@@ -3745,6 +4125,9 @@
       <c r="I121">
         <v>1000</v>
       </c>
+      <c r="J121" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B122">
@@ -3771,6 +4154,9 @@
       <c r="I122">
         <v>1050</v>
       </c>
+      <c r="J122" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="123" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B123">
@@ -4088,7 +4474,7 @@
         <v>100</v>
       </c>
       <c r="J133" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
     </row>
     <row r="134" spans="2:10" x14ac:dyDescent="0.3">
@@ -4117,7 +4503,7 @@
         <v>150</v>
       </c>
       <c r="J134" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
     </row>
     <row r="135" spans="2:10" x14ac:dyDescent="0.3">
@@ -4146,7 +4532,7 @@
         <v>200</v>
       </c>
       <c r="J135" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
     </row>
     <row r="136" spans="2:10" x14ac:dyDescent="0.3">
@@ -4175,7 +4561,7 @@
         <v>250</v>
       </c>
       <c r="J136" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
     </row>
     <row r="137" spans="2:10" x14ac:dyDescent="0.3">
@@ -4204,7 +4590,7 @@
         <v>300</v>
       </c>
       <c r="J137" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
     </row>
     <row r="138" spans="2:10" x14ac:dyDescent="0.3">
@@ -4233,7 +4619,7 @@
         <v>350</v>
       </c>
       <c r="J138" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
     </row>
     <row r="139" spans="2:10" x14ac:dyDescent="0.3">
@@ -4262,7 +4648,7 @@
         <v>400</v>
       </c>
       <c r="J139" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
     </row>
     <row r="140" spans="2:10" x14ac:dyDescent="0.3">
@@ -4291,7 +4677,7 @@
         <v>450</v>
       </c>
       <c r="J140" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
     </row>
     <row r="141" spans="2:10" x14ac:dyDescent="0.3">
@@ -4320,7 +4706,7 @@
         <v>500</v>
       </c>
       <c r="J141" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
     </row>
     <row r="142" spans="2:10" x14ac:dyDescent="0.3">
@@ -4349,7 +4735,7 @@
         <v>550</v>
       </c>
       <c r="J142" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
     </row>
     <row r="143" spans="2:10" x14ac:dyDescent="0.3">
@@ -4357,13 +4743,13 @@
         <v>9</v>
       </c>
       <c r="C143" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D143">
         <v>1</v>
       </c>
       <c r="E143" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F143">
         <v>20</v>
@@ -4378,7 +4764,7 @@
         <v>100</v>
       </c>
       <c r="J143" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
     </row>
     <row r="144" spans="2:10" x14ac:dyDescent="0.3">
@@ -4386,13 +4772,13 @@
         <v>9</v>
       </c>
       <c r="C144" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D144">
         <v>2</v>
       </c>
       <c r="E144" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F144">
         <v>25</v>
@@ -4407,7 +4793,7 @@
         <v>150</v>
       </c>
       <c r="J144" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
     </row>
     <row r="145" spans="2:10" x14ac:dyDescent="0.3">
@@ -4415,13 +4801,13 @@
         <v>9</v>
       </c>
       <c r="C145" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D145">
         <v>3</v>
       </c>
       <c r="E145" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F145">
         <v>30</v>
@@ -4436,7 +4822,7 @@
         <v>200</v>
       </c>
       <c r="J145" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
     </row>
     <row r="146" spans="2:10" x14ac:dyDescent="0.3">
@@ -4444,13 +4830,13 @@
         <v>9</v>
       </c>
       <c r="C146" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D146">
         <v>4</v>
       </c>
       <c r="E146" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F146">
         <v>35</v>
@@ -4465,7 +4851,7 @@
         <v>250</v>
       </c>
       <c r="J146" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.3">
@@ -4473,13 +4859,13 @@
         <v>9</v>
       </c>
       <c r="C147" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D147">
         <v>5</v>
       </c>
       <c r="E147" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F147">
         <v>40</v>
@@ -4494,7 +4880,7 @@
         <v>300</v>
       </c>
       <c r="J147" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
     </row>
     <row r="148" spans="2:10" x14ac:dyDescent="0.3">
@@ -4502,13 +4888,13 @@
         <v>9</v>
       </c>
       <c r="C148" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D148">
         <v>6</v>
       </c>
       <c r="E148" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F148">
         <v>45</v>
@@ -4523,7 +4909,7 @@
         <v>350</v>
       </c>
       <c r="J148" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
     </row>
     <row r="149" spans="2:10" x14ac:dyDescent="0.3">
@@ -4531,13 +4917,13 @@
         <v>9</v>
       </c>
       <c r="C149" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D149">
         <v>7</v>
       </c>
       <c r="E149" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F149">
         <v>50</v>
@@ -4552,7 +4938,7 @@
         <v>400</v>
       </c>
       <c r="J149" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.3">
@@ -4560,13 +4946,13 @@
         <v>9</v>
       </c>
       <c r="C150" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D150">
         <v>8</v>
       </c>
       <c r="E150" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F150">
         <v>55</v>
@@ -4581,7 +4967,7 @@
         <v>450</v>
       </c>
       <c r="J150" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.3">
@@ -4589,13 +4975,13 @@
         <v>9</v>
       </c>
       <c r="C151" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D151">
         <v>9</v>
       </c>
       <c r="E151" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F151">
         <v>60</v>
@@ -4610,7 +4996,7 @@
         <v>500</v>
       </c>
       <c r="J151" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
     </row>
     <row r="152" spans="2:10" x14ac:dyDescent="0.3">
@@ -4618,13 +5004,13 @@
         <v>9</v>
       </c>
       <c r="C152" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D152">
         <v>10</v>
       </c>
       <c r="E152" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F152">
         <v>65</v>
@@ -4639,7 +5025,7 @@
         <v>550</v>
       </c>
       <c r="J152" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -4680,7 +5066,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
@@ -4694,7 +5080,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
@@ -4775,10 +5161,10 @@
         <v>8</v>
       </c>
       <c r="K2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
@@ -4786,16 +5172,16 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K3" s="3">
         <v>0.12</v>
@@ -4809,13 +5195,13 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G4" t="s">
         <v>17</v>
@@ -4832,13 +5218,13 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G5" t="s">
         <v>17</v>
@@ -4855,13 +5241,13 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G6" t="s">
         <v>17</v>
@@ -4878,16 +5264,16 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K7" s="8">
         <v>0.12</v>
@@ -4901,13 +5287,13 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G8" t="s">
         <v>17</v>
@@ -4924,13 +5310,13 @@
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G9" t="s">
         <v>11</v>
@@ -4947,13 +5333,13 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G10" t="s">
         <v>11</v>
@@ -4970,13 +5356,13 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G11" t="s">
         <v>11</v>
@@ -4993,16 +5379,16 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G12" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K12" s="3">
         <f t="shared" ref="K12:K17" si="0">K3*2</f>
@@ -5017,13 +5403,13 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
         <v>17</v>
@@ -5041,13 +5427,13 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G14" t="s">
         <v>17</v>
@@ -5066,13 +5452,13 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G15" t="s">
         <v>17</v>
@@ -5091,16 +5477,16 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G16" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K16" s="8">
         <f t="shared" si="0"/>
@@ -5116,13 +5502,13 @@
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G17" t="s">
         <v>17</v>
@@ -5180,25 +5566,25 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" t="s">
         <v>53</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>54</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>55</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>56</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>57</v>
-      </c>
-      <c r="G2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">
@@ -5212,7 +5598,7 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F3">
         <v>33</v>
@@ -5232,7 +5618,7 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F4">
         <v>55</v>
@@ -5253,14 +5639,14 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F5">
         <v>165</v>
       </c>
       <c r="G5">
-        <f>G4*2</f>
-        <v>220</v>
+        <f>ROUNDUP(G4*1.7,-1)</f>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.3">
@@ -5274,7 +5660,7 @@
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F6">
         <v>36</v>
@@ -5295,7 +5681,7 @@
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F7">
         <v>60</v>
@@ -5316,14 +5702,14 @@
         <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F8">
         <v>180</v>
       </c>
       <c r="G8">
-        <f>G7*2</f>
-        <v>240</v>
+        <f>ROUNDUP(G7*1.7,-1)</f>
+        <v>210</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.3">
@@ -5337,7 +5723,7 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F9">
         <v>39</v>
@@ -5358,7 +5744,7 @@
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F10">
         <v>65</v>
@@ -5379,14 +5765,14 @@
         <v>3</v>
       </c>
       <c r="E11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F11">
         <v>195</v>
       </c>
       <c r="G11">
-        <f t="shared" si="1"/>
-        <v>260</v>
+        <f t="shared" ref="G11:G74" si="2">ROUNDUP(G10*1.7,-1)</f>
+        <v>230</v>
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.3">
@@ -5400,13 +5786,13 @@
         <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F12">
         <v>42</v>
       </c>
       <c r="G12">
-        <f t="shared" ref="G12" si="2">G9+5</f>
+        <f t="shared" ref="G12" si="3">G9+5</f>
         <v>70</v>
       </c>
     </row>
@@ -5421,13 +5807,13 @@
         <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F13">
         <v>70</v>
       </c>
       <c r="G13">
-        <f t="shared" ref="G13:G76" si="3">G12*2</f>
+        <f t="shared" ref="G13:G76" si="4">G12*2</f>
         <v>140</v>
       </c>
     </row>
@@ -5442,14 +5828,14 @@
         <v>4</v>
       </c>
       <c r="E14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F14">
         <v>210</v>
       </c>
       <c r="G14">
-        <f t="shared" si="3"/>
-        <v>280</v>
+        <f t="shared" ref="G14:G77" si="5">ROUNDUP(G13*1.7,-1)</f>
+        <v>240</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.3">
@@ -5463,13 +5849,13 @@
         <v>5</v>
       </c>
       <c r="E15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F15">
         <v>45</v>
       </c>
       <c r="G15">
-        <f t="shared" ref="G15" si="4">G12+5</f>
+        <f t="shared" ref="G15" si="6">G12+5</f>
         <v>75</v>
       </c>
     </row>
@@ -5484,13 +5870,13 @@
         <v>5</v>
       </c>
       <c r="E16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F16">
         <v>75</v>
       </c>
       <c r="G16">
-        <f t="shared" ref="G16:G79" si="5">G15*2</f>
+        <f t="shared" ref="G16:G79" si="7">G15*2</f>
         <v>150</v>
       </c>
     </row>
@@ -5505,14 +5891,14 @@
         <v>5</v>
       </c>
       <c r="E17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F17">
         <v>225</v>
       </c>
       <c r="G17">
-        <f t="shared" si="5"/>
-        <v>300</v>
+        <f t="shared" ref="G17:G80" si="8">ROUNDUP(G16*1.7,-1)</f>
+        <v>260</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.3">
@@ -5526,13 +5912,13 @@
         <v>6</v>
       </c>
       <c r="E18" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F18">
         <v>48</v>
       </c>
       <c r="G18">
-        <f t="shared" ref="G18" si="6">G15+5</f>
+        <f t="shared" ref="G18" si="9">G15+5</f>
         <v>80</v>
       </c>
     </row>
@@ -5547,13 +5933,13 @@
         <v>6</v>
       </c>
       <c r="E19" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F19">
         <v>80</v>
       </c>
       <c r="G19">
-        <f t="shared" ref="G19:G82" si="7">G18*2</f>
+        <f t="shared" ref="G19:G82" si="10">G18*2</f>
         <v>160</v>
       </c>
     </row>
@@ -5568,14 +5954,14 @@
         <v>6</v>
       </c>
       <c r="E20" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F20">
         <v>240</v>
       </c>
       <c r="G20">
-        <f t="shared" si="7"/>
-        <v>320</v>
+        <f t="shared" ref="G20:G83" si="11">ROUNDUP(G19*1.7,-1)</f>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.3">
@@ -5589,13 +5975,13 @@
         <v>7</v>
       </c>
       <c r="E21" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F21">
         <v>51</v>
       </c>
       <c r="G21">
-        <f t="shared" ref="G21" si="8">G18+5</f>
+        <f t="shared" ref="G21" si="12">G18+5</f>
         <v>85</v>
       </c>
     </row>
@@ -5610,13 +5996,13 @@
         <v>7</v>
       </c>
       <c r="E22" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F22">
         <v>85</v>
       </c>
       <c r="G22">
-        <f t="shared" ref="G22:G85" si="9">G21*2</f>
+        <f t="shared" ref="G22:G85" si="13">G21*2</f>
         <v>170</v>
       </c>
     </row>
@@ -5631,14 +6017,14 @@
         <v>7</v>
       </c>
       <c r="E23" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F23">
         <v>255</v>
       </c>
       <c r="G23">
-        <f t="shared" si="9"/>
-        <v>340</v>
+        <f t="shared" ref="G23:G86" si="14">ROUNDUP(G22*1.7,-1)</f>
+        <v>290</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.3">
@@ -5652,13 +6038,13 @@
         <v>8</v>
       </c>
       <c r="E24" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F24">
         <v>54</v>
       </c>
       <c r="G24">
-        <f t="shared" ref="G24" si="10">G21+5</f>
+        <f t="shared" ref="G24" si="15">G21+5</f>
         <v>90</v>
       </c>
     </row>
@@ -5673,13 +6059,13 @@
         <v>8</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F25">
         <v>90</v>
       </c>
       <c r="G25">
-        <f t="shared" ref="G25:G88" si="11">G24*2</f>
+        <f t="shared" ref="G25:G88" si="16">G24*2</f>
         <v>180</v>
       </c>
     </row>
@@ -5694,14 +6080,14 @@
         <v>8</v>
       </c>
       <c r="E26" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F26">
         <v>270</v>
       </c>
       <c r="G26">
-        <f t="shared" si="11"/>
-        <v>360</v>
+        <f t="shared" ref="G26:G89" si="17">ROUNDUP(G25*1.7,-1)</f>
+        <v>310</v>
       </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.3">
@@ -5715,13 +6101,13 @@
         <v>9</v>
       </c>
       <c r="E27" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F27">
         <v>57</v>
       </c>
       <c r="G27">
-        <f t="shared" ref="G27" si="12">G24+5</f>
+        <f t="shared" ref="G27" si="18">G24+5</f>
         <v>95</v>
       </c>
     </row>
@@ -5736,13 +6122,13 @@
         <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F28">
         <v>95</v>
       </c>
       <c r="G28">
-        <f t="shared" ref="G28:G91" si="13">G27*2</f>
+        <f t="shared" ref="G28:G91" si="19">G27*2</f>
         <v>190</v>
       </c>
     </row>
@@ -5757,14 +6143,14 @@
         <v>9</v>
       </c>
       <c r="E29" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F29">
         <v>285</v>
       </c>
       <c r="G29">
-        <f t="shared" si="13"/>
-        <v>380</v>
+        <f t="shared" ref="G29:G92" si="20">ROUNDUP(G28*1.7,-1)</f>
+        <v>330</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.3">
@@ -5778,13 +6164,13 @@
         <v>10</v>
       </c>
       <c r="E30" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F30">
         <v>60</v>
       </c>
       <c r="G30">
-        <f t="shared" ref="G30" si="14">G27+5</f>
+        <f t="shared" ref="G30" si="21">G27+5</f>
         <v>100</v>
       </c>
     </row>
@@ -5799,13 +6185,13 @@
         <v>10</v>
       </c>
       <c r="E31" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F31">
         <v>100</v>
       </c>
       <c r="G31">
-        <f t="shared" ref="G31:G94" si="15">G30*2</f>
+        <f t="shared" ref="G31:G94" si="22">G30*2</f>
         <v>200</v>
       </c>
     </row>
@@ -5820,14 +6206,14 @@
         <v>10</v>
       </c>
       <c r="E32" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F32">
         <v>300</v>
       </c>
       <c r="G32">
-        <f t="shared" si="15"/>
-        <v>400</v>
+        <f t="shared" ref="G32:G95" si="23">ROUNDUP(G31*1.7,-1)</f>
+        <v>340</v>
       </c>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.3">
@@ -5841,13 +6227,13 @@
         <v>1</v>
       </c>
       <c r="E33" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F33">
         <v>63</v>
       </c>
       <c r="G33">
-        <f t="shared" ref="G33" si="16">G30+5</f>
+        <f t="shared" ref="G33" si="24">G30+5</f>
         <v>105</v>
       </c>
     </row>
@@ -5862,13 +6248,13 @@
         <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F34">
         <v>105</v>
       </c>
       <c r="G34">
-        <f t="shared" ref="G34:G97" si="17">G33*2</f>
+        <f t="shared" ref="G34:G97" si="25">G33*2</f>
         <v>210</v>
       </c>
     </row>
@@ -5883,14 +6269,14 @@
         <v>1</v>
       </c>
       <c r="E35" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F35">
         <v>315</v>
       </c>
       <c r="G35">
-        <f t="shared" si="17"/>
-        <v>420</v>
+        <f t="shared" ref="G35:G98" si="26">ROUNDUP(G34*1.7,-1)</f>
+        <v>360</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.3">
@@ -5904,13 +6290,13 @@
         <v>2</v>
       </c>
       <c r="E36" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F36">
         <v>66</v>
       </c>
       <c r="G36">
-        <f t="shared" ref="G36" si="18">G33+5</f>
+        <f t="shared" ref="G36" si="27">G33+5</f>
         <v>110</v>
       </c>
     </row>
@@ -5925,13 +6311,13 @@
         <v>2</v>
       </c>
       <c r="E37" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F37">
         <v>110</v>
       </c>
       <c r="G37">
-        <f t="shared" ref="G37:G100" si="19">G36*2</f>
+        <f t="shared" ref="G37:G100" si="28">G36*2</f>
         <v>220</v>
       </c>
     </row>
@@ -5946,14 +6332,14 @@
         <v>2</v>
       </c>
       <c r="E38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F38">
         <v>330</v>
       </c>
       <c r="G38">
-        <f t="shared" si="19"/>
-        <v>440</v>
+        <f t="shared" ref="G38:G101" si="29">ROUNDUP(G37*1.7,-1)</f>
+        <v>380</v>
       </c>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.3">
@@ -5967,13 +6353,13 @@
         <v>3</v>
       </c>
       <c r="E39" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F39">
         <v>69</v>
       </c>
       <c r="G39">
-        <f t="shared" ref="G39" si="20">G36+5</f>
+        <f t="shared" ref="G39" si="30">G36+5</f>
         <v>115</v>
       </c>
     </row>
@@ -5988,13 +6374,13 @@
         <v>3</v>
       </c>
       <c r="E40" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F40">
         <v>115</v>
       </c>
       <c r="G40">
-        <f t="shared" ref="G40:G103" si="21">G39*2</f>
+        <f t="shared" ref="G40:G103" si="31">G39*2</f>
         <v>230</v>
       </c>
     </row>
@@ -6009,14 +6395,14 @@
         <v>3</v>
       </c>
       <c r="E41" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F41">
         <v>345</v>
       </c>
       <c r="G41">
-        <f t="shared" si="21"/>
-        <v>460</v>
+        <f t="shared" ref="G41:G104" si="32">ROUNDUP(G40*1.7,-1)</f>
+        <v>400</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.3">
@@ -6030,13 +6416,13 @@
         <v>4</v>
       </c>
       <c r="E42" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F42">
         <v>72</v>
       </c>
       <c r="G42">
-        <f t="shared" ref="G42" si="22">G39+5</f>
+        <f t="shared" ref="G42" si="33">G39+5</f>
         <v>120</v>
       </c>
     </row>
@@ -6051,13 +6437,13 @@
         <v>4</v>
       </c>
       <c r="E43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F43">
         <v>120</v>
       </c>
       <c r="G43">
-        <f t="shared" ref="G43:G106" si="23">G42*2</f>
+        <f t="shared" ref="G43:G106" si="34">G42*2</f>
         <v>240</v>
       </c>
     </row>
@@ -6072,14 +6458,14 @@
         <v>4</v>
       </c>
       <c r="E44" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F44">
         <v>360</v>
       </c>
       <c r="G44">
-        <f t="shared" si="23"/>
-        <v>480</v>
+        <f t="shared" ref="G44:G107" si="35">ROUNDUP(G43*1.7,-1)</f>
+        <v>410</v>
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.3">
@@ -6093,13 +6479,13 @@
         <v>5</v>
       </c>
       <c r="E45" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F45">
         <v>75</v>
       </c>
       <c r="G45">
-        <f t="shared" ref="G45" si="24">G42+5</f>
+        <f t="shared" ref="G45" si="36">G42+5</f>
         <v>125</v>
       </c>
     </row>
@@ -6114,13 +6500,13 @@
         <v>5</v>
       </c>
       <c r="E46" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F46">
         <v>125</v>
       </c>
       <c r="G46">
-        <f t="shared" ref="G46:G109" si="25">G45*2</f>
+        <f t="shared" ref="G46:G109" si="37">G45*2</f>
         <v>250</v>
       </c>
     </row>
@@ -6135,14 +6521,14 @@
         <v>5</v>
       </c>
       <c r="E47" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F47">
         <v>375</v>
       </c>
       <c r="G47">
-        <f t="shared" si="25"/>
-        <v>500</v>
+        <f t="shared" ref="G47:G110" si="38">ROUNDUP(G46*1.7,-1)</f>
+        <v>430</v>
       </c>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.3">
@@ -6156,13 +6542,13 @@
         <v>6</v>
       </c>
       <c r="E48" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F48">
         <v>78</v>
       </c>
       <c r="G48">
-        <f t="shared" ref="G48" si="26">G45+5</f>
+        <f t="shared" ref="G48" si="39">G45+5</f>
         <v>130</v>
       </c>
     </row>
@@ -6177,13 +6563,13 @@
         <v>6</v>
       </c>
       <c r="E49" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F49">
         <v>130</v>
       </c>
       <c r="G49">
-        <f t="shared" ref="G49:G112" si="27">G48*2</f>
+        <f t="shared" ref="G49:G112" si="40">G48*2</f>
         <v>260</v>
       </c>
     </row>
@@ -6198,14 +6584,14 @@
         <v>6</v>
       </c>
       <c r="E50" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F50">
         <v>390</v>
       </c>
       <c r="G50">
-        <f t="shared" si="27"/>
-        <v>520</v>
+        <f t="shared" ref="G50:G113" si="41">ROUNDUP(G49*1.7,-1)</f>
+        <v>450</v>
       </c>
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.3">
@@ -6219,13 +6605,13 @@
         <v>7</v>
       </c>
       <c r="E51" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F51">
         <v>81</v>
       </c>
       <c r="G51">
-        <f t="shared" ref="G51" si="28">G48+5</f>
+        <f t="shared" ref="G51" si="42">G48+5</f>
         <v>135</v>
       </c>
     </row>
@@ -6240,13 +6626,13 @@
         <v>7</v>
       </c>
       <c r="E52" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F52">
         <v>135</v>
       </c>
       <c r="G52">
-        <f t="shared" ref="G52:G115" si="29">G51*2</f>
+        <f t="shared" ref="G52:G115" si="43">G51*2</f>
         <v>270</v>
       </c>
     </row>
@@ -6261,14 +6647,14 @@
         <v>7</v>
       </c>
       <c r="E53" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F53">
         <v>405</v>
       </c>
       <c r="G53">
-        <f t="shared" si="29"/>
-        <v>540</v>
+        <f t="shared" ref="G53:G116" si="44">ROUNDUP(G52*1.7,-1)</f>
+        <v>460</v>
       </c>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.3">
@@ -6282,13 +6668,13 @@
         <v>8</v>
       </c>
       <c r="E54" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F54">
         <v>84</v>
       </c>
       <c r="G54">
-        <f t="shared" ref="G54" si="30">G51+5</f>
+        <f t="shared" ref="G54" si="45">G51+5</f>
         <v>140</v>
       </c>
     </row>
@@ -6303,13 +6689,13 @@
         <v>8</v>
       </c>
       <c r="E55" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F55">
         <v>140</v>
       </c>
       <c r="G55">
-        <f t="shared" ref="G55:G118" si="31">G54*2</f>
+        <f t="shared" ref="G55:G118" si="46">G54*2</f>
         <v>280</v>
       </c>
     </row>
@@ -6324,14 +6710,14 @@
         <v>8</v>
       </c>
       <c r="E56" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F56">
         <v>420</v>
       </c>
       <c r="G56">
-        <f t="shared" si="31"/>
-        <v>560</v>
+        <f t="shared" ref="G56:G119" si="47">ROUNDUP(G55*1.7,-1)</f>
+        <v>480</v>
       </c>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.3">
@@ -6345,13 +6731,13 @@
         <v>9</v>
       </c>
       <c r="E57" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F57">
         <v>87</v>
       </c>
       <c r="G57">
-        <f t="shared" ref="G57" si="32">G54+5</f>
+        <f t="shared" ref="G57" si="48">G54+5</f>
         <v>145</v>
       </c>
     </row>
@@ -6366,13 +6752,13 @@
         <v>9</v>
       </c>
       <c r="E58" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F58">
         <v>145</v>
       </c>
       <c r="G58">
-        <f t="shared" ref="G58:G121" si="33">G57*2</f>
+        <f t="shared" ref="G58:G121" si="49">G57*2</f>
         <v>290</v>
       </c>
     </row>
@@ -6387,14 +6773,14 @@
         <v>9</v>
       </c>
       <c r="E59" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F59">
         <v>435</v>
       </c>
       <c r="G59">
-        <f t="shared" si="33"/>
-        <v>580</v>
+        <f t="shared" ref="G59:G122" si="50">ROUNDUP(G58*1.7,-1)</f>
+        <v>500</v>
       </c>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.3">
@@ -6408,13 +6794,13 @@
         <v>10</v>
       </c>
       <c r="E60" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F60">
         <v>90</v>
       </c>
       <c r="G60">
-        <f t="shared" ref="G60" si="34">G57+5</f>
+        <f t="shared" ref="G60" si="51">G57+5</f>
         <v>150</v>
       </c>
     </row>
@@ -6429,13 +6815,13 @@
         <v>10</v>
       </c>
       <c r="E61" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F61">
         <v>150</v>
       </c>
       <c r="G61">
-        <f t="shared" ref="G61:G124" si="35">G60*2</f>
+        <f t="shared" ref="G61:G124" si="52">G60*2</f>
         <v>300</v>
       </c>
     </row>
@@ -6450,14 +6836,14 @@
         <v>10</v>
       </c>
       <c r="E62" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F62">
         <v>450</v>
       </c>
       <c r="G62">
-        <f t="shared" si="35"/>
-        <v>600</v>
+        <f t="shared" ref="G62:G125" si="53">ROUNDUP(G61*1.7,-1)</f>
+        <v>510</v>
       </c>
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.3">
@@ -6471,13 +6857,13 @@
         <v>1</v>
       </c>
       <c r="E63" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F63">
         <v>93</v>
       </c>
       <c r="G63">
-        <f t="shared" ref="G63" si="36">G60+5</f>
+        <f t="shared" ref="G63" si="54">G60+5</f>
         <v>155</v>
       </c>
     </row>
@@ -6492,13 +6878,13 @@
         <v>1</v>
       </c>
       <c r="E64" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F64">
         <v>155</v>
       </c>
       <c r="G64">
-        <f t="shared" ref="G64:G127" si="37">G63*2</f>
+        <f t="shared" ref="G64:G127" si="55">G63*2</f>
         <v>310</v>
       </c>
     </row>
@@ -6513,14 +6899,14 @@
         <v>1</v>
       </c>
       <c r="E65" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F65">
         <v>465</v>
       </c>
       <c r="G65">
-        <f t="shared" si="37"/>
-        <v>620</v>
+        <f t="shared" ref="G65:G128" si="56">ROUNDUP(G64*1.7,-1)</f>
+        <v>530</v>
       </c>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.3">
@@ -6534,13 +6920,13 @@
         <v>2</v>
       </c>
       <c r="E66" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F66">
         <v>96</v>
       </c>
       <c r="G66">
-        <f t="shared" ref="G66" si="38">G63+5</f>
+        <f t="shared" ref="G66" si="57">G63+5</f>
         <v>160</v>
       </c>
     </row>
@@ -6555,13 +6941,13 @@
         <v>2</v>
       </c>
       <c r="E67" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F67">
         <v>160</v>
       </c>
       <c r="G67">
-        <f t="shared" ref="G67:G130" si="39">G66*2</f>
+        <f t="shared" ref="G67:G130" si="58">G66*2</f>
         <v>320</v>
       </c>
     </row>
@@ -6576,14 +6962,14 @@
         <v>2</v>
       </c>
       <c r="E68" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F68">
         <v>480</v>
       </c>
       <c r="G68">
-        <f t="shared" si="39"/>
-        <v>640</v>
+        <f t="shared" ref="G68:G131" si="59">ROUNDUP(G67*1.7,-1)</f>
+        <v>550</v>
       </c>
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.3">
@@ -6597,13 +6983,13 @@
         <v>3</v>
       </c>
       <c r="E69" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F69">
         <v>99</v>
       </c>
       <c r="G69">
-        <f t="shared" ref="G69" si="40">G66+5</f>
+        <f t="shared" ref="G69" si="60">G66+5</f>
         <v>165</v>
       </c>
     </row>
@@ -6618,13 +7004,13 @@
         <v>3</v>
       </c>
       <c r="E70" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F70">
         <v>165</v>
       </c>
       <c r="G70">
-        <f t="shared" ref="G70:G133" si="41">G69*2</f>
+        <f t="shared" ref="G70:G133" si="61">G69*2</f>
         <v>330</v>
       </c>
     </row>
@@ -6639,14 +7025,14 @@
         <v>3</v>
       </c>
       <c r="E71" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F71">
         <v>495</v>
       </c>
       <c r="G71">
-        <f t="shared" si="41"/>
-        <v>660</v>
+        <f t="shared" ref="G71:G134" si="62">ROUNDUP(G70*1.7,-1)</f>
+        <v>570</v>
       </c>
     </row>
     <row r="72" spans="2:7" x14ac:dyDescent="0.3">
@@ -6660,13 +7046,13 @@
         <v>4</v>
       </c>
       <c r="E72" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F72">
         <v>102</v>
       </c>
       <c r="G72">
-        <f t="shared" ref="G72" si="42">G69+5</f>
+        <f t="shared" ref="G72" si="63">G69+5</f>
         <v>170</v>
       </c>
     </row>
@@ -6681,13 +7067,13 @@
         <v>4</v>
       </c>
       <c r="E73" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F73">
         <v>170</v>
       </c>
       <c r="G73">
-        <f t="shared" ref="G73:G136" si="43">G72*2</f>
+        <f t="shared" ref="G73:G136" si="64">G72*2</f>
         <v>340</v>
       </c>
     </row>
@@ -6702,14 +7088,14 @@
         <v>4</v>
       </c>
       <c r="E74" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F74">
         <v>510</v>
       </c>
       <c r="G74">
-        <f t="shared" si="43"/>
-        <v>680</v>
+        <f t="shared" ref="G74:G137" si="65">ROUNDUP(G73*1.7,-1)</f>
+        <v>580</v>
       </c>
     </row>
     <row r="75" spans="2:7" x14ac:dyDescent="0.3">
@@ -6723,13 +7109,13 @@
         <v>5</v>
       </c>
       <c r="E75" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F75">
         <v>105</v>
       </c>
       <c r="G75">
-        <f t="shared" ref="G75" si="44">G72+5</f>
+        <f t="shared" ref="G75" si="66">G72+5</f>
         <v>175</v>
       </c>
     </row>
@@ -6744,13 +7130,13 @@
         <v>5</v>
       </c>
       <c r="E76" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F76">
         <v>175</v>
       </c>
       <c r="G76">
-        <f t="shared" ref="G76:G139" si="45">G75*2</f>
+        <f t="shared" ref="G76:G139" si="67">G75*2</f>
         <v>350</v>
       </c>
     </row>
@@ -6765,14 +7151,14 @@
         <v>5</v>
       </c>
       <c r="E77" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F77">
         <v>525</v>
       </c>
       <c r="G77">
-        <f t="shared" si="45"/>
-        <v>700</v>
+        <f t="shared" ref="G77:G140" si="68">ROUNDUP(G76*1.7,-1)</f>
+        <v>600</v>
       </c>
     </row>
     <row r="78" spans="2:7" x14ac:dyDescent="0.3">
@@ -6786,13 +7172,13 @@
         <v>6</v>
       </c>
       <c r="E78" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F78">
         <v>108</v>
       </c>
       <c r="G78">
-        <f t="shared" ref="G78" si="46">G75+5</f>
+        <f t="shared" ref="G78" si="69">G75+5</f>
         <v>180</v>
       </c>
     </row>
@@ -6807,13 +7193,13 @@
         <v>6</v>
       </c>
       <c r="E79" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F79">
         <v>180</v>
       </c>
       <c r="G79">
-        <f t="shared" ref="G79:G142" si="47">G78*2</f>
+        <f t="shared" ref="G79:G142" si="70">G78*2</f>
         <v>360</v>
       </c>
     </row>
@@ -6828,14 +7214,14 @@
         <v>6</v>
       </c>
       <c r="E80" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F80">
         <v>540</v>
       </c>
       <c r="G80">
-        <f t="shared" si="47"/>
-        <v>720</v>
+        <f t="shared" ref="G80:G143" si="71">ROUNDUP(G79*1.7,-1)</f>
+        <v>620</v>
       </c>
     </row>
     <row r="81" spans="2:7" x14ac:dyDescent="0.3">
@@ -6849,13 +7235,13 @@
         <v>7</v>
       </c>
       <c r="E81" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F81">
         <v>111</v>
       </c>
       <c r="G81">
-        <f t="shared" ref="G81" si="48">G78+5</f>
+        <f t="shared" ref="G81" si="72">G78+5</f>
         <v>185</v>
       </c>
     </row>
@@ -6870,13 +7256,13 @@
         <v>7</v>
       </c>
       <c r="E82" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F82">
         <v>185</v>
       </c>
       <c r="G82">
-        <f t="shared" ref="G82:G145" si="49">G81*2</f>
+        <f t="shared" ref="G82:G145" si="73">G81*2</f>
         <v>370</v>
       </c>
     </row>
@@ -6891,14 +7277,14 @@
         <v>7</v>
       </c>
       <c r="E83" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F83">
         <v>555</v>
       </c>
       <c r="G83">
-        <f t="shared" si="49"/>
-        <v>740</v>
+        <f t="shared" ref="G83:G146" si="74">ROUNDUP(G82*1.7,-1)</f>
+        <v>630</v>
       </c>
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.3">
@@ -6912,13 +7298,13 @@
         <v>8</v>
       </c>
       <c r="E84" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F84">
         <v>114</v>
       </c>
       <c r="G84">
-        <f t="shared" ref="G84" si="50">G81+5</f>
+        <f t="shared" ref="G84" si="75">G81+5</f>
         <v>190</v>
       </c>
     </row>
@@ -6933,13 +7319,13 @@
         <v>8</v>
       </c>
       <c r="E85" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F85">
         <v>190</v>
       </c>
       <c r="G85">
-        <f t="shared" ref="G85:G148" si="51">G84*2</f>
+        <f t="shared" ref="G85:G148" si="76">G84*2</f>
         <v>380</v>
       </c>
     </row>
@@ -6954,14 +7340,14 @@
         <v>8</v>
       </c>
       <c r="E86" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F86">
         <v>570</v>
       </c>
       <c r="G86">
-        <f t="shared" si="51"/>
-        <v>760</v>
+        <f t="shared" ref="G86:G149" si="77">ROUNDUP(G85*1.7,-1)</f>
+        <v>650</v>
       </c>
     </row>
     <row r="87" spans="2:7" x14ac:dyDescent="0.3">
@@ -6975,13 +7361,13 @@
         <v>9</v>
       </c>
       <c r="E87" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F87">
         <v>117</v>
       </c>
       <c r="G87">
-        <f t="shared" ref="G87" si="52">G84+5</f>
+        <f t="shared" ref="G87" si="78">G84+5</f>
         <v>195</v>
       </c>
     </row>
@@ -6996,13 +7382,13 @@
         <v>9</v>
       </c>
       <c r="E88" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F88">
         <v>195</v>
       </c>
       <c r="G88">
-        <f t="shared" ref="G88:G151" si="53">G87*2</f>
+        <f t="shared" ref="G88:G151" si="79">G87*2</f>
         <v>390</v>
       </c>
     </row>
@@ -7017,14 +7403,14 @@
         <v>9</v>
       </c>
       <c r="E89" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F89">
         <v>585</v>
       </c>
       <c r="G89">
-        <f t="shared" si="53"/>
-        <v>780</v>
+        <f t="shared" ref="G89:G152" si="80">ROUNDUP(G88*1.7,-1)</f>
+        <v>670</v>
       </c>
     </row>
     <row r="90" spans="2:7" x14ac:dyDescent="0.3">
@@ -7038,13 +7424,13 @@
         <v>10</v>
       </c>
       <c r="E90" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F90">
         <v>120</v>
       </c>
       <c r="G90">
-        <f t="shared" ref="G90" si="54">G87+5</f>
+        <f t="shared" ref="G90" si="81">G87+5</f>
         <v>200</v>
       </c>
     </row>
@@ -7059,13 +7445,13 @@
         <v>10</v>
       </c>
       <c r="E91" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F91">
         <v>200</v>
       </c>
       <c r="G91">
-        <f t="shared" ref="G91:G154" si="55">G90*2</f>
+        <f t="shared" ref="G91:G154" si="82">G90*2</f>
         <v>400</v>
       </c>
     </row>
@@ -7080,14 +7466,14 @@
         <v>10</v>
       </c>
       <c r="E92" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F92">
         <v>600</v>
       </c>
       <c r="G92">
-        <f t="shared" si="55"/>
-        <v>800</v>
+        <f t="shared" ref="G92:G155" si="83">ROUNDUP(G91*1.7,-1)</f>
+        <v>680</v>
       </c>
     </row>
     <row r="93" spans="2:7" x14ac:dyDescent="0.3">
@@ -7101,13 +7487,13 @@
         <v>1</v>
       </c>
       <c r="E93" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F93">
         <v>123</v>
       </c>
       <c r="G93">
-        <f t="shared" ref="G93" si="56">G90+5</f>
+        <f t="shared" ref="G93" si="84">G90+5</f>
         <v>205</v>
       </c>
     </row>
@@ -7122,13 +7508,13 @@
         <v>1</v>
       </c>
       <c r="E94" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F94">
         <v>205</v>
       </c>
       <c r="G94">
-        <f t="shared" ref="G94:G157" si="57">G93*2</f>
+        <f t="shared" ref="G94:G157" si="85">G93*2</f>
         <v>410</v>
       </c>
     </row>
@@ -7143,14 +7529,14 @@
         <v>1</v>
       </c>
       <c r="E95" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F95">
         <v>615</v>
       </c>
       <c r="G95">
-        <f t="shared" si="57"/>
-        <v>820</v>
+        <f t="shared" ref="G95:G158" si="86">ROUNDUP(G94*1.7,-1)</f>
+        <v>700</v>
       </c>
     </row>
     <row r="96" spans="2:7" x14ac:dyDescent="0.3">
@@ -7164,13 +7550,13 @@
         <v>2</v>
       </c>
       <c r="E96" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F96">
         <v>126</v>
       </c>
       <c r="G96">
-        <f t="shared" ref="G96" si="58">G93+5</f>
+        <f t="shared" ref="G96" si="87">G93+5</f>
         <v>210</v>
       </c>
     </row>
@@ -7185,13 +7571,13 @@
         <v>2</v>
       </c>
       <c r="E97" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F97">
         <v>210</v>
       </c>
       <c r="G97">
-        <f t="shared" ref="G97:G160" si="59">G96*2</f>
+        <f t="shared" ref="G97:G160" si="88">G96*2</f>
         <v>420</v>
       </c>
     </row>
@@ -7206,14 +7592,14 @@
         <v>2</v>
       </c>
       <c r="E98" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F98">
         <v>630</v>
       </c>
       <c r="G98">
-        <f t="shared" si="59"/>
-        <v>840</v>
+        <f t="shared" ref="G98:G161" si="89">ROUNDUP(G97*1.7,-1)</f>
+        <v>720</v>
       </c>
     </row>
     <row r="99" spans="2:7" x14ac:dyDescent="0.3">
@@ -7227,13 +7613,13 @@
         <v>3</v>
       </c>
       <c r="E99" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F99">
         <v>129</v>
       </c>
       <c r="G99">
-        <f t="shared" ref="G99" si="60">G96+5</f>
+        <f t="shared" ref="G99" si="90">G96+5</f>
         <v>215</v>
       </c>
     </row>
@@ -7248,13 +7634,13 @@
         <v>3</v>
       </c>
       <c r="E100" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F100">
         <v>215</v>
       </c>
       <c r="G100">
-        <f t="shared" ref="G100:G163" si="61">G99*2</f>
+        <f t="shared" ref="G100:G163" si="91">G99*2</f>
         <v>430</v>
       </c>
     </row>
@@ -7269,14 +7655,14 @@
         <v>3</v>
       </c>
       <c r="E101" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F101">
         <v>645</v>
       </c>
       <c r="G101">
-        <f t="shared" si="61"/>
-        <v>860</v>
+        <f t="shared" ref="G101:G164" si="92">ROUNDUP(G100*1.7,-1)</f>
+        <v>740</v>
       </c>
     </row>
     <row r="102" spans="2:7" x14ac:dyDescent="0.3">
@@ -7290,13 +7676,13 @@
         <v>4</v>
       </c>
       <c r="E102" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F102">
         <v>132</v>
       </c>
       <c r="G102">
-        <f t="shared" ref="G102" si="62">G99+5</f>
+        <f t="shared" ref="G102" si="93">G99+5</f>
         <v>220</v>
       </c>
     </row>
@@ -7311,13 +7697,13 @@
         <v>4</v>
       </c>
       <c r="E103" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F103">
         <v>220</v>
       </c>
       <c r="G103">
-        <f t="shared" ref="G103:G134" si="63">G102*2</f>
+        <f t="shared" ref="G103:G134" si="94">G102*2</f>
         <v>440</v>
       </c>
     </row>
@@ -7332,14 +7718,14 @@
         <v>4</v>
       </c>
       <c r="E104" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F104">
         <v>660</v>
       </c>
       <c r="G104">
-        <f t="shared" si="63"/>
-        <v>880</v>
+        <f t="shared" ref="G104:G135" si="95">ROUNDUP(G103*1.7,-1)</f>
+        <v>750</v>
       </c>
     </row>
     <row r="105" spans="2:7" x14ac:dyDescent="0.3">
@@ -7353,13 +7739,13 @@
         <v>5</v>
       </c>
       <c r="E105" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F105">
         <v>135</v>
       </c>
       <c r="G105">
-        <f t="shared" ref="G105" si="64">G102+5</f>
+        <f t="shared" ref="G105" si="96">G102+5</f>
         <v>225</v>
       </c>
     </row>
@@ -7374,13 +7760,13 @@
         <v>5</v>
       </c>
       <c r="E106" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F106">
         <v>225</v>
       </c>
       <c r="G106">
-        <f t="shared" ref="G106:G137" si="65">G105*2</f>
+        <f t="shared" ref="G106:G137" si="97">G105*2</f>
         <v>450</v>
       </c>
     </row>
@@ -7395,14 +7781,14 @@
         <v>5</v>
       </c>
       <c r="E107" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F107">
         <v>675</v>
       </c>
       <c r="G107">
-        <f t="shared" si="65"/>
-        <v>900</v>
+        <f t="shared" ref="G107:G138" si="98">ROUNDUP(G106*1.7,-1)</f>
+        <v>770</v>
       </c>
     </row>
     <row r="108" spans="2:7" x14ac:dyDescent="0.3">
@@ -7416,13 +7802,13 @@
         <v>6</v>
       </c>
       <c r="E108" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F108">
         <v>138</v>
       </c>
       <c r="G108">
-        <f t="shared" ref="G108" si="66">G105+5</f>
+        <f t="shared" ref="G108" si="99">G105+5</f>
         <v>230</v>
       </c>
     </row>
@@ -7437,13 +7823,13 @@
         <v>6</v>
       </c>
       <c r="E109" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F109">
         <v>230</v>
       </c>
       <c r="G109">
-        <f t="shared" ref="G109:G140" si="67">G108*2</f>
+        <f t="shared" ref="G109:G140" si="100">G108*2</f>
         <v>460</v>
       </c>
     </row>
@@ -7458,14 +7844,14 @@
         <v>6</v>
       </c>
       <c r="E110" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F110">
         <v>690</v>
       </c>
       <c r="G110">
-        <f t="shared" si="67"/>
-        <v>920</v>
+        <f t="shared" ref="G110:G141" si="101">ROUNDUP(G109*1.7,-1)</f>
+        <v>790</v>
       </c>
     </row>
     <row r="111" spans="2:7" x14ac:dyDescent="0.3">
@@ -7479,13 +7865,13 @@
         <v>7</v>
       </c>
       <c r="E111" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F111">
         <v>141</v>
       </c>
       <c r="G111">
-        <f t="shared" ref="G111" si="68">G108+5</f>
+        <f t="shared" ref="G111" si="102">G108+5</f>
         <v>235</v>
       </c>
     </row>
@@ -7500,13 +7886,13 @@
         <v>7</v>
       </c>
       <c r="E112" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F112">
         <v>235</v>
       </c>
       <c r="G112">
-        <f t="shared" ref="G112:G143" si="69">G111*2</f>
+        <f t="shared" ref="G112:G143" si="103">G111*2</f>
         <v>470</v>
       </c>
     </row>
@@ -7521,14 +7907,14 @@
         <v>7</v>
       </c>
       <c r="E113" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F113">
         <v>705</v>
       </c>
       <c r="G113">
-        <f t="shared" si="69"/>
-        <v>940</v>
+        <f t="shared" ref="G113:G144" si="104">ROUNDUP(G112*1.7,-1)</f>
+        <v>800</v>
       </c>
     </row>
     <row r="114" spans="2:7" x14ac:dyDescent="0.3">
@@ -7542,13 +7928,13 @@
         <v>8</v>
       </c>
       <c r="E114" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F114">
         <v>144</v>
       </c>
       <c r="G114">
-        <f t="shared" ref="G114" si="70">G111+5</f>
+        <f t="shared" ref="G114" si="105">G111+5</f>
         <v>240</v>
       </c>
     </row>
@@ -7563,13 +7949,13 @@
         <v>8</v>
       </c>
       <c r="E115" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F115">
         <v>240</v>
       </c>
       <c r="G115">
-        <f t="shared" ref="G115:G146" si="71">G114*2</f>
+        <f t="shared" ref="G115:G146" si="106">G114*2</f>
         <v>480</v>
       </c>
     </row>
@@ -7584,14 +7970,14 @@
         <v>8</v>
       </c>
       <c r="E116" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F116">
         <v>720</v>
       </c>
       <c r="G116">
-        <f t="shared" si="71"/>
-        <v>960</v>
+        <f t="shared" ref="G116:G147" si="107">ROUNDUP(G115*1.7,-1)</f>
+        <v>820</v>
       </c>
     </row>
     <row r="117" spans="2:7" x14ac:dyDescent="0.3">
@@ -7605,13 +7991,13 @@
         <v>9</v>
       </c>
       <c r="E117" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F117">
         <v>147</v>
       </c>
       <c r="G117">
-        <f t="shared" ref="G117" si="72">G114+5</f>
+        <f t="shared" ref="G117" si="108">G114+5</f>
         <v>245</v>
       </c>
     </row>
@@ -7626,13 +8012,13 @@
         <v>9</v>
       </c>
       <c r="E118" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F118">
         <v>245</v>
       </c>
       <c r="G118">
-        <f t="shared" ref="G118:G149" si="73">G117*2</f>
+        <f t="shared" ref="G118:G149" si="109">G117*2</f>
         <v>490</v>
       </c>
     </row>
@@ -7647,14 +8033,14 @@
         <v>9</v>
       </c>
       <c r="E119" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F119">
         <v>735</v>
       </c>
       <c r="G119">
-        <f t="shared" si="73"/>
-        <v>980</v>
+        <f t="shared" ref="G119:G150" si="110">ROUNDUP(G118*1.7,-1)</f>
+        <v>840</v>
       </c>
     </row>
     <row r="120" spans="2:7" x14ac:dyDescent="0.3">
@@ -7668,13 +8054,13 @@
         <v>10</v>
       </c>
       <c r="E120" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F120">
         <v>150</v>
       </c>
       <c r="G120">
-        <f t="shared" ref="G120" si="74">G117+5</f>
+        <f t="shared" ref="G120" si="111">G117+5</f>
         <v>250</v>
       </c>
     </row>
@@ -7689,13 +8075,13 @@
         <v>10</v>
       </c>
       <c r="E121" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F121">
         <v>250</v>
       </c>
       <c r="G121">
-        <f t="shared" ref="G121:G152" si="75">G120*2</f>
+        <f t="shared" ref="G121:G152" si="112">G120*2</f>
         <v>500</v>
       </c>
     </row>
@@ -7710,14 +8096,14 @@
         <v>10</v>
       </c>
       <c r="E122" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F122">
         <v>750</v>
       </c>
       <c r="G122">
-        <f t="shared" si="75"/>
-        <v>1000</v>
+        <f t="shared" ref="G122:G153" si="113">ROUNDUP(G121*1.7,-1)</f>
+        <v>850</v>
       </c>
     </row>
     <row r="123" spans="2:7" x14ac:dyDescent="0.3">
@@ -7731,13 +8117,13 @@
         <v>1</v>
       </c>
       <c r="E123" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F123">
         <v>153</v>
       </c>
       <c r="G123">
-        <f t="shared" ref="G123" si="76">G120+5</f>
+        <f t="shared" ref="G123" si="114">G120+5</f>
         <v>255</v>
       </c>
     </row>
@@ -7752,13 +8138,13 @@
         <v>1</v>
       </c>
       <c r="E124" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F124">
         <v>255</v>
       </c>
       <c r="G124">
-        <f t="shared" ref="G124:G155" si="77">G123*2</f>
+        <f t="shared" ref="G124:G155" si="115">G123*2</f>
         <v>510</v>
       </c>
     </row>
@@ -7773,14 +8159,14 @@
         <v>1</v>
       </c>
       <c r="E125" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F125">
         <v>765</v>
       </c>
       <c r="G125">
-        <f t="shared" si="77"/>
-        <v>1020</v>
+        <f t="shared" ref="G125:G156" si="116">ROUNDUP(G124*1.7,-1)</f>
+        <v>870</v>
       </c>
     </row>
     <row r="126" spans="2:7" x14ac:dyDescent="0.3">
@@ -7794,13 +8180,13 @@
         <v>2</v>
       </c>
       <c r="E126" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F126">
         <v>156</v>
       </c>
       <c r="G126">
-        <f t="shared" ref="G126" si="78">G123+5</f>
+        <f t="shared" ref="G126" si="117">G123+5</f>
         <v>260</v>
       </c>
     </row>
@@ -7815,13 +8201,13 @@
         <v>2</v>
       </c>
       <c r="E127" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F127">
         <v>260</v>
       </c>
       <c r="G127">
-        <f t="shared" ref="G127:G158" si="79">G126*2</f>
+        <f t="shared" ref="G127:G158" si="118">G126*2</f>
         <v>520</v>
       </c>
     </row>
@@ -7836,14 +8222,14 @@
         <v>2</v>
       </c>
       <c r="E128" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F128">
         <v>780</v>
       </c>
       <c r="G128">
-        <f t="shared" si="79"/>
-        <v>1040</v>
+        <f t="shared" ref="G128:G159" si="119">ROUNDUP(G127*1.7,-1)</f>
+        <v>890</v>
       </c>
     </row>
     <row r="129" spans="2:7" x14ac:dyDescent="0.3">
@@ -7857,13 +8243,13 @@
         <v>3</v>
       </c>
       <c r="E129" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F129">
         <v>159</v>
       </c>
       <c r="G129">
-        <f t="shared" ref="G129" si="80">G126+5</f>
+        <f t="shared" ref="G129" si="120">G126+5</f>
         <v>265</v>
       </c>
     </row>
@@ -7878,13 +8264,13 @@
         <v>3</v>
       </c>
       <c r="E130" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F130">
         <v>265</v>
       </c>
       <c r="G130">
-        <f t="shared" ref="G130:G161" si="81">G129*2</f>
+        <f t="shared" ref="G130:G161" si="121">G129*2</f>
         <v>530</v>
       </c>
     </row>
@@ -7899,14 +8285,14 @@
         <v>3</v>
       </c>
       <c r="E131" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F131">
         <v>795</v>
       </c>
       <c r="G131">
-        <f t="shared" si="81"/>
-        <v>1060</v>
+        <f t="shared" ref="G131:G162" si="122">ROUNDUP(G130*1.7,-1)</f>
+        <v>910</v>
       </c>
     </row>
     <row r="132" spans="2:7" x14ac:dyDescent="0.3">
@@ -7920,13 +8306,13 @@
         <v>4</v>
       </c>
       <c r="E132" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F132">
         <v>162</v>
       </c>
       <c r="G132">
-        <f t="shared" ref="G132" si="82">G129+5</f>
+        <f t="shared" ref="G132" si="123">G129+5</f>
         <v>270</v>
       </c>
     </row>
@@ -7941,13 +8327,13 @@
         <v>4</v>
       </c>
       <c r="E133" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F133">
         <v>270</v>
       </c>
       <c r="G133">
-        <f t="shared" ref="G133:G164" si="83">G132*2</f>
+        <f t="shared" ref="G133:G164" si="124">G132*2</f>
         <v>540</v>
       </c>
     </row>
@@ -7962,14 +8348,14 @@
         <v>4</v>
       </c>
       <c r="E134" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F134">
         <v>810</v>
       </c>
       <c r="G134">
-        <f t="shared" si="83"/>
-        <v>1080</v>
+        <f t="shared" ref="G134:G165" si="125">ROUNDUP(G133*1.7,-1)</f>
+        <v>920</v>
       </c>
     </row>
     <row r="135" spans="2:7" x14ac:dyDescent="0.3">
@@ -7983,13 +8369,13 @@
         <v>5</v>
       </c>
       <c r="E135" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F135">
         <v>165</v>
       </c>
       <c r="G135">
-        <f t="shared" ref="G135" si="84">G132+5</f>
+        <f t="shared" ref="G135" si="126">G132+5</f>
         <v>275</v>
       </c>
     </row>
@@ -8004,13 +8390,13 @@
         <v>5</v>
       </c>
       <c r="E136" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F136">
         <v>275</v>
       </c>
       <c r="G136">
-        <f t="shared" ref="G136:G167" si="85">G135*2</f>
+        <f t="shared" ref="G136:G167" si="127">G135*2</f>
         <v>550</v>
       </c>
     </row>
@@ -8025,14 +8411,14 @@
         <v>5</v>
       </c>
       <c r="E137" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F137">
         <v>825</v>
       </c>
       <c r="G137">
-        <f t="shared" si="85"/>
-        <v>1100</v>
+        <f t="shared" ref="G137:G168" si="128">ROUNDUP(G136*1.7,-1)</f>
+        <v>940</v>
       </c>
     </row>
     <row r="138" spans="2:7" x14ac:dyDescent="0.3">
@@ -8046,13 +8432,13 @@
         <v>6</v>
       </c>
       <c r="E138" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F138">
         <v>168</v>
       </c>
       <c r="G138">
-        <f t="shared" ref="G138" si="86">G135+5</f>
+        <f t="shared" ref="G138" si="129">G135+5</f>
         <v>280</v>
       </c>
     </row>
@@ -8067,13 +8453,13 @@
         <v>6</v>
       </c>
       <c r="E139" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F139">
         <v>280</v>
       </c>
       <c r="G139">
-        <f t="shared" ref="G139:G170" si="87">G138*2</f>
+        <f t="shared" ref="G139:G170" si="130">G138*2</f>
         <v>560</v>
       </c>
     </row>
@@ -8088,14 +8474,14 @@
         <v>6</v>
       </c>
       <c r="E140" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F140">
         <v>840</v>
       </c>
       <c r="G140">
-        <f t="shared" si="87"/>
-        <v>1120</v>
+        <f t="shared" ref="G140:G171" si="131">ROUNDUP(G139*1.7,-1)</f>
+        <v>960</v>
       </c>
     </row>
     <row r="141" spans="2:7" x14ac:dyDescent="0.3">
@@ -8109,13 +8495,13 @@
         <v>7</v>
       </c>
       <c r="E141" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F141">
         <v>171</v>
       </c>
       <c r="G141">
-        <f t="shared" ref="G141" si="88">G138+5</f>
+        <f t="shared" ref="G141" si="132">G138+5</f>
         <v>285</v>
       </c>
     </row>
@@ -8130,13 +8516,13 @@
         <v>7</v>
       </c>
       <c r="E142" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F142">
         <v>285</v>
       </c>
       <c r="G142">
-        <f t="shared" ref="G142:G173" si="89">G141*2</f>
+        <f t="shared" ref="G142:G173" si="133">G141*2</f>
         <v>570</v>
       </c>
     </row>
@@ -8151,14 +8537,14 @@
         <v>7</v>
       </c>
       <c r="E143" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F143">
         <v>855</v>
       </c>
       <c r="G143">
-        <f t="shared" si="89"/>
-        <v>1140</v>
+        <f t="shared" ref="G143:G174" si="134">ROUNDUP(G142*1.7,-1)</f>
+        <v>970</v>
       </c>
     </row>
     <row r="144" spans="2:7" x14ac:dyDescent="0.3">
@@ -8172,13 +8558,13 @@
         <v>8</v>
       </c>
       <c r="E144" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F144">
         <v>174</v>
       </c>
       <c r="G144">
-        <f t="shared" ref="G144" si="90">G141+5</f>
+        <f t="shared" ref="G144" si="135">G141+5</f>
         <v>290</v>
       </c>
     </row>
@@ -8193,13 +8579,13 @@
         <v>8</v>
       </c>
       <c r="E145" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F145">
         <v>290</v>
       </c>
       <c r="G145">
-        <f t="shared" ref="G145:G176" si="91">G144*2</f>
+        <f t="shared" ref="G145:G176" si="136">G144*2</f>
         <v>580</v>
       </c>
     </row>
@@ -8214,14 +8600,14 @@
         <v>8</v>
       </c>
       <c r="E146" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F146">
         <v>870</v>
       </c>
       <c r="G146">
-        <f t="shared" si="91"/>
-        <v>1160</v>
+        <f t="shared" ref="G146:G177" si="137">ROUNDUP(G145*1.7,-1)</f>
+        <v>990</v>
       </c>
     </row>
     <row r="147" spans="2:7" x14ac:dyDescent="0.3">
@@ -8235,13 +8621,13 @@
         <v>9</v>
       </c>
       <c r="E147" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F147">
         <v>177</v>
       </c>
       <c r="G147">
-        <f t="shared" ref="G147" si="92">G144+5</f>
+        <f t="shared" ref="G147" si="138">G144+5</f>
         <v>295</v>
       </c>
     </row>
@@ -8256,13 +8642,13 @@
         <v>9</v>
       </c>
       <c r="E148" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F148">
         <v>295</v>
       </c>
       <c r="G148">
-        <f t="shared" ref="G148:G179" si="93">G147*2</f>
+        <f t="shared" ref="G148:G179" si="139">G147*2</f>
         <v>590</v>
       </c>
     </row>
@@ -8277,14 +8663,14 @@
         <v>9</v>
       </c>
       <c r="E149" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F149">
         <v>885</v>
       </c>
       <c r="G149">
-        <f t="shared" si="93"/>
-        <v>1180</v>
+        <f t="shared" ref="G149:G180" si="140">ROUNDUP(G148*1.7,-1)</f>
+        <v>1010</v>
       </c>
     </row>
     <row r="150" spans="2:7" x14ac:dyDescent="0.3">
@@ -8298,13 +8684,13 @@
         <v>10</v>
       </c>
       <c r="E150" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F150">
         <v>180</v>
       </c>
       <c r="G150">
-        <f t="shared" ref="G150" si="94">G147+5</f>
+        <f t="shared" ref="G150" si="141">G147+5</f>
         <v>300</v>
       </c>
     </row>
@@ -8319,13 +8705,13 @@
         <v>10</v>
       </c>
       <c r="E151" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F151">
         <v>300</v>
       </c>
       <c r="G151">
-        <f t="shared" ref="G151:G182" si="95">G150*2</f>
+        <f t="shared" ref="G151:G182" si="142">G150*2</f>
         <v>600</v>
       </c>
     </row>
@@ -8340,14 +8726,14 @@
         <v>10</v>
       </c>
       <c r="E152" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F152">
         <v>900</v>
       </c>
       <c r="G152">
-        <f t="shared" si="95"/>
-        <v>1200</v>
+        <f t="shared" ref="G152:G183" si="143">ROUNDUP(G151*1.7,-1)</f>
+        <v>1020</v>
       </c>
     </row>
     <row r="153" spans="2:7" x14ac:dyDescent="0.3">
@@ -8361,13 +8747,13 @@
         <v>1</v>
       </c>
       <c r="E153" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F153">
         <v>183</v>
       </c>
       <c r="G153">
-        <f t="shared" ref="G153" si="96">G150+5</f>
+        <f t="shared" ref="G153" si="144">G150+5</f>
         <v>305</v>
       </c>
     </row>
@@ -8382,13 +8768,13 @@
         <v>1</v>
       </c>
       <c r="E154" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F154">
         <v>305</v>
       </c>
       <c r="G154">
-        <f t="shared" ref="G154:G185" si="97">G153*2</f>
+        <f t="shared" ref="G154:G185" si="145">G153*2</f>
         <v>610</v>
       </c>
     </row>
@@ -8403,14 +8789,14 @@
         <v>1</v>
       </c>
       <c r="E155" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F155">
         <v>915</v>
       </c>
       <c r="G155">
-        <f t="shared" si="97"/>
-        <v>1220</v>
+        <f t="shared" ref="G155:G186" si="146">ROUNDUP(G154*1.7,-1)</f>
+        <v>1040</v>
       </c>
     </row>
     <row r="156" spans="2:7" x14ac:dyDescent="0.3">
@@ -8424,13 +8810,13 @@
         <v>2</v>
       </c>
       <c r="E156" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F156">
         <v>186</v>
       </c>
       <c r="G156">
-        <f t="shared" ref="G156" si="98">G153+5</f>
+        <f t="shared" ref="G156" si="147">G153+5</f>
         <v>310</v>
       </c>
     </row>
@@ -8445,13 +8831,13 @@
         <v>2</v>
       </c>
       <c r="E157" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F157">
         <v>310</v>
       </c>
       <c r="G157">
-        <f t="shared" ref="G157:G188" si="99">G156*2</f>
+        <f t="shared" ref="G157:G188" si="148">G156*2</f>
         <v>620</v>
       </c>
     </row>
@@ -8466,14 +8852,14 @@
         <v>2</v>
       </c>
       <c r="E158" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F158">
         <v>930</v>
       </c>
       <c r="G158">
-        <f t="shared" si="99"/>
-        <v>1240</v>
+        <f t="shared" ref="G158:G189" si="149">ROUNDUP(G157*1.7,-1)</f>
+        <v>1060</v>
       </c>
     </row>
     <row r="159" spans="2:7" x14ac:dyDescent="0.3">
@@ -8487,13 +8873,13 @@
         <v>3</v>
       </c>
       <c r="E159" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F159">
         <v>189</v>
       </c>
       <c r="G159">
-        <f t="shared" ref="G159" si="100">G156+5</f>
+        <f t="shared" ref="G159" si="150">G156+5</f>
         <v>315</v>
       </c>
     </row>
@@ -8508,13 +8894,13 @@
         <v>3</v>
       </c>
       <c r="E160" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F160">
         <v>315</v>
       </c>
       <c r="G160">
-        <f t="shared" ref="G160:G191" si="101">G159*2</f>
+        <f t="shared" ref="G160:G191" si="151">G159*2</f>
         <v>630</v>
       </c>
     </row>
@@ -8529,14 +8915,14 @@
         <v>3</v>
       </c>
       <c r="E161" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F161">
         <v>945</v>
       </c>
       <c r="G161">
-        <f t="shared" si="101"/>
-        <v>1260</v>
+        <f t="shared" ref="G161:G192" si="152">ROUNDUP(G160*1.7,-1)</f>
+        <v>1080</v>
       </c>
     </row>
     <row r="162" spans="2:7" x14ac:dyDescent="0.3">
@@ -8550,13 +8936,13 @@
         <v>4</v>
       </c>
       <c r="E162" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F162">
         <v>192</v>
       </c>
       <c r="G162">
-        <f t="shared" ref="G162" si="102">G159+5</f>
+        <f t="shared" ref="G162" si="153">G159+5</f>
         <v>320</v>
       </c>
     </row>
@@ -8571,13 +8957,13 @@
         <v>4</v>
       </c>
       <c r="E163" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F163">
         <v>320</v>
       </c>
       <c r="G163">
-        <f t="shared" ref="G163:G194" si="103">G162*2</f>
+        <f t="shared" ref="G163:G194" si="154">G162*2</f>
         <v>640</v>
       </c>
     </row>
@@ -8592,14 +8978,14 @@
         <v>4</v>
       </c>
       <c r="E164" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F164">
         <v>960</v>
       </c>
       <c r="G164">
-        <f t="shared" si="103"/>
-        <v>1280</v>
+        <f t="shared" ref="G164:G195" si="155">ROUNDUP(G163*1.7,-1)</f>
+        <v>1090</v>
       </c>
     </row>
     <row r="165" spans="2:7" x14ac:dyDescent="0.3">
@@ -8613,13 +8999,13 @@
         <v>5</v>
       </c>
       <c r="E165" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F165">
         <v>195</v>
       </c>
       <c r="G165">
-        <f t="shared" ref="G165" si="104">G162+5</f>
+        <f t="shared" ref="G165" si="156">G162+5</f>
         <v>325</v>
       </c>
     </row>
@@ -8634,13 +9020,13 @@
         <v>5</v>
       </c>
       <c r="E166" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F166">
         <v>325</v>
       </c>
       <c r="G166">
-        <f t="shared" ref="G166:G197" si="105">G165*2</f>
+        <f t="shared" ref="G166:G197" si="157">G165*2</f>
         <v>650</v>
       </c>
     </row>
@@ -8655,14 +9041,14 @@
         <v>5</v>
       </c>
       <c r="E167" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F167">
         <v>975</v>
       </c>
       <c r="G167">
-        <f t="shared" si="105"/>
-        <v>1300</v>
+        <f t="shared" ref="G167:G198" si="158">ROUNDUP(G166*1.7,-1)</f>
+        <v>1110</v>
       </c>
     </row>
     <row r="168" spans="2:7" x14ac:dyDescent="0.3">
@@ -8676,13 +9062,13 @@
         <v>6</v>
       </c>
       <c r="E168" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F168">
         <v>198</v>
       </c>
       <c r="G168">
-        <f t="shared" ref="G168" si="106">G165+5</f>
+        <f t="shared" ref="G168" si="159">G165+5</f>
         <v>330</v>
       </c>
     </row>
@@ -8697,13 +9083,13 @@
         <v>6</v>
       </c>
       <c r="E169" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F169">
         <v>330</v>
       </c>
       <c r="G169">
-        <f t="shared" ref="G169:G200" si="107">G168*2</f>
+        <f t="shared" ref="G169:G200" si="160">G168*2</f>
         <v>660</v>
       </c>
     </row>
@@ -8718,14 +9104,14 @@
         <v>6</v>
       </c>
       <c r="E170" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F170">
         <v>990</v>
       </c>
       <c r="G170">
-        <f t="shared" si="107"/>
-        <v>1320</v>
+        <f t="shared" ref="G170:G201" si="161">ROUNDUP(G169*1.7,-1)</f>
+        <v>1130</v>
       </c>
     </row>
     <row r="171" spans="2:7" x14ac:dyDescent="0.3">
@@ -8739,13 +9125,13 @@
         <v>7</v>
       </c>
       <c r="E171" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F171">
         <v>201</v>
       </c>
       <c r="G171">
-        <f t="shared" ref="G171" si="108">G168+5</f>
+        <f t="shared" ref="G171" si="162">G168+5</f>
         <v>335</v>
       </c>
     </row>
@@ -8760,13 +9146,13 @@
         <v>7</v>
       </c>
       <c r="E172" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F172">
         <v>335</v>
       </c>
       <c r="G172">
-        <f t="shared" ref="G172:G203" si="109">G171*2</f>
+        <f t="shared" ref="G172:G203" si="163">G171*2</f>
         <v>670</v>
       </c>
     </row>
@@ -8781,14 +9167,14 @@
         <v>7</v>
       </c>
       <c r="E173" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F173">
         <v>1005</v>
       </c>
       <c r="G173">
-        <f t="shared" si="109"/>
-        <v>1340</v>
+        <f t="shared" ref="G173:G204" si="164">ROUNDUP(G172*1.7,-1)</f>
+        <v>1140</v>
       </c>
     </row>
     <row r="174" spans="2:7" x14ac:dyDescent="0.3">
@@ -8802,13 +9188,13 @@
         <v>8</v>
       </c>
       <c r="E174" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F174">
         <v>204</v>
       </c>
       <c r="G174">
-        <f t="shared" ref="G174" si="110">G171+5</f>
+        <f t="shared" ref="G174" si="165">G171+5</f>
         <v>340</v>
       </c>
     </row>
@@ -8823,13 +9209,13 @@
         <v>8</v>
       </c>
       <c r="E175" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F175">
         <v>340</v>
       </c>
       <c r="G175">
-        <f t="shared" ref="G175:G206" si="111">G174*2</f>
+        <f t="shared" ref="G175:G206" si="166">G174*2</f>
         <v>680</v>
       </c>
     </row>
@@ -8844,14 +9230,14 @@
         <v>8</v>
       </c>
       <c r="E176" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F176">
         <v>1020</v>
       </c>
       <c r="G176">
-        <f t="shared" si="111"/>
-        <v>1360</v>
+        <f t="shared" ref="G176:G207" si="167">ROUNDUP(G175*1.7,-1)</f>
+        <v>1160</v>
       </c>
     </row>
     <row r="177" spans="2:7" x14ac:dyDescent="0.3">
@@ -8865,13 +9251,13 @@
         <v>9</v>
       </c>
       <c r="E177" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F177">
         <v>207</v>
       </c>
       <c r="G177">
-        <f t="shared" ref="G177" si="112">G174+5</f>
+        <f t="shared" ref="G177" si="168">G174+5</f>
         <v>345</v>
       </c>
     </row>
@@ -8886,13 +9272,13 @@
         <v>9</v>
       </c>
       <c r="E178" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F178">
         <v>345</v>
       </c>
       <c r="G178">
-        <f t="shared" ref="G178:G209" si="113">G177*2</f>
+        <f t="shared" ref="G178:G209" si="169">G177*2</f>
         <v>690</v>
       </c>
     </row>
@@ -8907,14 +9293,14 @@
         <v>9</v>
       </c>
       <c r="E179" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F179">
         <v>1035</v>
       </c>
       <c r="G179">
-        <f t="shared" si="113"/>
-        <v>1380</v>
+        <f t="shared" ref="G179:G210" si="170">ROUNDUP(G178*1.7,-1)</f>
+        <v>1180</v>
       </c>
     </row>
     <row r="180" spans="2:7" x14ac:dyDescent="0.3">
@@ -8928,13 +9314,13 @@
         <v>10</v>
       </c>
       <c r="E180" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F180">
         <v>210</v>
       </c>
       <c r="G180">
-        <f t="shared" ref="G180" si="114">G177+5</f>
+        <f t="shared" ref="G180" si="171">G177+5</f>
         <v>350</v>
       </c>
     </row>
@@ -8949,13 +9335,13 @@
         <v>10</v>
       </c>
       <c r="E181" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F181">
         <v>350</v>
       </c>
       <c r="G181">
-        <f t="shared" ref="G181:G212" si="115">G180*2</f>
+        <f t="shared" ref="G181:G212" si="172">G180*2</f>
         <v>700</v>
       </c>
     </row>
@@ -8970,14 +9356,14 @@
         <v>10</v>
       </c>
       <c r="E182" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F182">
         <v>1050</v>
       </c>
       <c r="G182">
-        <f t="shared" si="115"/>
-        <v>1400</v>
+        <f t="shared" ref="G182:G213" si="173">ROUNDUP(G181*1.7,-1)</f>
+        <v>1190</v>
       </c>
     </row>
     <row r="183" spans="2:7" x14ac:dyDescent="0.3">
@@ -8991,13 +9377,13 @@
         <v>1</v>
       </c>
       <c r="E183" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F183">
         <v>213</v>
       </c>
       <c r="G183">
-        <f t="shared" ref="G183" si="116">G180+5</f>
+        <f t="shared" ref="G183" si="174">G180+5</f>
         <v>355</v>
       </c>
     </row>
@@ -9012,13 +9398,13 @@
         <v>1</v>
       </c>
       <c r="E184" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F184">
         <v>355</v>
       </c>
       <c r="G184">
-        <f t="shared" ref="G184:G215" si="117">G183*2</f>
+        <f t="shared" ref="G184:G215" si="175">G183*2</f>
         <v>710</v>
       </c>
     </row>
@@ -9033,14 +9419,14 @@
         <v>1</v>
       </c>
       <c r="E185" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F185">
         <v>1065</v>
       </c>
       <c r="G185">
-        <f t="shared" si="117"/>
-        <v>1420</v>
+        <f t="shared" ref="G185:G216" si="176">ROUNDUP(G184*1.7,-1)</f>
+        <v>1210</v>
       </c>
     </row>
     <row r="186" spans="2:7" x14ac:dyDescent="0.3">
@@ -9054,13 +9440,13 @@
         <v>2</v>
       </c>
       <c r="E186" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F186">
         <v>216</v>
       </c>
       <c r="G186">
-        <f t="shared" ref="G186" si="118">G183+5</f>
+        <f t="shared" ref="G186" si="177">G183+5</f>
         <v>360</v>
       </c>
     </row>
@@ -9075,13 +9461,13 @@
         <v>2</v>
       </c>
       <c r="E187" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F187">
         <v>360</v>
       </c>
       <c r="G187">
-        <f t="shared" ref="G187:G218" si="119">G186*2</f>
+        <f t="shared" ref="G187:G218" si="178">G186*2</f>
         <v>720</v>
       </c>
     </row>
@@ -9096,14 +9482,14 @@
         <v>2</v>
       </c>
       <c r="E188" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F188">
         <v>1080</v>
       </c>
       <c r="G188">
-        <f t="shared" si="119"/>
-        <v>1440</v>
+        <f t="shared" ref="G188:G219" si="179">ROUNDUP(G187*1.7,-1)</f>
+        <v>1230</v>
       </c>
     </row>
     <row r="189" spans="2:7" x14ac:dyDescent="0.3">
@@ -9117,13 +9503,13 @@
         <v>3</v>
       </c>
       <c r="E189" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F189">
         <v>219</v>
       </c>
       <c r="G189">
-        <f t="shared" ref="G189" si="120">G186+5</f>
+        <f t="shared" ref="G189" si="180">G186+5</f>
         <v>365</v>
       </c>
     </row>
@@ -9138,13 +9524,13 @@
         <v>3</v>
       </c>
       <c r="E190" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F190">
         <v>365</v>
       </c>
       <c r="G190">
-        <f t="shared" ref="G190:G221" si="121">G189*2</f>
+        <f t="shared" ref="G190:G221" si="181">G189*2</f>
         <v>730</v>
       </c>
     </row>
@@ -9159,14 +9545,14 @@
         <v>3</v>
       </c>
       <c r="E191" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F191">
         <v>1095</v>
       </c>
       <c r="G191">
-        <f t="shared" si="121"/>
-        <v>1460</v>
+        <f t="shared" ref="G191:G222" si="182">ROUNDUP(G190*1.7,-1)</f>
+        <v>1250</v>
       </c>
     </row>
     <row r="192" spans="2:7" x14ac:dyDescent="0.3">
@@ -9180,13 +9566,13 @@
         <v>4</v>
       </c>
       <c r="E192" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F192">
         <v>222</v>
       </c>
       <c r="G192">
-        <f t="shared" ref="G192" si="122">G189+5</f>
+        <f t="shared" ref="G192" si="183">G189+5</f>
         <v>370</v>
       </c>
     </row>
@@ -9201,13 +9587,13 @@
         <v>4</v>
       </c>
       <c r="E193" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F193">
         <v>370</v>
       </c>
       <c r="G193">
-        <f t="shared" ref="G193:G224" si="123">G192*2</f>
+        <f t="shared" ref="G193:G224" si="184">G192*2</f>
         <v>740</v>
       </c>
     </row>
@@ -9222,14 +9608,14 @@
         <v>4</v>
       </c>
       <c r="E194" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F194">
         <v>1110</v>
       </c>
       <c r="G194">
-        <f t="shared" si="123"/>
-        <v>1480</v>
+        <f t="shared" ref="G194:G225" si="185">ROUNDUP(G193*1.7,-1)</f>
+        <v>1260</v>
       </c>
     </row>
     <row r="195" spans="2:7" x14ac:dyDescent="0.3">
@@ -9243,13 +9629,13 @@
         <v>5</v>
       </c>
       <c r="E195" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F195">
         <v>225</v>
       </c>
       <c r="G195">
-        <f t="shared" ref="G195" si="124">G192+5</f>
+        <f t="shared" ref="G195" si="186">G192+5</f>
         <v>375</v>
       </c>
     </row>
@@ -9264,13 +9650,13 @@
         <v>5</v>
       </c>
       <c r="E196" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F196">
         <v>375</v>
       </c>
       <c r="G196">
-        <f t="shared" ref="G196:G227" si="125">G195*2</f>
+        <f t="shared" ref="G196:G227" si="187">G195*2</f>
         <v>750</v>
       </c>
     </row>
@@ -9285,14 +9671,14 @@
         <v>5</v>
       </c>
       <c r="E197" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F197">
         <v>1125</v>
       </c>
       <c r="G197">
-        <f t="shared" si="125"/>
-        <v>1500</v>
+        <f t="shared" ref="G197:G228" si="188">ROUNDUP(G196*1.7,-1)</f>
+        <v>1280</v>
       </c>
     </row>
     <row r="198" spans="2:7" x14ac:dyDescent="0.3">
@@ -9306,13 +9692,13 @@
         <v>6</v>
       </c>
       <c r="E198" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F198">
         <v>228</v>
       </c>
       <c r="G198">
-        <f t="shared" ref="G198" si="126">G195+5</f>
+        <f t="shared" ref="G198" si="189">G195+5</f>
         <v>380</v>
       </c>
     </row>
@@ -9327,13 +9713,13 @@
         <v>6</v>
       </c>
       <c r="E199" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F199">
         <v>380</v>
       </c>
       <c r="G199">
-        <f t="shared" ref="G199:G230" si="127">G198*2</f>
+        <f t="shared" ref="G199:G230" si="190">G198*2</f>
         <v>760</v>
       </c>
     </row>
@@ -9348,14 +9734,14 @@
         <v>6</v>
       </c>
       <c r="E200" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F200">
         <v>1140</v>
       </c>
       <c r="G200">
-        <f t="shared" si="127"/>
-        <v>1520</v>
+        <f t="shared" ref="G200:G231" si="191">ROUNDUP(G199*1.7,-1)</f>
+        <v>1300</v>
       </c>
     </row>
     <row r="201" spans="2:7" x14ac:dyDescent="0.3">
@@ -9369,13 +9755,13 @@
         <v>7</v>
       </c>
       <c r="E201" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F201">
         <v>231</v>
       </c>
       <c r="G201">
-        <f t="shared" ref="G201" si="128">G198+5</f>
+        <f t="shared" ref="G201" si="192">G198+5</f>
         <v>385</v>
       </c>
     </row>
@@ -9390,13 +9776,13 @@
         <v>7</v>
       </c>
       <c r="E202" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F202">
         <v>385</v>
       </c>
       <c r="G202">
-        <f t="shared" ref="G202:G233" si="129">G201*2</f>
+        <f t="shared" ref="G202:G233" si="193">G201*2</f>
         <v>770</v>
       </c>
     </row>
@@ -9411,14 +9797,14 @@
         <v>7</v>
       </c>
       <c r="E203" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F203">
         <v>1155</v>
       </c>
       <c r="G203">
-        <f t="shared" si="129"/>
-        <v>1540</v>
+        <f t="shared" ref="G203:G234" si="194">ROUNDUP(G202*1.7,-1)</f>
+        <v>1310</v>
       </c>
     </row>
     <row r="204" spans="2:7" x14ac:dyDescent="0.3">
@@ -9432,13 +9818,13 @@
         <v>8</v>
       </c>
       <c r="E204" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F204">
         <v>234</v>
       </c>
       <c r="G204">
-        <f t="shared" ref="G204" si="130">G201+5</f>
+        <f t="shared" ref="G204" si="195">G201+5</f>
         <v>390</v>
       </c>
     </row>
@@ -9453,13 +9839,13 @@
         <v>8</v>
       </c>
       <c r="E205" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F205">
         <v>390</v>
       </c>
       <c r="G205">
-        <f t="shared" ref="G205:G236" si="131">G204*2</f>
+        <f t="shared" ref="G205:G236" si="196">G204*2</f>
         <v>780</v>
       </c>
     </row>
@@ -9474,14 +9860,14 @@
         <v>8</v>
       </c>
       <c r="E206" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F206">
         <v>1170</v>
       </c>
       <c r="G206">
-        <f t="shared" si="131"/>
-        <v>1560</v>
+        <f t="shared" ref="G206:G237" si="197">ROUNDUP(G205*1.7,-1)</f>
+        <v>1330</v>
       </c>
     </row>
     <row r="207" spans="2:7" x14ac:dyDescent="0.3">
@@ -9495,13 +9881,13 @@
         <v>9</v>
       </c>
       <c r="E207" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F207">
         <v>237</v>
       </c>
       <c r="G207">
-        <f t="shared" ref="G207" si="132">G204+5</f>
+        <f t="shared" ref="G207" si="198">G204+5</f>
         <v>395</v>
       </c>
     </row>
@@ -9516,13 +9902,13 @@
         <v>9</v>
       </c>
       <c r="E208" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F208">
         <v>395</v>
       </c>
       <c r="G208">
-        <f t="shared" ref="G208:G239" si="133">G207*2</f>
+        <f t="shared" ref="G208:G239" si="199">G207*2</f>
         <v>790</v>
       </c>
     </row>
@@ -9537,14 +9923,14 @@
         <v>9</v>
       </c>
       <c r="E209" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F209">
         <v>1185</v>
       </c>
       <c r="G209">
-        <f t="shared" si="133"/>
-        <v>1580</v>
+        <f t="shared" ref="G209:G240" si="200">ROUNDUP(G208*1.7,-1)</f>
+        <v>1350</v>
       </c>
     </row>
     <row r="210" spans="2:7" x14ac:dyDescent="0.3">
@@ -9558,13 +9944,13 @@
         <v>10</v>
       </c>
       <c r="E210" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F210">
         <v>240</v>
       </c>
       <c r="G210">
-        <f t="shared" ref="G210" si="134">G207+5</f>
+        <f t="shared" ref="G210" si="201">G207+5</f>
         <v>400</v>
       </c>
     </row>
@@ -9579,13 +9965,13 @@
         <v>10</v>
       </c>
       <c r="E211" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F211">
         <v>400</v>
       </c>
       <c r="G211">
-        <f t="shared" ref="G211:G242" si="135">G210*2</f>
+        <f t="shared" ref="G211:G242" si="202">G210*2</f>
         <v>800</v>
       </c>
     </row>
@@ -9600,14 +9986,14 @@
         <v>10</v>
       </c>
       <c r="E212" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F212">
         <v>1200</v>
       </c>
       <c r="G212">
-        <f t="shared" si="135"/>
-        <v>1600</v>
+        <f t="shared" ref="G212:G243" si="203">ROUNDUP(G211*1.7,-1)</f>
+        <v>1360</v>
       </c>
     </row>
     <row r="213" spans="2:7" x14ac:dyDescent="0.3">
@@ -9621,13 +10007,13 @@
         <v>1</v>
       </c>
       <c r="E213" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F213">
         <v>243</v>
       </c>
       <c r="G213">
-        <f t="shared" ref="G213" si="136">G210+5</f>
+        <f t="shared" ref="G213" si="204">G210+5</f>
         <v>405</v>
       </c>
     </row>
@@ -9642,13 +10028,13 @@
         <v>1</v>
       </c>
       <c r="E214" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F214">
         <v>405</v>
       </c>
       <c r="G214">
-        <f t="shared" ref="G214:G245" si="137">G213*2</f>
+        <f t="shared" ref="G214:G245" si="205">G213*2</f>
         <v>810</v>
       </c>
     </row>
@@ -9663,14 +10049,14 @@
         <v>1</v>
       </c>
       <c r="E215" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F215">
         <v>1215</v>
       </c>
       <c r="G215">
-        <f t="shared" si="137"/>
-        <v>1620</v>
+        <f t="shared" ref="G215:G246" si="206">ROUNDUP(G214*1.7,-1)</f>
+        <v>1380</v>
       </c>
     </row>
     <row r="216" spans="2:7" x14ac:dyDescent="0.3">
@@ -9684,13 +10070,13 @@
         <v>2</v>
       </c>
       <c r="E216" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F216">
         <v>246</v>
       </c>
       <c r="G216">
-        <f t="shared" ref="G216" si="138">G213+5</f>
+        <f t="shared" ref="G216" si="207">G213+5</f>
         <v>410</v>
       </c>
     </row>
@@ -9705,13 +10091,13 @@
         <v>2</v>
       </c>
       <c r="E217" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F217">
         <v>410</v>
       </c>
       <c r="G217">
-        <f t="shared" ref="G217:G248" si="139">G216*2</f>
+        <f t="shared" ref="G217:G248" si="208">G216*2</f>
         <v>820</v>
       </c>
     </row>
@@ -9726,14 +10112,14 @@
         <v>2</v>
       </c>
       <c r="E218" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F218">
         <v>1230</v>
       </c>
       <c r="G218">
-        <f t="shared" si="139"/>
-        <v>1640</v>
+        <f t="shared" ref="G218:G249" si="209">ROUNDUP(G217*1.7,-1)</f>
+        <v>1400</v>
       </c>
     </row>
     <row r="219" spans="2:7" x14ac:dyDescent="0.3">
@@ -9747,13 +10133,13 @@
         <v>3</v>
       </c>
       <c r="E219" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F219">
         <v>249</v>
       </c>
       <c r="G219">
-        <f t="shared" ref="G219" si="140">G216+5</f>
+        <f t="shared" ref="G219" si="210">G216+5</f>
         <v>415</v>
       </c>
     </row>
@@ -9768,13 +10154,13 @@
         <v>3</v>
       </c>
       <c r="E220" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F220">
         <v>415</v>
       </c>
       <c r="G220">
-        <f t="shared" ref="G220:G251" si="141">G219*2</f>
+        <f t="shared" ref="G220:G251" si="211">G219*2</f>
         <v>830</v>
       </c>
     </row>
@@ -9789,14 +10175,14 @@
         <v>3</v>
       </c>
       <c r="E221" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F221">
         <v>1245</v>
       </c>
       <c r="G221">
-        <f t="shared" si="141"/>
-        <v>1660</v>
+        <f t="shared" ref="G221:G252" si="212">ROUNDUP(G220*1.7,-1)</f>
+        <v>1420</v>
       </c>
     </row>
     <row r="222" spans="2:7" x14ac:dyDescent="0.3">
@@ -9810,13 +10196,13 @@
         <v>4</v>
       </c>
       <c r="E222" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F222">
         <v>252</v>
       </c>
       <c r="G222">
-        <f t="shared" ref="G222" si="142">G219+5</f>
+        <f t="shared" ref="G222" si="213">G219+5</f>
         <v>420</v>
       </c>
     </row>
@@ -9831,13 +10217,13 @@
         <v>4</v>
       </c>
       <c r="E223" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F223">
         <v>420</v>
       </c>
       <c r="G223">
-        <f t="shared" ref="G223:G254" si="143">G222*2</f>
+        <f t="shared" ref="G223:G254" si="214">G222*2</f>
         <v>840</v>
       </c>
     </row>
@@ -9852,14 +10238,14 @@
         <v>4</v>
       </c>
       <c r="E224" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F224">
         <v>1260</v>
       </c>
       <c r="G224">
-        <f t="shared" si="143"/>
-        <v>1680</v>
+        <f t="shared" ref="G224:G255" si="215">ROUNDUP(G223*1.7,-1)</f>
+        <v>1430</v>
       </c>
     </row>
     <row r="225" spans="2:7" x14ac:dyDescent="0.3">
@@ -9873,13 +10259,13 @@
         <v>5</v>
       </c>
       <c r="E225" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F225">
         <v>255</v>
       </c>
       <c r="G225">
-        <f t="shared" ref="G225" si="144">G222+5</f>
+        <f t="shared" ref="G225" si="216">G222+5</f>
         <v>425</v>
       </c>
     </row>
@@ -9894,13 +10280,13 @@
         <v>5</v>
       </c>
       <c r="E226" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F226">
         <v>425</v>
       </c>
       <c r="G226">
-        <f t="shared" ref="G226:G257" si="145">G225*2</f>
+        <f t="shared" ref="G226:G257" si="217">G225*2</f>
         <v>850</v>
       </c>
     </row>
@@ -9915,14 +10301,14 @@
         <v>5</v>
       </c>
       <c r="E227" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F227">
         <v>1275</v>
       </c>
       <c r="G227">
-        <f t="shared" si="145"/>
-        <v>1700</v>
+        <f t="shared" ref="G227:G258" si="218">ROUNDUP(G226*1.7,-1)</f>
+        <v>1450</v>
       </c>
     </row>
     <row r="228" spans="2:7" x14ac:dyDescent="0.3">
@@ -9936,13 +10322,13 @@
         <v>6</v>
       </c>
       <c r="E228" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F228">
         <v>258</v>
       </c>
       <c r="G228">
-        <f t="shared" ref="G228" si="146">G225+5</f>
+        <f t="shared" ref="G228" si="219">G225+5</f>
         <v>430</v>
       </c>
     </row>
@@ -9957,13 +10343,13 @@
         <v>6</v>
       </c>
       <c r="E229" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F229">
         <v>430</v>
       </c>
       <c r="G229">
-        <f t="shared" ref="G229:G260" si="147">G228*2</f>
+        <f t="shared" ref="G229:G260" si="220">G228*2</f>
         <v>860</v>
       </c>
     </row>
@@ -9978,14 +10364,14 @@
         <v>6</v>
       </c>
       <c r="E230" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F230">
         <v>1290</v>
       </c>
       <c r="G230">
-        <f t="shared" si="147"/>
-        <v>1720</v>
+        <f t="shared" ref="G230:G261" si="221">ROUNDUP(G229*1.7,-1)</f>
+        <v>1470</v>
       </c>
     </row>
     <row r="231" spans="2:7" x14ac:dyDescent="0.3">
@@ -9999,13 +10385,13 @@
         <v>7</v>
       </c>
       <c r="E231" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F231">
         <v>261</v>
       </c>
       <c r="G231">
-        <f t="shared" ref="G231" si="148">G228+5</f>
+        <f t="shared" ref="G231" si="222">G228+5</f>
         <v>435</v>
       </c>
     </row>
@@ -10020,13 +10406,13 @@
         <v>7</v>
       </c>
       <c r="E232" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F232">
         <v>435</v>
       </c>
       <c r="G232">
-        <f t="shared" ref="G232:G263" si="149">G231*2</f>
+        <f t="shared" ref="G232:G263" si="223">G231*2</f>
         <v>870</v>
       </c>
     </row>
@@ -10041,14 +10427,14 @@
         <v>7</v>
       </c>
       <c r="E233" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F233">
         <v>1305</v>
       </c>
       <c r="G233">
-        <f t="shared" si="149"/>
-        <v>1740</v>
+        <f t="shared" ref="G233:G264" si="224">ROUNDUP(G232*1.7,-1)</f>
+        <v>1480</v>
       </c>
     </row>
     <row r="234" spans="2:7" x14ac:dyDescent="0.3">
@@ -10062,13 +10448,13 @@
         <v>8</v>
       </c>
       <c r="E234" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F234">
         <v>264</v>
       </c>
       <c r="G234">
-        <f t="shared" ref="G234" si="150">G231+5</f>
+        <f t="shared" ref="G234" si="225">G231+5</f>
         <v>440</v>
       </c>
     </row>
@@ -10083,13 +10469,13 @@
         <v>8</v>
       </c>
       <c r="E235" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F235">
         <v>440</v>
       </c>
       <c r="G235">
-        <f t="shared" ref="G235:G266" si="151">G234*2</f>
+        <f t="shared" ref="G235:G266" si="226">G234*2</f>
         <v>880</v>
       </c>
     </row>
@@ -10104,14 +10490,14 @@
         <v>8</v>
       </c>
       <c r="E236" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F236">
         <v>1320</v>
       </c>
       <c r="G236">
-        <f t="shared" si="151"/>
-        <v>1760</v>
+        <f t="shared" ref="G236:G267" si="227">ROUNDUP(G235*1.7,-1)</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="237" spans="2:7" x14ac:dyDescent="0.3">
@@ -10125,13 +10511,13 @@
         <v>9</v>
       </c>
       <c r="E237" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F237">
         <v>267</v>
       </c>
       <c r="G237">
-        <f t="shared" ref="G237" si="152">G234+5</f>
+        <f t="shared" ref="G237" si="228">G234+5</f>
         <v>445</v>
       </c>
     </row>
@@ -10146,13 +10532,13 @@
         <v>9</v>
       </c>
       <c r="E238" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F238">
         <v>445</v>
       </c>
       <c r="G238">
-        <f t="shared" ref="G238:G269" si="153">G237*2</f>
+        <f t="shared" ref="G238:G269" si="229">G237*2</f>
         <v>890</v>
       </c>
     </row>
@@ -10167,14 +10553,14 @@
         <v>9</v>
       </c>
       <c r="E239" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F239">
         <v>1335</v>
       </c>
       <c r="G239">
-        <f t="shared" si="153"/>
-        <v>1780</v>
+        <f t="shared" ref="G239:G270" si="230">ROUNDUP(G238*1.7,-1)</f>
+        <v>1520</v>
       </c>
     </row>
     <row r="240" spans="2:7" x14ac:dyDescent="0.3">
@@ -10188,13 +10574,13 @@
         <v>10</v>
       </c>
       <c r="E240" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F240">
         <v>270</v>
       </c>
       <c r="G240">
-        <f t="shared" ref="G240" si="154">G237+5</f>
+        <f t="shared" ref="G240" si="231">G237+5</f>
         <v>450</v>
       </c>
     </row>
@@ -10209,13 +10595,13 @@
         <v>10</v>
       </c>
       <c r="E241" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F241">
         <v>450</v>
       </c>
       <c r="G241">
-        <f t="shared" ref="G241:G272" si="155">G240*2</f>
+        <f t="shared" ref="G241:G272" si="232">G240*2</f>
         <v>900</v>
       </c>
     </row>
@@ -10230,14 +10616,14 @@
         <v>10</v>
       </c>
       <c r="E242" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F242">
         <v>1350</v>
       </c>
       <c r="G242">
-        <f t="shared" si="155"/>
-        <v>1800</v>
+        <f t="shared" ref="G242:G273" si="233">ROUNDUP(G241*1.7,-1)</f>
+        <v>1530</v>
       </c>
     </row>
     <row r="243" spans="2:7" x14ac:dyDescent="0.3">
@@ -10251,13 +10637,13 @@
         <v>1</v>
       </c>
       <c r="E243" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F243">
         <v>273</v>
       </c>
       <c r="G243">
-        <f t="shared" ref="G243" si="156">G240+5</f>
+        <f t="shared" ref="G243" si="234">G240+5</f>
         <v>455</v>
       </c>
     </row>
@@ -10272,13 +10658,13 @@
         <v>1</v>
       </c>
       <c r="E244" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F244">
         <v>455</v>
       </c>
       <c r="G244">
-        <f t="shared" ref="G244:G275" si="157">G243*2</f>
+        <f t="shared" ref="G244:G275" si="235">G243*2</f>
         <v>910</v>
       </c>
     </row>
@@ -10293,14 +10679,14 @@
         <v>1</v>
       </c>
       <c r="E245" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F245">
         <v>1365</v>
       </c>
       <c r="G245">
-        <f t="shared" si="157"/>
-        <v>1820</v>
+        <f t="shared" ref="G245:G276" si="236">ROUNDUP(G244*1.7,-1)</f>
+        <v>1550</v>
       </c>
     </row>
     <row r="246" spans="2:7" x14ac:dyDescent="0.3">
@@ -10314,13 +10700,13 @@
         <v>2</v>
       </c>
       <c r="E246" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F246">
         <v>276</v>
       </c>
       <c r="G246">
-        <f t="shared" ref="G246" si="158">G243+5</f>
+        <f t="shared" ref="G246" si="237">G243+5</f>
         <v>460</v>
       </c>
     </row>
@@ -10335,13 +10721,13 @@
         <v>2</v>
       </c>
       <c r="E247" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F247">
         <v>460</v>
       </c>
       <c r="G247">
-        <f t="shared" ref="G247:G278" si="159">G246*2</f>
+        <f t="shared" ref="G247:G278" si="238">G246*2</f>
         <v>920</v>
       </c>
     </row>
@@ -10356,14 +10742,14 @@
         <v>2</v>
       </c>
       <c r="E248" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F248">
         <v>1380</v>
       </c>
       <c r="G248">
-        <f t="shared" si="159"/>
-        <v>1840</v>
+        <f t="shared" ref="G248:G279" si="239">ROUNDUP(G247*1.7,-1)</f>
+        <v>1570</v>
       </c>
     </row>
     <row r="249" spans="2:7" x14ac:dyDescent="0.3">
@@ -10377,13 +10763,13 @@
         <v>3</v>
       </c>
       <c r="E249" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F249">
         <v>279</v>
       </c>
       <c r="G249">
-        <f t="shared" ref="G249" si="160">G246+5</f>
+        <f t="shared" ref="G249" si="240">G246+5</f>
         <v>465</v>
       </c>
     </row>
@@ -10398,13 +10784,13 @@
         <v>3</v>
       </c>
       <c r="E250" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F250">
         <v>465</v>
       </c>
       <c r="G250">
-        <f t="shared" ref="G250:G281" si="161">G249*2</f>
+        <f t="shared" ref="G250:G281" si="241">G249*2</f>
         <v>930</v>
       </c>
     </row>
@@ -10419,14 +10805,14 @@
         <v>3</v>
       </c>
       <c r="E251" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F251">
         <v>1395</v>
       </c>
       <c r="G251">
-        <f t="shared" si="161"/>
-        <v>1860</v>
+        <f t="shared" ref="G251:G282" si="242">ROUNDUP(G250*1.7,-1)</f>
+        <v>1590</v>
       </c>
     </row>
     <row r="252" spans="2:7" x14ac:dyDescent="0.3">
@@ -10440,13 +10826,13 @@
         <v>4</v>
       </c>
       <c r="E252" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F252">
         <v>282</v>
       </c>
       <c r="G252">
-        <f t="shared" ref="G252" si="162">G249+5</f>
+        <f t="shared" ref="G252" si="243">G249+5</f>
         <v>470</v>
       </c>
     </row>
@@ -10461,13 +10847,13 @@
         <v>4</v>
       </c>
       <c r="E253" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F253">
         <v>470</v>
       </c>
       <c r="G253">
-        <f t="shared" ref="G253:G284" si="163">G252*2</f>
+        <f t="shared" ref="G253:G284" si="244">G252*2</f>
         <v>940</v>
       </c>
     </row>
@@ -10482,14 +10868,14 @@
         <v>4</v>
       </c>
       <c r="E254" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F254">
         <v>1410</v>
       </c>
       <c r="G254">
-        <f t="shared" si="163"/>
-        <v>1880</v>
+        <f t="shared" ref="G254:G285" si="245">ROUNDUP(G253*1.7,-1)</f>
+        <v>1600</v>
       </c>
     </row>
     <row r="255" spans="2:7" x14ac:dyDescent="0.3">
@@ -10503,13 +10889,13 @@
         <v>5</v>
       </c>
       <c r="E255" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F255">
         <v>285</v>
       </c>
       <c r="G255">
-        <f t="shared" ref="G255" si="164">G252+5</f>
+        <f t="shared" ref="G255" si="246">G252+5</f>
         <v>475</v>
       </c>
     </row>
@@ -10524,13 +10910,13 @@
         <v>5</v>
       </c>
       <c r="E256" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F256">
         <v>475</v>
       </c>
       <c r="G256">
-        <f t="shared" ref="G256:G302" si="165">G255*2</f>
+        <f t="shared" ref="G256:G302" si="247">G255*2</f>
         <v>950</v>
       </c>
     </row>
@@ -10545,14 +10931,14 @@
         <v>5</v>
       </c>
       <c r="E257" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F257">
         <v>1425</v>
       </c>
       <c r="G257">
-        <f t="shared" si="165"/>
-        <v>1900</v>
+        <f t="shared" ref="G257:G302" si="248">ROUNDUP(G256*1.7,-1)</f>
+        <v>1620</v>
       </c>
     </row>
     <row r="258" spans="2:7" x14ac:dyDescent="0.3">
@@ -10566,13 +10952,13 @@
         <v>6</v>
       </c>
       <c r="E258" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F258">
         <v>288</v>
       </c>
       <c r="G258">
-        <f t="shared" ref="G258" si="166">G255+5</f>
+        <f t="shared" ref="G258" si="249">G255+5</f>
         <v>480</v>
       </c>
     </row>
@@ -10587,13 +10973,13 @@
         <v>6</v>
       </c>
       <c r="E259" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F259">
         <v>480</v>
       </c>
       <c r="G259">
-        <f t="shared" ref="G259:G302" si="167">G258*2</f>
+        <f t="shared" ref="G259:G302" si="250">G258*2</f>
         <v>960</v>
       </c>
     </row>
@@ -10608,14 +10994,14 @@
         <v>6</v>
       </c>
       <c r="E260" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F260">
         <v>1440</v>
       </c>
       <c r="G260">
-        <f t="shared" si="167"/>
-        <v>1920</v>
+        <f t="shared" ref="G260:G302" si="251">ROUNDUP(G259*1.7,-1)</f>
+        <v>1640</v>
       </c>
     </row>
     <row r="261" spans="2:7" x14ac:dyDescent="0.3">
@@ -10629,13 +11015,13 @@
         <v>7</v>
       </c>
       <c r="E261" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F261">
         <v>291</v>
       </c>
       <c r="G261">
-        <f t="shared" ref="G261" si="168">G258+5</f>
+        <f t="shared" ref="G261" si="252">G258+5</f>
         <v>485</v>
       </c>
     </row>
@@ -10650,13 +11036,13 @@
         <v>7</v>
       </c>
       <c r="E262" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F262">
         <v>485</v>
       </c>
       <c r="G262">
-        <f t="shared" ref="G262:G302" si="169">G261*2</f>
+        <f t="shared" ref="G262:G302" si="253">G261*2</f>
         <v>970</v>
       </c>
     </row>
@@ -10671,14 +11057,14 @@
         <v>7</v>
       </c>
       <c r="E263" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F263">
         <v>1455</v>
       </c>
       <c r="G263">
-        <f t="shared" si="169"/>
-        <v>1940</v>
+        <f t="shared" ref="G263:G302" si="254">ROUNDUP(G262*1.7,-1)</f>
+        <v>1650</v>
       </c>
     </row>
     <row r="264" spans="2:7" x14ac:dyDescent="0.3">
@@ -10692,13 +11078,13 @@
         <v>8</v>
       </c>
       <c r="E264" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F264">
         <v>294</v>
       </c>
       <c r="G264">
-        <f t="shared" ref="G264" si="170">G261+5</f>
+        <f t="shared" ref="G264" si="255">G261+5</f>
         <v>490</v>
       </c>
     </row>
@@ -10713,13 +11099,13 @@
         <v>8</v>
       </c>
       <c r="E265" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F265">
         <v>490</v>
       </c>
       <c r="G265">
-        <f t="shared" ref="G265:G302" si="171">G264*2</f>
+        <f t="shared" ref="G265:G302" si="256">G264*2</f>
         <v>980</v>
       </c>
     </row>
@@ -10734,14 +11120,14 @@
         <v>8</v>
       </c>
       <c r="E266" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F266">
         <v>1470</v>
       </c>
       <c r="G266">
-        <f t="shared" si="171"/>
-        <v>1960</v>
+        <f t="shared" ref="G266:G302" si="257">ROUNDUP(G265*1.7,-1)</f>
+        <v>1670</v>
       </c>
     </row>
     <row r="267" spans="2:7" x14ac:dyDescent="0.3">
@@ -10755,13 +11141,13 @@
         <v>9</v>
       </c>
       <c r="E267" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F267">
         <v>297</v>
       </c>
       <c r="G267">
-        <f t="shared" ref="G267" si="172">G264+5</f>
+        <f t="shared" ref="G267" si="258">G264+5</f>
         <v>495</v>
       </c>
     </row>
@@ -10776,13 +11162,13 @@
         <v>9</v>
       </c>
       <c r="E268" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F268">
         <v>495</v>
       </c>
       <c r="G268">
-        <f t="shared" ref="G268:G302" si="173">G267*2</f>
+        <f t="shared" ref="G268:G302" si="259">G267*2</f>
         <v>990</v>
       </c>
     </row>
@@ -10797,14 +11183,14 @@
         <v>9</v>
       </c>
       <c r="E269" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F269">
         <v>1485</v>
       </c>
       <c r="G269">
-        <f t="shared" si="173"/>
-        <v>1980</v>
+        <f t="shared" ref="G269:G302" si="260">ROUNDUP(G268*1.7,-1)</f>
+        <v>1690</v>
       </c>
     </row>
     <row r="270" spans="2:7" x14ac:dyDescent="0.3">
@@ -10818,13 +11204,13 @@
         <v>10</v>
       </c>
       <c r="E270" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F270">
         <v>300</v>
       </c>
       <c r="G270">
-        <f t="shared" ref="G270" si="174">G267+5</f>
+        <f t="shared" ref="G270" si="261">G267+5</f>
         <v>500</v>
       </c>
     </row>
@@ -10839,13 +11225,13 @@
         <v>10</v>
       </c>
       <c r="E271" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F271">
         <v>500</v>
       </c>
       <c r="G271">
-        <f t="shared" ref="G271:G302" si="175">G270*2</f>
+        <f t="shared" ref="G271:G302" si="262">G270*2</f>
         <v>1000</v>
       </c>
     </row>
@@ -10860,14 +11246,14 @@
         <v>10</v>
       </c>
       <c r="E272" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F272">
         <v>1500</v>
       </c>
       <c r="G272">
-        <f t="shared" si="175"/>
-        <v>2000</v>
+        <f t="shared" ref="G272:G302" si="263">ROUNDUP(G271*1.7,-1)</f>
+        <v>1700</v>
       </c>
     </row>
     <row r="273" spans="2:7" x14ac:dyDescent="0.3">
@@ -10881,13 +11267,13 @@
         <v>1</v>
       </c>
       <c r="E273" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F273">
         <v>303</v>
       </c>
       <c r="G273">
-        <f t="shared" ref="G273" si="176">G270+5</f>
+        <f t="shared" ref="G273" si="264">G270+5</f>
         <v>505</v>
       </c>
     </row>
@@ -10902,13 +11288,13 @@
         <v>1</v>
       </c>
       <c r="E274" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F274">
         <v>505</v>
       </c>
       <c r="G274">
-        <f t="shared" ref="G274:G302" si="177">G273*2</f>
+        <f t="shared" ref="G274:G302" si="265">G273*2</f>
         <v>1010</v>
       </c>
     </row>
@@ -10923,14 +11309,14 @@
         <v>1</v>
       </c>
       <c r="E275" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F275">
         <v>1515</v>
       </c>
       <c r="G275">
-        <f t="shared" si="177"/>
-        <v>2020</v>
+        <f t="shared" ref="G275:G302" si="266">ROUNDUP(G274*1.7,-1)</f>
+        <v>1720</v>
       </c>
     </row>
     <row r="276" spans="2:7" x14ac:dyDescent="0.3">
@@ -10944,13 +11330,13 @@
         <v>2</v>
       </c>
       <c r="E276" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F276">
         <v>306</v>
       </c>
       <c r="G276">
-        <f t="shared" ref="G276" si="178">G273+5</f>
+        <f t="shared" ref="G276" si="267">G273+5</f>
         <v>510</v>
       </c>
     </row>
@@ -10965,13 +11351,13 @@
         <v>2</v>
       </c>
       <c r="E277" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F277">
         <v>510</v>
       </c>
       <c r="G277">
-        <f t="shared" ref="G277:G302" si="179">G276*2</f>
+        <f t="shared" ref="G277:G302" si="268">G276*2</f>
         <v>1020</v>
       </c>
     </row>
@@ -10986,14 +11372,14 @@
         <v>2</v>
       </c>
       <c r="E278" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F278">
         <v>1530</v>
       </c>
       <c r="G278">
-        <f t="shared" si="179"/>
-        <v>2040</v>
+        <f t="shared" ref="G278:G302" si="269">ROUNDUP(G277*1.7,-1)</f>
+        <v>1740</v>
       </c>
     </row>
     <row r="279" spans="2:7" x14ac:dyDescent="0.3">
@@ -11007,13 +11393,13 @@
         <v>3</v>
       </c>
       <c r="E279" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F279">
         <v>309</v>
       </c>
       <c r="G279">
-        <f t="shared" ref="G279" si="180">G276+5</f>
+        <f t="shared" ref="G279" si="270">G276+5</f>
         <v>515</v>
       </c>
     </row>
@@ -11028,13 +11414,13 @@
         <v>3</v>
       </c>
       <c r="E280" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F280">
         <v>515</v>
       </c>
       <c r="G280">
-        <f t="shared" ref="G280:G302" si="181">G279*2</f>
+        <f t="shared" ref="G280:G302" si="271">G279*2</f>
         <v>1030</v>
       </c>
     </row>
@@ -11049,14 +11435,14 @@
         <v>3</v>
       </c>
       <c r="E281" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F281">
         <v>1545</v>
       </c>
       <c r="G281">
-        <f t="shared" si="181"/>
-        <v>2060</v>
+        <f t="shared" ref="G281:G302" si="272">ROUNDUP(G280*1.7,-1)</f>
+        <v>1760</v>
       </c>
     </row>
     <row r="282" spans="2:7" x14ac:dyDescent="0.3">
@@ -11070,13 +11456,13 @@
         <v>4</v>
       </c>
       <c r="E282" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F282">
         <v>312</v>
       </c>
       <c r="G282">
-        <f t="shared" ref="G282" si="182">G279+5</f>
+        <f t="shared" ref="G282" si="273">G279+5</f>
         <v>520</v>
       </c>
     </row>
@@ -11091,13 +11477,13 @@
         <v>4</v>
       </c>
       <c r="E283" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F283">
         <v>520</v>
       </c>
       <c r="G283">
-        <f t="shared" ref="G283:G302" si="183">G282*2</f>
+        <f t="shared" ref="G283:G302" si="274">G282*2</f>
         <v>1040</v>
       </c>
     </row>
@@ -11112,14 +11498,14 @@
         <v>4</v>
       </c>
       <c r="E284" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F284">
         <v>1560</v>
       </c>
       <c r="G284">
-        <f t="shared" si="183"/>
-        <v>2080</v>
+        <f t="shared" ref="G284:G302" si="275">ROUNDUP(G283*1.7,-1)</f>
+        <v>1770</v>
       </c>
     </row>
     <row r="285" spans="2:7" x14ac:dyDescent="0.3">
@@ -11133,13 +11519,13 @@
         <v>5</v>
       </c>
       <c r="E285" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F285">
         <v>315</v>
       </c>
       <c r="G285">
-        <f t="shared" ref="G285" si="184">G282+5</f>
+        <f t="shared" ref="G285" si="276">G282+5</f>
         <v>525</v>
       </c>
     </row>
@@ -11154,13 +11540,13 @@
         <v>5</v>
       </c>
       <c r="E286" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F286">
         <v>525</v>
       </c>
       <c r="G286">
-        <f t="shared" ref="G286:G302" si="185">G285*2</f>
+        <f t="shared" ref="G286:G302" si="277">G285*2</f>
         <v>1050</v>
       </c>
     </row>
@@ -11175,14 +11561,14 @@
         <v>5</v>
       </c>
       <c r="E287" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F287">
         <v>1575</v>
       </c>
       <c r="G287">
-        <f t="shared" si="185"/>
-        <v>2100</v>
+        <f t="shared" ref="G287:G302" si="278">ROUNDUP(G286*1.7,-1)</f>
+        <v>1790</v>
       </c>
     </row>
     <row r="288" spans="2:7" x14ac:dyDescent="0.3">
@@ -11196,13 +11582,13 @@
         <v>6</v>
       </c>
       <c r="E288" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F288">
         <v>318</v>
       </c>
       <c r="G288">
-        <f t="shared" ref="G288" si="186">G285+5</f>
+        <f t="shared" ref="G288" si="279">G285+5</f>
         <v>530</v>
       </c>
     </row>
@@ -11217,13 +11603,13 @@
         <v>6</v>
       </c>
       <c r="E289" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F289">
         <v>530</v>
       </c>
       <c r="G289">
-        <f t="shared" ref="G289:G302" si="187">G288*2</f>
+        <f t="shared" ref="G289:G302" si="280">G288*2</f>
         <v>1060</v>
       </c>
     </row>
@@ -11238,14 +11624,14 @@
         <v>6</v>
       </c>
       <c r="E290" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F290">
         <v>1590</v>
       </c>
       <c r="G290">
-        <f t="shared" si="187"/>
-        <v>2120</v>
+        <f t="shared" ref="G290:G302" si="281">ROUNDUP(G289*1.7,-1)</f>
+        <v>1810</v>
       </c>
     </row>
     <row r="291" spans="2:7" x14ac:dyDescent="0.3">
@@ -11259,13 +11645,13 @@
         <v>7</v>
       </c>
       <c r="E291" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F291">
         <v>321</v>
       </c>
       <c r="G291">
-        <f t="shared" ref="G291" si="188">G288+5</f>
+        <f t="shared" ref="G291" si="282">G288+5</f>
         <v>535</v>
       </c>
     </row>
@@ -11280,13 +11666,13 @@
         <v>7</v>
       </c>
       <c r="E292" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F292">
         <v>535</v>
       </c>
       <c r="G292">
-        <f t="shared" ref="G292:G302" si="189">G291*2</f>
+        <f t="shared" ref="G292:G302" si="283">G291*2</f>
         <v>1070</v>
       </c>
     </row>
@@ -11301,14 +11687,14 @@
         <v>7</v>
       </c>
       <c r="E293" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F293">
         <v>1605</v>
       </c>
       <c r="G293">
-        <f t="shared" si="189"/>
-        <v>2140</v>
+        <f t="shared" ref="G293:G302" si="284">ROUNDUP(G292*1.7,-1)</f>
+        <v>1820</v>
       </c>
     </row>
     <row r="294" spans="2:7" x14ac:dyDescent="0.3">
@@ -11322,13 +11708,13 @@
         <v>8</v>
       </c>
       <c r="E294" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F294">
         <v>324</v>
       </c>
       <c r="G294">
-        <f t="shared" ref="G294" si="190">G291+5</f>
+        <f t="shared" ref="G294" si="285">G291+5</f>
         <v>540</v>
       </c>
     </row>
@@ -11343,13 +11729,13 @@
         <v>8</v>
       </c>
       <c r="E295" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F295">
         <v>540</v>
       </c>
       <c r="G295">
-        <f t="shared" ref="G295:G302" si="191">G294*2</f>
+        <f t="shared" ref="G295:G302" si="286">G294*2</f>
         <v>1080</v>
       </c>
     </row>
@@ -11364,14 +11750,14 @@
         <v>8</v>
       </c>
       <c r="E296" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F296">
         <v>1620</v>
       </c>
       <c r="G296">
-        <f t="shared" si="191"/>
-        <v>2160</v>
+        <f t="shared" ref="G296:G302" si="287">ROUNDUP(G295*1.7,-1)</f>
+        <v>1840</v>
       </c>
     </row>
     <row r="297" spans="2:7" x14ac:dyDescent="0.3">
@@ -11385,13 +11771,13 @@
         <v>9</v>
       </c>
       <c r="E297" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F297">
         <v>327</v>
       </c>
       <c r="G297">
-        <f t="shared" ref="G297" si="192">G294+5</f>
+        <f t="shared" ref="G297" si="288">G294+5</f>
         <v>545</v>
       </c>
     </row>
@@ -11406,13 +11792,13 @@
         <v>9</v>
       </c>
       <c r="E298" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F298">
         <v>545</v>
       </c>
       <c r="G298">
-        <f t="shared" ref="G298:G302" si="193">G297*2</f>
+        <f t="shared" ref="G298:G302" si="289">G297*2</f>
         <v>1090</v>
       </c>
     </row>
@@ -11427,14 +11813,14 @@
         <v>9</v>
       </c>
       <c r="E299" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F299">
         <v>1635</v>
       </c>
       <c r="G299">
-        <f t="shared" si="193"/>
-        <v>2180</v>
+        <f t="shared" ref="G299:G302" si="290">ROUNDUP(G298*1.7,-1)</f>
+        <v>1860</v>
       </c>
     </row>
     <row r="300" spans="2:7" x14ac:dyDescent="0.3">
@@ -11448,13 +11834,13 @@
         <v>10</v>
       </c>
       <c r="E300" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F300">
         <v>330</v>
       </c>
       <c r="G300">
-        <f t="shared" ref="G300" si="194">G297+5</f>
+        <f t="shared" ref="G300" si="291">G297+5</f>
         <v>550</v>
       </c>
     </row>
@@ -11469,13 +11855,13 @@
         <v>10</v>
       </c>
       <c r="E301" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F301">
         <v>550</v>
       </c>
       <c r="G301">
-        <f t="shared" ref="G301:G302" si="195">G300*2</f>
+        <f t="shared" ref="G301:G302" si="292">G300*2</f>
         <v>1100</v>
       </c>
     </row>
@@ -11490,21 +11876,21 @@
         <v>10</v>
       </c>
       <c r="E302" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F302">
         <v>1650</v>
       </c>
       <c r="G302">
-        <f t="shared" si="195"/>
-        <v>2200</v>
+        <f t="shared" ref="G302" si="293">ROUNDUP(G301*1.7,-1)</f>
+        <v>1870</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
-    <ignoredError sqref="G6:G302" formula="1"/>
+    <ignoredError sqref="G6:G7" formula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Data.xlsx
+++ b/Assets/StreamingAssets/Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ljh\tralalero Shooter\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03717BEE-53C4-4A18-BEB4-B2781FAEEEC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48ABB79A-08EC-48FA-A8EE-82AB728CBC0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="업그레이드" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2281" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2731" uniqueCount="123">
   <si>
     <t>식별 순번</t>
   </si>
@@ -817,7 +817,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:K152"/>
+  <dimension ref="B2:K242"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="18.625" bestFit="1" customWidth="1"/>
@@ -1445,19 +1445,19 @@
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E23" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F23">
-        <v>5</v>
+        <v>105</v>
       </c>
       <c r="G23" t="s">
         <v>11</v>
@@ -1466,27 +1466,27 @@
         <v>12</v>
       </c>
       <c r="I23">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="J23" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="E24" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F24">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="G24" t="s">
         <v>11</v>
@@ -1495,27 +1495,27 @@
         <v>12</v>
       </c>
       <c r="I24">
-        <v>150</v>
+        <v>1150</v>
       </c>
       <c r="J24" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D25">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="E25" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F25">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="G25" t="s">
         <v>11</v>
@@ -1524,27 +1524,27 @@
         <v>12</v>
       </c>
       <c r="I25">
-        <v>200</v>
+        <v>1200</v>
       </c>
       <c r="J25" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D26">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E26" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F26">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="G26" t="s">
         <v>11</v>
@@ -1553,27 +1553,27 @@
         <v>12</v>
       </c>
       <c r="I26">
-        <v>250</v>
+        <v>1250</v>
       </c>
       <c r="J26" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D27">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E27" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F27">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="G27" t="s">
         <v>11</v>
@@ -1582,27 +1582,27 @@
         <v>12</v>
       </c>
       <c r="I27">
-        <v>300</v>
+        <v>1300</v>
       </c>
       <c r="J27" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D28">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="E28" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F28">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="G28" t="s">
         <v>11</v>
@@ -1611,27 +1611,27 @@
         <v>12</v>
       </c>
       <c r="I28">
-        <v>350</v>
+        <v>1350</v>
       </c>
       <c r="J28" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D29">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="E29" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F29">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="G29" t="s">
         <v>11</v>
@@ -1640,27 +1640,27 @@
         <v>12</v>
       </c>
       <c r="I29">
-        <v>400</v>
+        <v>1400</v>
       </c>
       <c r="J29" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D30">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="E30" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F30">
-        <v>40</v>
+        <v>140</v>
       </c>
       <c r="G30" t="s">
         <v>11</v>
@@ -1669,27 +1669,27 @@
         <v>12</v>
       </c>
       <c r="I30">
-        <v>450</v>
+        <v>1450</v>
       </c>
       <c r="J30" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D31">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="E31" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F31">
-        <v>45</v>
+        <v>145</v>
       </c>
       <c r="G31" t="s">
         <v>11</v>
@@ -1698,27 +1698,27 @@
         <v>12</v>
       </c>
       <c r="I31">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="J31" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D32">
+        <v>30</v>
+      </c>
+      <c r="E32" t="s">
         <v>10</v>
       </c>
-      <c r="E32" t="s">
-        <v>15</v>
-      </c>
       <c r="F32">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="G32" t="s">
         <v>11</v>
@@ -1727,10 +1727,10 @@
         <v>12</v>
       </c>
       <c r="I32">
-        <v>550</v>
+        <v>1550</v>
       </c>
       <c r="J32" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.3">
@@ -1741,13 +1741,13 @@
         <v>14</v>
       </c>
       <c r="D33">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E33" t="s">
         <v>15</v>
       </c>
       <c r="F33">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="G33" t="s">
         <v>11</v>
@@ -1756,7 +1756,7 @@
         <v>12</v>
       </c>
       <c r="I33">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="J33" t="s">
         <v>16</v>
@@ -1770,13 +1770,13 @@
         <v>14</v>
       </c>
       <c r="D34">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E34" t="s">
         <v>15</v>
       </c>
       <c r="F34">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="G34" t="s">
         <v>11</v>
@@ -1785,7 +1785,7 @@
         <v>12</v>
       </c>
       <c r="I34">
-        <v>650</v>
+        <v>150</v>
       </c>
       <c r="J34" t="s">
         <v>16</v>
@@ -1799,13 +1799,13 @@
         <v>14</v>
       </c>
       <c r="D35">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E35" t="s">
         <v>15</v>
       </c>
       <c r="F35">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="G35" t="s">
         <v>11</v>
@@ -1814,7 +1814,7 @@
         <v>12</v>
       </c>
       <c r="I35">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="J35" t="s">
         <v>16</v>
@@ -1828,13 +1828,13 @@
         <v>14</v>
       </c>
       <c r="D36">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
       </c>
       <c r="F36">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="G36" t="s">
         <v>11</v>
@@ -1843,7 +1843,7 @@
         <v>12</v>
       </c>
       <c r="I36">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="J36" t="s">
         <v>16</v>
@@ -1857,13 +1857,13 @@
         <v>14</v>
       </c>
       <c r="D37">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
       </c>
       <c r="F37">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="G37" t="s">
         <v>11</v>
@@ -1872,7 +1872,7 @@
         <v>12</v>
       </c>
       <c r="I37">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="J37" t="s">
         <v>16</v>
@@ -1886,13 +1886,13 @@
         <v>14</v>
       </c>
       <c r="D38">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E38" t="s">
         <v>15</v>
       </c>
       <c r="F38">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="G38" t="s">
         <v>11</v>
@@ -1901,7 +1901,7 @@
         <v>12</v>
       </c>
       <c r="I38">
-        <v>850</v>
+        <v>350</v>
       </c>
       <c r="J38" t="s">
         <v>16</v>
@@ -1915,13 +1915,13 @@
         <v>14</v>
       </c>
       <c r="D39">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E39" t="s">
         <v>15</v>
       </c>
       <c r="F39">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="G39" t="s">
         <v>11</v>
@@ -1930,7 +1930,7 @@
         <v>12</v>
       </c>
       <c r="I39">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="J39" t="s">
         <v>16</v>
@@ -1944,13 +1944,13 @@
         <v>14</v>
       </c>
       <c r="D40">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
       </c>
       <c r="F40">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="G40" t="s">
         <v>11</v>
@@ -1959,7 +1959,7 @@
         <v>12</v>
       </c>
       <c r="I40">
-        <v>950</v>
+        <v>450</v>
       </c>
       <c r="J40" t="s">
         <v>16</v>
@@ -1973,13 +1973,13 @@
         <v>14</v>
       </c>
       <c r="D41">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E41" t="s">
         <v>15</v>
       </c>
       <c r="F41">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="G41" t="s">
         <v>11</v>
@@ -1988,7 +1988,7 @@
         <v>12</v>
       </c>
       <c r="I41">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="J41" t="s">
         <v>16</v>
@@ -2002,13 +2002,13 @@
         <v>14</v>
       </c>
       <c r="D42">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E42" t="s">
         <v>15</v>
       </c>
       <c r="F42">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G42" t="s">
         <v>11</v>
@@ -2017,7 +2017,7 @@
         <v>12</v>
       </c>
       <c r="I42">
-        <v>1050</v>
+        <v>550</v>
       </c>
       <c r="J42" t="s">
         <v>16</v>
@@ -2025,596 +2025,596 @@
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E43" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F43">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="G43" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H43" t="s">
         <v>12</v>
       </c>
       <c r="I43">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="J43" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F44">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="G44" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H44" t="s">
         <v>12</v>
       </c>
       <c r="I44">
-        <v>150</v>
+        <v>650</v>
       </c>
       <c r="J44" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E45" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F45">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="G45" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H45" t="s">
         <v>12</v>
       </c>
       <c r="I45">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="J45" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D46">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E46" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F46">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="G46" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H46" t="s">
         <v>12</v>
       </c>
       <c r="I46">
-        <v>250</v>
+        <v>750</v>
       </c>
       <c r="J46" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D47">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E47" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F47">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="G47" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H47" t="s">
         <v>12</v>
       </c>
       <c r="I47">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="J47" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D48">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E48" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F48">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="G48" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H48" t="s">
         <v>12</v>
       </c>
       <c r="I48">
-        <v>350</v>
+        <v>850</v>
       </c>
       <c r="J48" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C49" t="s">
+        <v>14</v>
+      </c>
+      <c r="D49">
         <v>17</v>
       </c>
-      <c r="D49">
-        <v>7</v>
-      </c>
       <c r="E49" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F49">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="G49" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H49" t="s">
         <v>12</v>
       </c>
       <c r="I49">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="J49" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D50">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E50" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F50">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="G50" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H50" t="s">
         <v>12</v>
       </c>
       <c r="I50">
-        <v>450</v>
+        <v>950</v>
       </c>
       <c r="J50" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D51">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E51" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F51">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="G51" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H51" t="s">
         <v>12</v>
       </c>
       <c r="I51">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="J51" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D52">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E52" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F52">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G52" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H52" t="s">
         <v>12</v>
       </c>
       <c r="I52">
-        <v>550</v>
+        <v>1050</v>
       </c>
       <c r="J52" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D53">
+        <v>21</v>
+      </c>
+      <c r="E53" t="s">
+        <v>15</v>
+      </c>
+      <c r="F53">
+        <v>105</v>
+      </c>
+      <c r="G53" t="s">
         <v>11</v>
-      </c>
-      <c r="E53" t="s">
-        <v>18</v>
-      </c>
-      <c r="F53">
-        <v>55</v>
-      </c>
-      <c r="G53" t="s">
-        <v>19</v>
       </c>
       <c r="H53" t="s">
         <v>12</v>
       </c>
       <c r="I53">
-        <v>600</v>
+        <v>1100</v>
       </c>
       <c r="J53" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D54">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E54" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F54">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="G54" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H54" t="s">
         <v>12</v>
       </c>
       <c r="I54">
-        <v>650</v>
+        <v>1150</v>
       </c>
       <c r="J54" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D55">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E55" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F55">
-        <v>65</v>
+        <v>115</v>
       </c>
       <c r="G55" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H55" t="s">
         <v>12</v>
       </c>
       <c r="I55">
-        <v>700</v>
+        <v>1200</v>
       </c>
       <c r="J55" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D56">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E56" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F56">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="G56" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H56" t="s">
         <v>12</v>
       </c>
       <c r="I56">
-        <v>750</v>
+        <v>1250</v>
       </c>
       <c r="J56" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D57">
+        <v>25</v>
+      </c>
+      <c r="E57" t="s">
         <v>15</v>
       </c>
-      <c r="E57" t="s">
-        <v>18</v>
-      </c>
       <c r="F57">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="G57" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H57" t="s">
         <v>12</v>
       </c>
       <c r="I57">
-        <v>800</v>
+        <v>1300</v>
       </c>
       <c r="J57" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D58">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E58" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F58">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="G58" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H58" t="s">
         <v>12</v>
       </c>
       <c r="I58">
-        <v>850</v>
+        <v>1350</v>
       </c>
       <c r="J58" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C59" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D59">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E59" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F59">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="G59" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H59" t="s">
         <v>12</v>
       </c>
       <c r="I59">
-        <v>900</v>
+        <v>1400</v>
       </c>
       <c r="J59" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D60">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E60" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F60">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="G60" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H60" t="s">
         <v>12</v>
       </c>
       <c r="I60">
-        <v>950</v>
+        <v>1450</v>
       </c>
       <c r="J60" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D61">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E61" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F61">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="G61" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H61" t="s">
         <v>12</v>
       </c>
       <c r="I61">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="J61" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D62">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E62" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F62">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G62" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H62" t="s">
         <v>12</v>
       </c>
       <c r="I62">
-        <v>1050</v>
+        <v>1550</v>
       </c>
       <c r="J62" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C63" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D63">
         <v>1</v>
       </c>
       <c r="E63" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F63">
         <v>5</v>
@@ -2629,21 +2629,21 @@
         <v>100</v>
       </c>
       <c r="J63" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C64" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D64">
         <v>2</v>
       </c>
       <c r="E64" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F64">
         <v>10</v>
@@ -2658,21 +2658,21 @@
         <v>150</v>
       </c>
       <c r="J64" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C65" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D65">
         <v>3</v>
       </c>
       <c r="E65" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F65">
         <v>15</v>
@@ -2687,21 +2687,21 @@
         <v>200</v>
       </c>
       <c r="J65" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C66" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D66">
         <v>4</v>
       </c>
       <c r="E66" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F66">
         <v>20</v>
@@ -2716,21 +2716,21 @@
         <v>250</v>
       </c>
       <c r="J66" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C67" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D67">
         <v>5</v>
       </c>
       <c r="E67" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F67">
         <v>25</v>
@@ -2745,21 +2745,21 @@
         <v>300</v>
       </c>
       <c r="J67" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C68" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D68">
         <v>6</v>
       </c>
       <c r="E68" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F68">
         <v>30</v>
@@ -2774,21 +2774,21 @@
         <v>350</v>
       </c>
       <c r="J68" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C69" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D69">
         <v>7</v>
       </c>
       <c r="E69" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F69">
         <v>35</v>
@@ -2803,21 +2803,21 @@
         <v>400</v>
       </c>
       <c r="J69" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C70" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D70">
         <v>8</v>
       </c>
       <c r="E70" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F70">
         <v>40</v>
@@ -2832,21 +2832,21 @@
         <v>450</v>
       </c>
       <c r="J70" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C71" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D71">
         <v>9</v>
       </c>
       <c r="E71" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F71">
         <v>45</v>
@@ -2861,21 +2861,21 @@
         <v>500</v>
       </c>
       <c r="J71" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B72">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C72" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D72">
         <v>10</v>
       </c>
       <c r="E72" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F72">
         <v>50</v>
@@ -2890,21 +2890,21 @@
         <v>550</v>
       </c>
       <c r="J72" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C73" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D73">
         <v>11</v>
       </c>
       <c r="E73" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F73">
         <v>55</v>
@@ -2919,21 +2919,21 @@
         <v>600</v>
       </c>
       <c r="J73" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C74" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D74">
         <v>12</v>
       </c>
       <c r="E74" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F74">
         <v>60</v>
@@ -2948,21 +2948,21 @@
         <v>650</v>
       </c>
       <c r="J74" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="75" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B75">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C75" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D75">
         <v>13</v>
       </c>
       <c r="E75" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F75">
         <v>65</v>
@@ -2977,21 +2977,21 @@
         <v>700</v>
       </c>
       <c r="J75" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="76" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C76" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D76">
         <v>14</v>
       </c>
       <c r="E76" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F76">
         <v>70</v>
@@ -3006,21 +3006,21 @@
         <v>750</v>
       </c>
       <c r="J76" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="77" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B77">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C77" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D77">
         <v>15</v>
       </c>
       <c r="E77" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F77">
         <v>75</v>
@@ -3035,21 +3035,21 @@
         <v>800</v>
       </c>
       <c r="J77" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C78" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D78">
         <v>16</v>
       </c>
       <c r="E78" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F78">
         <v>80</v>
@@ -3064,21 +3064,21 @@
         <v>850</v>
       </c>
       <c r="J78" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="79" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D79">
         <v>17</v>
       </c>
       <c r="E79" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F79">
         <v>85</v>
@@ -3093,21 +3093,21 @@
         <v>900</v>
       </c>
       <c r="J79" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="80" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B80">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C80" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D80">
         <v>18</v>
       </c>
       <c r="E80" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F80">
         <v>90</v>
@@ -3122,21 +3122,21 @@
         <v>950</v>
       </c>
       <c r="J80" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="81" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B81">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D81">
         <v>19</v>
       </c>
       <c r="E81" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F81">
         <v>95</v>
@@ -3151,21 +3151,21 @@
         <v>1000</v>
       </c>
       <c r="J81" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B82">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C82" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D82">
         <v>20</v>
       </c>
       <c r="E82" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F82">
         <v>100</v>
@@ -3180,24 +3180,24 @@
         <v>1050</v>
       </c>
       <c r="J82" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B83">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C83" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D83">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E83" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F83">
-        <v>10</v>
+        <v>105</v>
       </c>
       <c r="G83" t="s">
         <v>19</v>
@@ -3206,27 +3206,27 @@
         <v>12</v>
       </c>
       <c r="I83">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="J83" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B84">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D84">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="E84" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F84">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="G84" t="s">
         <v>19</v>
@@ -3235,27 +3235,27 @@
         <v>12</v>
       </c>
       <c r="I84">
-        <v>150</v>
+        <v>1150</v>
       </c>
       <c r="J84" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B85">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C85" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D85">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="E85" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F85">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="G85" t="s">
         <v>19</v>
@@ -3264,27 +3264,27 @@
         <v>12</v>
       </c>
       <c r="I85">
-        <v>200</v>
+        <v>1200</v>
       </c>
       <c r="J85" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B86">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C86" t="s">
+        <v>17</v>
+      </c>
+      <c r="D86">
         <v>24</v>
       </c>
-      <c r="D86">
-        <v>4</v>
-      </c>
       <c r="E86" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F86">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="G86" t="s">
         <v>19</v>
@@ -3293,27 +3293,27 @@
         <v>12</v>
       </c>
       <c r="I86">
-        <v>250</v>
+        <v>1250</v>
       </c>
       <c r="J86" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="87" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B87">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C87" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D87">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E87" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F87">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="G87" t="s">
         <v>19</v>
@@ -3322,27 +3322,27 @@
         <v>12</v>
       </c>
       <c r="I87">
-        <v>300</v>
+        <v>1300</v>
       </c>
       <c r="J87" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="88" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B88">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C88" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D88">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="E88" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F88">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="G88" t="s">
         <v>19</v>
@@ -3351,27 +3351,27 @@
         <v>12</v>
       </c>
       <c r="I88">
-        <v>350</v>
+        <v>1350</v>
       </c>
       <c r="J88" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B89">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C89" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D89">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="E89" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F89">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="G89" t="s">
         <v>19</v>
@@ -3380,27 +3380,27 @@
         <v>12</v>
       </c>
       <c r="I89">
-        <v>400</v>
+        <v>1400</v>
       </c>
       <c r="J89" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B90">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C90" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D90">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="E90" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F90">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="G90" t="s">
         <v>19</v>
@@ -3409,27 +3409,27 @@
         <v>12</v>
       </c>
       <c r="I90">
-        <v>450</v>
+        <v>1450</v>
       </c>
       <c r="J90" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="91" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B91">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C91" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D91">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="E91" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F91">
-        <v>90</v>
+        <v>145</v>
       </c>
       <c r="G91" t="s">
         <v>19</v>
@@ -3438,27 +3438,27 @@
         <v>12</v>
       </c>
       <c r="I91">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="J91" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="92" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B92">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C92" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D92">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E92" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F92">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G92" t="s">
         <v>19</v>
@@ -3467,27 +3467,27 @@
         <v>12</v>
       </c>
       <c r="I92">
-        <v>550</v>
+        <v>1550</v>
       </c>
       <c r="J92" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B93">
+        <v>4</v>
+      </c>
+      <c r="C93" t="s">
+        <v>21</v>
+      </c>
+      <c r="D93">
+        <v>1</v>
+      </c>
+      <c r="E93" t="s">
+        <v>22</v>
+      </c>
+      <c r="F93">
         <v>5</v>
-      </c>
-      <c r="C93" t="s">
-        <v>24</v>
-      </c>
-      <c r="D93">
-        <v>11</v>
-      </c>
-      <c r="E93" t="s">
-        <v>25</v>
-      </c>
-      <c r="F93">
-        <v>110</v>
       </c>
       <c r="G93" t="s">
         <v>19</v>
@@ -3496,27 +3496,27 @@
         <v>12</v>
       </c>
       <c r="I93">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="J93" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="94" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B94">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C94" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D94">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E94" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F94">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="G94" t="s">
         <v>19</v>
@@ -3525,27 +3525,27 @@
         <v>12</v>
       </c>
       <c r="I94">
-        <v>650</v>
+        <v>150</v>
       </c>
       <c r="J94" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="95" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B95">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C95" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D95">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E95" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F95">
-        <v>130</v>
+        <v>15</v>
       </c>
       <c r="G95" t="s">
         <v>19</v>
@@ -3554,27 +3554,27 @@
         <v>12</v>
       </c>
       <c r="I95">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="J95" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="96" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B96">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C96" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D96">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E96" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F96">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="G96" t="s">
         <v>19</v>
@@ -3583,27 +3583,27 @@
         <v>12</v>
       </c>
       <c r="I96">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="J96" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97">
+        <v>4</v>
+      </c>
+      <c r="C97" t="s">
+        <v>21</v>
+      </c>
+      <c r="D97">
         <v>5</v>
       </c>
-      <c r="C97" t="s">
-        <v>24</v>
-      </c>
-      <c r="D97">
-        <v>15</v>
-      </c>
       <c r="E97" t="s">
+        <v>22</v>
+      </c>
+      <c r="F97">
         <v>25</v>
-      </c>
-      <c r="F97">
-        <v>150</v>
       </c>
       <c r="G97" t="s">
         <v>19</v>
@@ -3612,27 +3612,27 @@
         <v>12</v>
       </c>
       <c r="I97">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="J97" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C98" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D98">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E98" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F98">
-        <v>160</v>
+        <v>30</v>
       </c>
       <c r="G98" t="s">
         <v>19</v>
@@ -3641,27 +3641,27 @@
         <v>12</v>
       </c>
       <c r="I98">
-        <v>850</v>
+        <v>350</v>
       </c>
       <c r="J98" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B99">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C99" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D99">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E99" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F99">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="G99" t="s">
         <v>19</v>
@@ -3670,27 +3670,27 @@
         <v>12</v>
       </c>
       <c r="I99">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="J99" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="100" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B100">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C100" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D100">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E100" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F100">
-        <v>180</v>
+        <v>40</v>
       </c>
       <c r="G100" t="s">
         <v>19</v>
@@ -3699,27 +3699,27 @@
         <v>12</v>
       </c>
       <c r="I100">
-        <v>950</v>
+        <v>450</v>
       </c>
       <c r="J100" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B101">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C101" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D101">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E101" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F101">
-        <v>190</v>
+        <v>45</v>
       </c>
       <c r="G101" t="s">
         <v>19</v>
@@ -3728,27 +3728,27 @@
         <v>12</v>
       </c>
       <c r="I101">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="J101" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B102">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C102" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D102">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E102" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F102">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="G102" t="s">
         <v>19</v>
@@ -3757,27 +3757,27 @@
         <v>12</v>
       </c>
       <c r="I102">
-        <v>1050</v>
+        <v>550</v>
       </c>
       <c r="J102" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="103" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B103">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C103" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D103">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E103" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F103">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="G103" t="s">
         <v>19</v>
@@ -3786,27 +3786,27 @@
         <v>12</v>
       </c>
       <c r="I103">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="J103" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="104" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B104">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C104" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D104">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E104" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F104">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="G104" t="s">
         <v>19</v>
@@ -3815,27 +3815,27 @@
         <v>12</v>
       </c>
       <c r="I104">
-        <v>150</v>
+        <v>650</v>
       </c>
       <c r="J104" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="105" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B105">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C105" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D105">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E105" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F105">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="G105" t="s">
         <v>19</v>
@@ -3844,27 +3844,27 @@
         <v>12</v>
       </c>
       <c r="I105">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="J105" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="106" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B106">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C106" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D106">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E106" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F106">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="G106" t="s">
         <v>19</v>
@@ -3873,27 +3873,27 @@
         <v>12</v>
       </c>
       <c r="I106">
-        <v>250</v>
+        <v>750</v>
       </c>
       <c r="J106" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="107" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B107">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C107" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D107">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E107" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F107">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="G107" t="s">
         <v>19</v>
@@ -3902,27 +3902,27 @@
         <v>12</v>
       </c>
       <c r="I107">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="J107" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="108" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B108">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C108" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D108">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E108" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F108">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="G108" t="s">
         <v>19</v>
@@ -3931,27 +3931,27 @@
         <v>12</v>
       </c>
       <c r="I108">
-        <v>350</v>
+        <v>850</v>
       </c>
       <c r="J108" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="109" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B109">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C109" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D109">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E109" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F109">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="G109" t="s">
         <v>19</v>
@@ -3960,27 +3960,27 @@
         <v>12</v>
       </c>
       <c r="I109">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="J109" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="110" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B110">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C110" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D110">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E110" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F110">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="G110" t="s">
         <v>19</v>
@@ -3989,27 +3989,27 @@
         <v>12</v>
       </c>
       <c r="I110">
-        <v>450</v>
+        <v>950</v>
       </c>
       <c r="J110" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="111" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B111">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C111" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D111">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E111" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F111">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="G111" t="s">
         <v>19</v>
@@ -4018,27 +4018,27 @@
         <v>12</v>
       </c>
       <c r="I111">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="J111" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="112" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B112">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C112" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D112">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E112" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F112">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G112" t="s">
         <v>19</v>
@@ -4047,27 +4047,27 @@
         <v>12</v>
       </c>
       <c r="I112">
-        <v>550</v>
+        <v>1050</v>
       </c>
       <c r="J112" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B113">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C113" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D113">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E113" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F113">
-        <v>55</v>
+        <v>105</v>
       </c>
       <c r="G113" t="s">
         <v>19</v>
@@ -4076,27 +4076,27 @@
         <v>12</v>
       </c>
       <c r="I113">
-        <v>600</v>
+        <v>1100</v>
       </c>
       <c r="J113" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="114" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B114">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C114" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D114">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E114" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F114">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="G114" t="s">
         <v>19</v>
@@ -4105,27 +4105,27 @@
         <v>12</v>
       </c>
       <c r="I114">
-        <v>650</v>
+        <v>1150</v>
       </c>
       <c r="J114" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="115" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B115">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C115" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D115">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E115" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F115">
-        <v>65</v>
+        <v>115</v>
       </c>
       <c r="G115" t="s">
         <v>19</v>
@@ -4134,27 +4134,27 @@
         <v>12</v>
       </c>
       <c r="I115">
-        <v>700</v>
+        <v>1200</v>
       </c>
       <c r="J115" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="116" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B116">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C116" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D116">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E116" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F116">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="G116" t="s">
         <v>19</v>
@@ -4163,27 +4163,27 @@
         <v>12</v>
       </c>
       <c r="I116">
-        <v>750</v>
+        <v>1250</v>
       </c>
       <c r="J116" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="117" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B117">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C117" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D117">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E117" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F117">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="G117" t="s">
         <v>19</v>
@@ -4192,27 +4192,27 @@
         <v>12</v>
       </c>
       <c r="I117">
-        <v>800</v>
+        <v>1300</v>
       </c>
       <c r="J117" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="118" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B118">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C118" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D118">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E118" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F118">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="G118" t="s">
         <v>19</v>
@@ -4221,27 +4221,27 @@
         <v>12</v>
       </c>
       <c r="I118">
-        <v>850</v>
+        <v>1350</v>
       </c>
       <c r="J118" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B119">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C119" t="s">
+        <v>21</v>
+      </c>
+      <c r="D119">
         <v>27</v>
       </c>
-      <c r="D119">
-        <v>17</v>
-      </c>
       <c r="E119" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F119">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="G119" t="s">
         <v>19</v>
@@ -4250,27 +4250,27 @@
         <v>12</v>
       </c>
       <c r="I119">
-        <v>900</v>
+        <v>1400</v>
       </c>
       <c r="J119" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="120" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B120">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C120" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D120">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E120" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F120">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="G120" t="s">
         <v>19</v>
@@ -4279,27 +4279,27 @@
         <v>12</v>
       </c>
       <c r="I120">
-        <v>950</v>
+        <v>1450</v>
       </c>
       <c r="J120" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="121" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B121">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D121">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E121" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F121">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="G121" t="s">
         <v>19</v>
@@ -4308,27 +4308,27 @@
         <v>12</v>
       </c>
       <c r="I121">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="J121" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B122">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C122" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D122">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E122" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F122">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G122" t="s">
         <v>19</v>
@@ -4337,879 +4337,3489 @@
         <v>12</v>
       </c>
       <c r="I122">
-        <v>1050</v>
+        <v>1550</v>
       </c>
       <c r="J122" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="123" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B123">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C123" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D123">
         <v>1</v>
       </c>
       <c r="E123" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F123">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G123" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H123" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I123">
         <v>100</v>
       </c>
       <c r="J123" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B124">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C124" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D124">
         <v>2</v>
       </c>
-      <c r="E124" s="1" t="s">
-        <v>31</v>
+      <c r="E124" t="s">
+        <v>25</v>
       </c>
       <c r="F124">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G124" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H124" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I124">
         <v>150</v>
       </c>
       <c r="J124" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B125">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C125" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D125">
         <v>3</v>
       </c>
-      <c r="E125" s="1" t="s">
-        <v>31</v>
+      <c r="E125" t="s">
+        <v>25</v>
       </c>
       <c r="F125">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="G125" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H125" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I125">
         <v>200</v>
       </c>
       <c r="J125" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="126" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B126">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C126" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D126">
         <v>4</v>
       </c>
-      <c r="E126" s="1" t="s">
-        <v>31</v>
+      <c r="E126" t="s">
+        <v>25</v>
       </c>
       <c r="F126">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="G126" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H126" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I126">
         <v>250</v>
       </c>
       <c r="J126" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="127" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B127">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C127" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D127">
         <v>5</v>
       </c>
-      <c r="E127" s="1" t="s">
-        <v>31</v>
+      <c r="E127" t="s">
+        <v>25</v>
       </c>
       <c r="F127">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="G127" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H127" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I127">
         <v>300</v>
       </c>
       <c r="J127" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B128">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C128" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D128">
         <v>6</v>
       </c>
-      <c r="E128" s="1" t="s">
-        <v>31</v>
+      <c r="E128" t="s">
+        <v>25</v>
       </c>
       <c r="F128">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="G128" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H128" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I128">
         <v>350</v>
       </c>
       <c r="J128" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B129">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C129" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D129">
         <v>7</v>
       </c>
-      <c r="E129" s="1" t="s">
-        <v>31</v>
+      <c r="E129" t="s">
+        <v>25</v>
       </c>
       <c r="F129">
-        <v>7</v>
+        <v>70</v>
       </c>
       <c r="G129" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H129" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I129">
         <v>400</v>
       </c>
       <c r="J129" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="130" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B130">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C130" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D130">
         <v>8</v>
       </c>
-      <c r="E130" s="1" t="s">
-        <v>31</v>
+      <c r="E130" t="s">
+        <v>25</v>
       </c>
       <c r="F130">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="G130" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H130" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I130">
         <v>450</v>
       </c>
       <c r="J130" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="131" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B131">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C131" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D131">
         <v>9</v>
       </c>
-      <c r="E131" s="1" t="s">
-        <v>31</v>
+      <c r="E131" t="s">
+        <v>25</v>
       </c>
       <c r="F131">
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="G131" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H131" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I131">
         <v>500</v>
       </c>
       <c r="J131" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="132" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B132">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C132" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D132">
         <v>10</v>
       </c>
-      <c r="E132" s="1" t="s">
-        <v>31</v>
+      <c r="E132" t="s">
+        <v>25</v>
       </c>
       <c r="F132">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G132" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H132" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I132">
         <v>550</v>
       </c>
       <c r="J132" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="133" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B133">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C133" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D133">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E133" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F133">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G133" t="s">
         <v>19</v>
       </c>
       <c r="H133" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I133">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="J133" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="134" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B134">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C134" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D134">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E134" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F134">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="G134" t="s">
         <v>19</v>
       </c>
       <c r="H134" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I134">
-        <v>150</v>
+        <v>650</v>
       </c>
       <c r="J134" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="135" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B135">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C135" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D135">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E135" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F135">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="G135" t="s">
         <v>19</v>
       </c>
       <c r="H135" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I135">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="J135" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="136" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B136">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C136" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D136">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E136" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F136">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="G136" t="s">
         <v>19</v>
       </c>
       <c r="H136" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I136">
-        <v>250</v>
+        <v>750</v>
       </c>
       <c r="J136" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="137" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B137">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C137" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D137">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E137" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F137">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="G137" t="s">
         <v>19</v>
       </c>
       <c r="H137" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I137">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="J137" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="138" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B138">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C138" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D138">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E138" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F138">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="G138" t="s">
         <v>19</v>
       </c>
       <c r="H138" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I138">
-        <v>350</v>
+        <v>850</v>
       </c>
       <c r="J138" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="139" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B139">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C139" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D139">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E139" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F139">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="G139" t="s">
         <v>19</v>
       </c>
       <c r="H139" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I139">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="J139" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="140" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B140">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C140" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D140">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E140" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F140">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="G140" t="s">
         <v>19</v>
       </c>
       <c r="H140" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I140">
-        <v>450</v>
+        <v>950</v>
       </c>
       <c r="J140" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="141" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B141">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C141" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D141">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E141" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F141">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="G141" t="s">
         <v>19</v>
       </c>
       <c r="H141" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I141">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="J141" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="142" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B142">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C142" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D142">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E142" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F142">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="G142" t="s">
         <v>19</v>
       </c>
       <c r="H142" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I142">
-        <v>550</v>
+        <v>1050</v>
       </c>
       <c r="J142" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="143" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B143">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C143" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D143">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E143" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="F143">
-        <v>20</v>
+        <v>210</v>
       </c>
       <c r="G143" t="s">
         <v>19</v>
       </c>
       <c r="H143" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I143">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="J143" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="144" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B144">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C144" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D144">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="E144" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="F144">
-        <v>25</v>
+        <v>220</v>
       </c>
       <c r="G144" t="s">
         <v>19</v>
       </c>
       <c r="H144" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I144">
-        <v>150</v>
+        <v>1150</v>
       </c>
       <c r="J144" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="145" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B145">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C145" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D145">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="E145" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="F145">
-        <v>30</v>
+        <v>230</v>
       </c>
       <c r="G145" t="s">
         <v>19</v>
       </c>
       <c r="H145" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I145">
-        <v>200</v>
+        <v>1200</v>
       </c>
       <c r="J145" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="146" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B146">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C146" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D146">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E146" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="F146">
-        <v>35</v>
+        <v>240</v>
       </c>
       <c r="G146" t="s">
         <v>19</v>
       </c>
       <c r="H146" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I146">
-        <v>250</v>
+        <v>1250</v>
       </c>
       <c r="J146" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="147" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B147">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C147" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D147">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E147" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="F147">
-        <v>40</v>
+        <v>250</v>
       </c>
       <c r="G147" t="s">
         <v>19</v>
       </c>
       <c r="H147" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I147">
-        <v>300</v>
+        <v>1300</v>
       </c>
       <c r="J147" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="148" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B148">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C148" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D148">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="E148" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="F148">
-        <v>45</v>
+        <v>260</v>
       </c>
       <c r="G148" t="s">
         <v>19</v>
       </c>
       <c r="H148" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I148">
-        <v>350</v>
+        <v>1350</v>
       </c>
       <c r="J148" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="149" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B149">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C149" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D149">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="E149" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="F149">
-        <v>50</v>
+        <v>270</v>
       </c>
       <c r="G149" t="s">
         <v>19</v>
       </c>
       <c r="H149" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I149">
-        <v>400</v>
+        <v>1400</v>
       </c>
       <c r="J149" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="150" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B150">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C150" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D150">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="E150" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="F150">
-        <v>55</v>
+        <v>280</v>
       </c>
       <c r="G150" t="s">
         <v>19</v>
       </c>
       <c r="H150" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I150">
-        <v>450</v>
+        <v>1450</v>
       </c>
       <c r="J150" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B151">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C151" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D151">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="E151" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="F151">
-        <v>60</v>
+        <v>290</v>
       </c>
       <c r="G151" t="s">
         <v>19</v>
       </c>
       <c r="H151" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I151">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="J151" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="152" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B152">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C152" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D152">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E152" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="F152">
-        <v>65</v>
+        <v>300</v>
       </c>
       <c r="G152" t="s">
         <v>19</v>
       </c>
       <c r="H152" t="s">
+        <v>12</v>
+      </c>
+      <c r="I152">
+        <v>1550</v>
+      </c>
+      <c r="J152" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="153" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B153">
+        <v>6</v>
+      </c>
+      <c r="C153" t="s">
+        <v>27</v>
+      </c>
+      <c r="D153">
+        <v>1</v>
+      </c>
+      <c r="E153" t="s">
+        <v>28</v>
+      </c>
+      <c r="F153">
+        <v>5</v>
+      </c>
+      <c r="G153" t="s">
+        <v>19</v>
+      </c>
+      <c r="H153" t="s">
+        <v>12</v>
+      </c>
+      <c r="I153">
+        <v>100</v>
+      </c>
+      <c r="J153" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="154" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B154">
+        <v>6</v>
+      </c>
+      <c r="C154" t="s">
+        <v>27</v>
+      </c>
+      <c r="D154">
+        <v>2</v>
+      </c>
+      <c r="E154" t="s">
+        <v>28</v>
+      </c>
+      <c r="F154">
+        <v>10</v>
+      </c>
+      <c r="G154" t="s">
+        <v>19</v>
+      </c>
+      <c r="H154" t="s">
+        <v>12</v>
+      </c>
+      <c r="I154">
+        <v>150</v>
+      </c>
+      <c r="J154" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="155" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B155">
+        <v>6</v>
+      </c>
+      <c r="C155" t="s">
+        <v>27</v>
+      </c>
+      <c r="D155">
+        <v>3</v>
+      </c>
+      <c r="E155" t="s">
+        <v>28</v>
+      </c>
+      <c r="F155">
+        <v>15</v>
+      </c>
+      <c r="G155" t="s">
+        <v>19</v>
+      </c>
+      <c r="H155" t="s">
+        <v>12</v>
+      </c>
+      <c r="I155">
+        <v>200</v>
+      </c>
+      <c r="J155" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="156" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B156">
+        <v>6</v>
+      </c>
+      <c r="C156" t="s">
+        <v>27</v>
+      </c>
+      <c r="D156">
+        <v>4</v>
+      </c>
+      <c r="E156" t="s">
+        <v>28</v>
+      </c>
+      <c r="F156">
+        <v>20</v>
+      </c>
+      <c r="G156" t="s">
+        <v>19</v>
+      </c>
+      <c r="H156" t="s">
+        <v>12</v>
+      </c>
+      <c r="I156">
+        <v>250</v>
+      </c>
+      <c r="J156" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="157" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B157">
+        <v>6</v>
+      </c>
+      <c r="C157" t="s">
+        <v>27</v>
+      </c>
+      <c r="D157">
+        <v>5</v>
+      </c>
+      <c r="E157" t="s">
+        <v>28</v>
+      </c>
+      <c r="F157">
+        <v>25</v>
+      </c>
+      <c r="G157" t="s">
+        <v>19</v>
+      </c>
+      <c r="H157" t="s">
+        <v>12</v>
+      </c>
+      <c r="I157">
+        <v>300</v>
+      </c>
+      <c r="J157" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="158" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B158">
+        <v>6</v>
+      </c>
+      <c r="C158" t="s">
+        <v>27</v>
+      </c>
+      <c r="D158">
+        <v>6</v>
+      </c>
+      <c r="E158" t="s">
+        <v>28</v>
+      </c>
+      <c r="F158">
+        <v>30</v>
+      </c>
+      <c r="G158" t="s">
+        <v>19</v>
+      </c>
+      <c r="H158" t="s">
+        <v>12</v>
+      </c>
+      <c r="I158">
+        <v>350</v>
+      </c>
+      <c r="J158" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="159" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B159">
+        <v>6</v>
+      </c>
+      <c r="C159" t="s">
+        <v>27</v>
+      </c>
+      <c r="D159">
+        <v>7</v>
+      </c>
+      <c r="E159" t="s">
+        <v>28</v>
+      </c>
+      <c r="F159">
+        <v>35</v>
+      </c>
+      <c r="G159" t="s">
+        <v>19</v>
+      </c>
+      <c r="H159" t="s">
+        <v>12</v>
+      </c>
+      <c r="I159">
+        <v>400</v>
+      </c>
+      <c r="J159" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="160" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B160">
+        <v>6</v>
+      </c>
+      <c r="C160" t="s">
+        <v>27</v>
+      </c>
+      <c r="D160">
+        <v>8</v>
+      </c>
+      <c r="E160" t="s">
+        <v>28</v>
+      </c>
+      <c r="F160">
+        <v>40</v>
+      </c>
+      <c r="G160" t="s">
+        <v>19</v>
+      </c>
+      <c r="H160" t="s">
+        <v>12</v>
+      </c>
+      <c r="I160">
+        <v>450</v>
+      </c>
+      <c r="J160" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="161" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B161">
+        <v>6</v>
+      </c>
+      <c r="C161" t="s">
+        <v>27</v>
+      </c>
+      <c r="D161">
+        <v>9</v>
+      </c>
+      <c r="E161" t="s">
+        <v>28</v>
+      </c>
+      <c r="F161">
+        <v>45</v>
+      </c>
+      <c r="G161" t="s">
+        <v>19</v>
+      </c>
+      <c r="H161" t="s">
+        <v>12</v>
+      </c>
+      <c r="I161">
+        <v>500</v>
+      </c>
+      <c r="J161" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="162" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B162">
+        <v>6</v>
+      </c>
+      <c r="C162" t="s">
+        <v>27</v>
+      </c>
+      <c r="D162">
+        <v>10</v>
+      </c>
+      <c r="E162" t="s">
+        <v>28</v>
+      </c>
+      <c r="F162">
+        <v>50</v>
+      </c>
+      <c r="G162" t="s">
+        <v>19</v>
+      </c>
+      <c r="H162" t="s">
+        <v>12</v>
+      </c>
+      <c r="I162">
+        <v>550</v>
+      </c>
+      <c r="J162" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="163" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B163">
+        <v>6</v>
+      </c>
+      <c r="C163" t="s">
+        <v>27</v>
+      </c>
+      <c r="D163">
+        <v>11</v>
+      </c>
+      <c r="E163" t="s">
+        <v>28</v>
+      </c>
+      <c r="F163">
+        <v>55</v>
+      </c>
+      <c r="G163" t="s">
+        <v>19</v>
+      </c>
+      <c r="H163" t="s">
+        <v>12</v>
+      </c>
+      <c r="I163">
+        <v>600</v>
+      </c>
+      <c r="J163" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="164" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B164">
+        <v>6</v>
+      </c>
+      <c r="C164" t="s">
+        <v>27</v>
+      </c>
+      <c r="D164">
+        <v>12</v>
+      </c>
+      <c r="E164" t="s">
+        <v>28</v>
+      </c>
+      <c r="F164">
+        <v>60</v>
+      </c>
+      <c r="G164" t="s">
+        <v>19</v>
+      </c>
+      <c r="H164" t="s">
+        <v>12</v>
+      </c>
+      <c r="I164">
+        <v>650</v>
+      </c>
+      <c r="J164" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="165" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B165">
+        <v>6</v>
+      </c>
+      <c r="C165" t="s">
+        <v>27</v>
+      </c>
+      <c r="D165">
+        <v>13</v>
+      </c>
+      <c r="E165" t="s">
+        <v>28</v>
+      </c>
+      <c r="F165">
+        <v>65</v>
+      </c>
+      <c r="G165" t="s">
+        <v>19</v>
+      </c>
+      <c r="H165" t="s">
+        <v>12</v>
+      </c>
+      <c r="I165">
+        <v>700</v>
+      </c>
+      <c r="J165" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="166" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B166">
+        <v>6</v>
+      </c>
+      <c r="C166" t="s">
+        <v>27</v>
+      </c>
+      <c r="D166">
+        <v>14</v>
+      </c>
+      <c r="E166" t="s">
+        <v>28</v>
+      </c>
+      <c r="F166">
+        <v>70</v>
+      </c>
+      <c r="G166" t="s">
+        <v>19</v>
+      </c>
+      <c r="H166" t="s">
+        <v>12</v>
+      </c>
+      <c r="I166">
+        <v>750</v>
+      </c>
+      <c r="J166" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="167" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B167">
+        <v>6</v>
+      </c>
+      <c r="C167" t="s">
+        <v>27</v>
+      </c>
+      <c r="D167">
+        <v>15</v>
+      </c>
+      <c r="E167" t="s">
+        <v>28</v>
+      </c>
+      <c r="F167">
+        <v>75</v>
+      </c>
+      <c r="G167" t="s">
+        <v>19</v>
+      </c>
+      <c r="H167" t="s">
+        <v>12</v>
+      </c>
+      <c r="I167">
+        <v>800</v>
+      </c>
+      <c r="J167" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="168" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B168">
+        <v>6</v>
+      </c>
+      <c r="C168" t="s">
+        <v>27</v>
+      </c>
+      <c r="D168">
+        <v>16</v>
+      </c>
+      <c r="E168" t="s">
+        <v>28</v>
+      </c>
+      <c r="F168">
+        <v>80</v>
+      </c>
+      <c r="G168" t="s">
+        <v>19</v>
+      </c>
+      <c r="H168" t="s">
+        <v>12</v>
+      </c>
+      <c r="I168">
+        <v>850</v>
+      </c>
+      <c r="J168" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="169" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B169">
+        <v>6</v>
+      </c>
+      <c r="C169" t="s">
+        <v>27</v>
+      </c>
+      <c r="D169">
+        <v>17</v>
+      </c>
+      <c r="E169" t="s">
+        <v>28</v>
+      </c>
+      <c r="F169">
+        <v>85</v>
+      </c>
+      <c r="G169" t="s">
+        <v>19</v>
+      </c>
+      <c r="H169" t="s">
+        <v>12</v>
+      </c>
+      <c r="I169">
+        <v>900</v>
+      </c>
+      <c r="J169" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="170" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B170">
+        <v>6</v>
+      </c>
+      <c r="C170" t="s">
+        <v>27</v>
+      </c>
+      <c r="D170">
+        <v>18</v>
+      </c>
+      <c r="E170" t="s">
+        <v>28</v>
+      </c>
+      <c r="F170">
+        <v>90</v>
+      </c>
+      <c r="G170" t="s">
+        <v>19</v>
+      </c>
+      <c r="H170" t="s">
+        <v>12</v>
+      </c>
+      <c r="I170">
+        <v>950</v>
+      </c>
+      <c r="J170" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="171" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B171">
+        <v>6</v>
+      </c>
+      <c r="C171" t="s">
+        <v>27</v>
+      </c>
+      <c r="D171">
+        <v>19</v>
+      </c>
+      <c r="E171" t="s">
+        <v>28</v>
+      </c>
+      <c r="F171">
+        <v>95</v>
+      </c>
+      <c r="G171" t="s">
+        <v>19</v>
+      </c>
+      <c r="H171" t="s">
+        <v>12</v>
+      </c>
+      <c r="I171">
+        <v>1000</v>
+      </c>
+      <c r="J171" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="172" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B172">
+        <v>6</v>
+      </c>
+      <c r="C172" t="s">
+        <v>27</v>
+      </c>
+      <c r="D172">
+        <v>20</v>
+      </c>
+      <c r="E172" t="s">
+        <v>28</v>
+      </c>
+      <c r="F172">
+        <v>100</v>
+      </c>
+      <c r="G172" t="s">
+        <v>19</v>
+      </c>
+      <c r="H172" t="s">
+        <v>12</v>
+      </c>
+      <c r="I172">
+        <v>1050</v>
+      </c>
+      <c r="J172" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="173" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B173">
+        <v>6</v>
+      </c>
+      <c r="C173" t="s">
+        <v>27</v>
+      </c>
+      <c r="D173">
+        <v>21</v>
+      </c>
+      <c r="E173" t="s">
+        <v>28</v>
+      </c>
+      <c r="F173">
+        <v>105</v>
+      </c>
+      <c r="G173" t="s">
+        <v>19</v>
+      </c>
+      <c r="H173" t="s">
+        <v>12</v>
+      </c>
+      <c r="I173">
+        <v>1100</v>
+      </c>
+      <c r="J173" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="174" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B174">
+        <v>6</v>
+      </c>
+      <c r="C174" t="s">
+        <v>27</v>
+      </c>
+      <c r="D174">
+        <v>22</v>
+      </c>
+      <c r="E174" t="s">
+        <v>28</v>
+      </c>
+      <c r="F174">
+        <v>110</v>
+      </c>
+      <c r="G174" t="s">
+        <v>19</v>
+      </c>
+      <c r="H174" t="s">
+        <v>12</v>
+      </c>
+      <c r="I174">
+        <v>1150</v>
+      </c>
+      <c r="J174" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="175" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B175">
+        <v>6</v>
+      </c>
+      <c r="C175" t="s">
+        <v>27</v>
+      </c>
+      <c r="D175">
+        <v>23</v>
+      </c>
+      <c r="E175" t="s">
+        <v>28</v>
+      </c>
+      <c r="F175">
+        <v>115</v>
+      </c>
+      <c r="G175" t="s">
+        <v>19</v>
+      </c>
+      <c r="H175" t="s">
+        <v>12</v>
+      </c>
+      <c r="I175">
+        <v>1200</v>
+      </c>
+      <c r="J175" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="176" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B176">
+        <v>6</v>
+      </c>
+      <c r="C176" t="s">
+        <v>27</v>
+      </c>
+      <c r="D176">
+        <v>24</v>
+      </c>
+      <c r="E176" t="s">
+        <v>28</v>
+      </c>
+      <c r="F176">
+        <v>120</v>
+      </c>
+      <c r="G176" t="s">
+        <v>19</v>
+      </c>
+      <c r="H176" t="s">
+        <v>12</v>
+      </c>
+      <c r="I176">
+        <v>1250</v>
+      </c>
+      <c r="J176" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="177" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B177">
+        <v>6</v>
+      </c>
+      <c r="C177" t="s">
+        <v>27</v>
+      </c>
+      <c r="D177">
+        <v>25</v>
+      </c>
+      <c r="E177" t="s">
+        <v>28</v>
+      </c>
+      <c r="F177">
+        <v>125</v>
+      </c>
+      <c r="G177" t="s">
+        <v>19</v>
+      </c>
+      <c r="H177" t="s">
+        <v>12</v>
+      </c>
+      <c r="I177">
+        <v>1300</v>
+      </c>
+      <c r="J177" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="178" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B178">
+        <v>6</v>
+      </c>
+      <c r="C178" t="s">
+        <v>27</v>
+      </c>
+      <c r="D178">
+        <v>26</v>
+      </c>
+      <c r="E178" t="s">
+        <v>28</v>
+      </c>
+      <c r="F178">
+        <v>130</v>
+      </c>
+      <c r="G178" t="s">
+        <v>19</v>
+      </c>
+      <c r="H178" t="s">
+        <v>12</v>
+      </c>
+      <c r="I178">
+        <v>1350</v>
+      </c>
+      <c r="J178" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="179" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B179">
+        <v>6</v>
+      </c>
+      <c r="C179" t="s">
+        <v>27</v>
+      </c>
+      <c r="D179">
+        <v>27</v>
+      </c>
+      <c r="E179" t="s">
+        <v>28</v>
+      </c>
+      <c r="F179">
+        <v>135</v>
+      </c>
+      <c r="G179" t="s">
+        <v>19</v>
+      </c>
+      <c r="H179" t="s">
+        <v>12</v>
+      </c>
+      <c r="I179">
+        <v>1400</v>
+      </c>
+      <c r="J179" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="180" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B180">
+        <v>6</v>
+      </c>
+      <c r="C180" t="s">
+        <v>27</v>
+      </c>
+      <c r="D180">
+        <v>28</v>
+      </c>
+      <c r="E180" t="s">
+        <v>28</v>
+      </c>
+      <c r="F180">
+        <v>140</v>
+      </c>
+      <c r="G180" t="s">
+        <v>19</v>
+      </c>
+      <c r="H180" t="s">
+        <v>12</v>
+      </c>
+      <c r="I180">
+        <v>1450</v>
+      </c>
+      <c r="J180" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="181" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B181">
+        <v>6</v>
+      </c>
+      <c r="C181" t="s">
+        <v>27</v>
+      </c>
+      <c r="D181">
+        <v>29</v>
+      </c>
+      <c r="E181" t="s">
+        <v>28</v>
+      </c>
+      <c r="F181">
+        <v>145</v>
+      </c>
+      <c r="G181" t="s">
+        <v>19</v>
+      </c>
+      <c r="H181" t="s">
+        <v>12</v>
+      </c>
+      <c r="I181">
+        <v>1500</v>
+      </c>
+      <c r="J181" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="182" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B182">
+        <v>6</v>
+      </c>
+      <c r="C182" t="s">
+        <v>27</v>
+      </c>
+      <c r="D182">
+        <v>30</v>
+      </c>
+      <c r="E182" t="s">
+        <v>28</v>
+      </c>
+      <c r="F182">
+        <v>150</v>
+      </c>
+      <c r="G182" t="s">
+        <v>19</v>
+      </c>
+      <c r="H182" t="s">
+        <v>12</v>
+      </c>
+      <c r="I182">
+        <v>1550</v>
+      </c>
+      <c r="J182" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="183" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B183">
+        <v>7</v>
+      </c>
+      <c r="C183" t="s">
+        <v>30</v>
+      </c>
+      <c r="D183">
+        <v>1</v>
+      </c>
+      <c r="E183" t="s">
+        <v>31</v>
+      </c>
+      <c r="F183">
+        <v>1</v>
+      </c>
+      <c r="G183" t="s">
+        <v>11</v>
+      </c>
+      <c r="H183" t="s">
         <v>32</v>
       </c>
-      <c r="I152">
+      <c r="I183">
+        <v>100</v>
+      </c>
+      <c r="J183" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="184" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B184">
+        <v>7</v>
+      </c>
+      <c r="C184" t="s">
+        <v>30</v>
+      </c>
+      <c r="D184">
+        <v>2</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F184">
+        <v>2</v>
+      </c>
+      <c r="G184" t="s">
+        <v>11</v>
+      </c>
+      <c r="H184" t="s">
+        <v>32</v>
+      </c>
+      <c r="I184">
+        <v>150</v>
+      </c>
+      <c r="J184" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="185" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B185">
+        <v>7</v>
+      </c>
+      <c r="C185" t="s">
+        <v>30</v>
+      </c>
+      <c r="D185">
+        <v>3</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F185">
+        <v>3</v>
+      </c>
+      <c r="G185" t="s">
+        <v>11</v>
+      </c>
+      <c r="H185" t="s">
+        <v>32</v>
+      </c>
+      <c r="I185">
+        <v>200</v>
+      </c>
+      <c r="J185" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="186" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B186">
+        <v>7</v>
+      </c>
+      <c r="C186" t="s">
+        <v>30</v>
+      </c>
+      <c r="D186">
+        <v>4</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F186">
+        <v>4</v>
+      </c>
+      <c r="G186" t="s">
+        <v>11</v>
+      </c>
+      <c r="H186" t="s">
+        <v>32</v>
+      </c>
+      <c r="I186">
+        <v>250</v>
+      </c>
+      <c r="J186" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="187" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B187">
+        <v>7</v>
+      </c>
+      <c r="C187" t="s">
+        <v>30</v>
+      </c>
+      <c r="D187">
+        <v>5</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F187">
+        <v>5</v>
+      </c>
+      <c r="G187" t="s">
+        <v>11</v>
+      </c>
+      <c r="H187" t="s">
+        <v>32</v>
+      </c>
+      <c r="I187">
+        <v>300</v>
+      </c>
+      <c r="J187" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="188" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B188">
+        <v>7</v>
+      </c>
+      <c r="C188" t="s">
+        <v>30</v>
+      </c>
+      <c r="D188">
+        <v>6</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F188">
+        <v>6</v>
+      </c>
+      <c r="G188" t="s">
+        <v>11</v>
+      </c>
+      <c r="H188" t="s">
+        <v>32</v>
+      </c>
+      <c r="I188">
+        <v>350</v>
+      </c>
+      <c r="J188" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="189" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B189">
+        <v>7</v>
+      </c>
+      <c r="C189" t="s">
+        <v>30</v>
+      </c>
+      <c r="D189">
+        <v>7</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F189">
+        <v>7</v>
+      </c>
+      <c r="G189" t="s">
+        <v>11</v>
+      </c>
+      <c r="H189" t="s">
+        <v>32</v>
+      </c>
+      <c r="I189">
+        <v>400</v>
+      </c>
+      <c r="J189" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="190" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B190">
+        <v>7</v>
+      </c>
+      <c r="C190" t="s">
+        <v>30</v>
+      </c>
+      <c r="D190">
+        <v>8</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F190">
+        <v>8</v>
+      </c>
+      <c r="G190" t="s">
+        <v>11</v>
+      </c>
+      <c r="H190" t="s">
+        <v>32</v>
+      </c>
+      <c r="I190">
+        <v>450</v>
+      </c>
+      <c r="J190" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="191" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B191">
+        <v>7</v>
+      </c>
+      <c r="C191" t="s">
+        <v>30</v>
+      </c>
+      <c r="D191">
+        <v>9</v>
+      </c>
+      <c r="E191" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F191">
+        <v>9</v>
+      </c>
+      <c r="G191" t="s">
+        <v>11</v>
+      </c>
+      <c r="H191" t="s">
+        <v>32</v>
+      </c>
+      <c r="I191">
+        <v>500</v>
+      </c>
+      <c r="J191" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="192" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B192">
+        <v>7</v>
+      </c>
+      <c r="C192" t="s">
+        <v>30</v>
+      </c>
+      <c r="D192">
+        <v>10</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F192">
+        <v>10</v>
+      </c>
+      <c r="G192" t="s">
+        <v>11</v>
+      </c>
+      <c r="H192" t="s">
+        <v>32</v>
+      </c>
+      <c r="I192">
         <v>550</v>
       </c>
-      <c r="J152" t="s">
+      <c r="J192" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="193" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B193">
+        <v>7</v>
+      </c>
+      <c r="C193" t="s">
+        <v>30</v>
+      </c>
+      <c r="D193">
+        <v>11</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F193">
+        <v>11</v>
+      </c>
+      <c r="G193" t="s">
+        <v>11</v>
+      </c>
+      <c r="H193" t="s">
+        <v>32</v>
+      </c>
+      <c r="I193">
+        <v>600</v>
+      </c>
+      <c r="J193" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="194" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B194">
+        <v>7</v>
+      </c>
+      <c r="C194" t="s">
+        <v>30</v>
+      </c>
+      <c r="D194">
+        <v>12</v>
+      </c>
+      <c r="E194" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F194">
+        <v>12</v>
+      </c>
+      <c r="G194" t="s">
+        <v>11</v>
+      </c>
+      <c r="H194" t="s">
+        <v>32</v>
+      </c>
+      <c r="I194">
+        <v>650</v>
+      </c>
+      <c r="J194" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="195" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B195">
+        <v>7</v>
+      </c>
+      <c r="C195" t="s">
+        <v>30</v>
+      </c>
+      <c r="D195">
+        <v>13</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F195">
+        <v>13</v>
+      </c>
+      <c r="G195" t="s">
+        <v>11</v>
+      </c>
+      <c r="H195" t="s">
+        <v>32</v>
+      </c>
+      <c r="I195">
+        <v>700</v>
+      </c>
+      <c r="J195" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="196" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B196">
+        <v>7</v>
+      </c>
+      <c r="C196" t="s">
+        <v>30</v>
+      </c>
+      <c r="D196">
+        <v>14</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F196">
+        <v>14</v>
+      </c>
+      <c r="G196" t="s">
+        <v>11</v>
+      </c>
+      <c r="H196" t="s">
+        <v>32</v>
+      </c>
+      <c r="I196">
+        <v>750</v>
+      </c>
+      <c r="J196" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="197" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B197">
+        <v>7</v>
+      </c>
+      <c r="C197" t="s">
+        <v>30</v>
+      </c>
+      <c r="D197">
+        <v>15</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F197">
+        <v>15</v>
+      </c>
+      <c r="G197" t="s">
+        <v>11</v>
+      </c>
+      <c r="H197" t="s">
+        <v>32</v>
+      </c>
+      <c r="I197">
+        <v>800</v>
+      </c>
+      <c r="J197" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="198" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B198">
+        <v>7</v>
+      </c>
+      <c r="C198" t="s">
+        <v>30</v>
+      </c>
+      <c r="D198">
+        <v>16</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F198">
+        <v>16</v>
+      </c>
+      <c r="G198" t="s">
+        <v>11</v>
+      </c>
+      <c r="H198" t="s">
+        <v>32</v>
+      </c>
+      <c r="I198">
+        <v>850</v>
+      </c>
+      <c r="J198" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="199" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B199">
+        <v>7</v>
+      </c>
+      <c r="C199" t="s">
+        <v>30</v>
+      </c>
+      <c r="D199">
+        <v>17</v>
+      </c>
+      <c r="E199" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F199">
+        <v>17</v>
+      </c>
+      <c r="G199" t="s">
+        <v>11</v>
+      </c>
+      <c r="H199" t="s">
+        <v>32</v>
+      </c>
+      <c r="I199">
+        <v>900</v>
+      </c>
+      <c r="J199" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="200" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B200">
+        <v>7</v>
+      </c>
+      <c r="C200" t="s">
+        <v>30</v>
+      </c>
+      <c r="D200">
+        <v>18</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F200">
+        <v>18</v>
+      </c>
+      <c r="G200" t="s">
+        <v>11</v>
+      </c>
+      <c r="H200" t="s">
+        <v>32</v>
+      </c>
+      <c r="I200">
+        <v>950</v>
+      </c>
+      <c r="J200" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="201" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B201">
+        <v>7</v>
+      </c>
+      <c r="C201" t="s">
+        <v>30</v>
+      </c>
+      <c r="D201">
+        <v>19</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F201">
+        <v>19</v>
+      </c>
+      <c r="G201" t="s">
+        <v>11</v>
+      </c>
+      <c r="H201" t="s">
+        <v>32</v>
+      </c>
+      <c r="I201">
+        <v>1000</v>
+      </c>
+      <c r="J201" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="202" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B202">
+        <v>7</v>
+      </c>
+      <c r="C202" t="s">
+        <v>30</v>
+      </c>
+      <c r="D202">
+        <v>20</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F202">
+        <v>20</v>
+      </c>
+      <c r="G202" t="s">
+        <v>11</v>
+      </c>
+      <c r="H202" t="s">
+        <v>32</v>
+      </c>
+      <c r="I202">
+        <v>1050</v>
+      </c>
+      <c r="J202" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="203" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B203">
+        <v>8</v>
+      </c>
+      <c r="C203" t="s">
+        <v>34</v>
+      </c>
+      <c r="D203">
+        <v>1</v>
+      </c>
+      <c r="E203" t="s">
+        <v>35</v>
+      </c>
+      <c r="F203">
+        <v>100</v>
+      </c>
+      <c r="G203" t="s">
+        <v>19</v>
+      </c>
+      <c r="H203" t="s">
+        <v>32</v>
+      </c>
+      <c r="I203">
+        <v>100</v>
+      </c>
+      <c r="J203" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="204" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B204">
+        <v>8</v>
+      </c>
+      <c r="C204" t="s">
+        <v>34</v>
+      </c>
+      <c r="D204">
+        <v>2</v>
+      </c>
+      <c r="E204" t="s">
+        <v>35</v>
+      </c>
+      <c r="F204">
+        <v>110</v>
+      </c>
+      <c r="G204" t="s">
+        <v>19</v>
+      </c>
+      <c r="H204" t="s">
+        <v>32</v>
+      </c>
+      <c r="I204">
+        <v>150</v>
+      </c>
+      <c r="J204" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="205" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B205">
+        <v>8</v>
+      </c>
+      <c r="C205" t="s">
+        <v>34</v>
+      </c>
+      <c r="D205">
+        <v>3</v>
+      </c>
+      <c r="E205" t="s">
+        <v>35</v>
+      </c>
+      <c r="F205">
+        <v>120</v>
+      </c>
+      <c r="G205" t="s">
+        <v>19</v>
+      </c>
+      <c r="H205" t="s">
+        <v>32</v>
+      </c>
+      <c r="I205">
+        <v>200</v>
+      </c>
+      <c r="J205" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="206" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B206">
+        <v>8</v>
+      </c>
+      <c r="C206" t="s">
+        <v>34</v>
+      </c>
+      <c r="D206">
+        <v>4</v>
+      </c>
+      <c r="E206" t="s">
+        <v>35</v>
+      </c>
+      <c r="F206">
+        <v>130</v>
+      </c>
+      <c r="G206" t="s">
+        <v>19</v>
+      </c>
+      <c r="H206" t="s">
+        <v>32</v>
+      </c>
+      <c r="I206">
+        <v>250</v>
+      </c>
+      <c r="J206" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="207" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B207">
+        <v>8</v>
+      </c>
+      <c r="C207" t="s">
+        <v>34</v>
+      </c>
+      <c r="D207">
+        <v>5</v>
+      </c>
+      <c r="E207" t="s">
+        <v>35</v>
+      </c>
+      <c r="F207">
+        <v>140</v>
+      </c>
+      <c r="G207" t="s">
+        <v>19</v>
+      </c>
+      <c r="H207" t="s">
+        <v>32</v>
+      </c>
+      <c r="I207">
+        <v>300</v>
+      </c>
+      <c r="J207" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="208" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B208">
+        <v>8</v>
+      </c>
+      <c r="C208" t="s">
+        <v>34</v>
+      </c>
+      <c r="D208">
+        <v>6</v>
+      </c>
+      <c r="E208" t="s">
+        <v>35</v>
+      </c>
+      <c r="F208">
+        <v>150</v>
+      </c>
+      <c r="G208" t="s">
+        <v>19</v>
+      </c>
+      <c r="H208" t="s">
+        <v>32</v>
+      </c>
+      <c r="I208">
+        <v>350</v>
+      </c>
+      <c r="J208" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="209" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B209">
+        <v>8</v>
+      </c>
+      <c r="C209" t="s">
+        <v>34</v>
+      </c>
+      <c r="D209">
+        <v>7</v>
+      </c>
+      <c r="E209" t="s">
+        <v>35</v>
+      </c>
+      <c r="F209">
+        <v>160</v>
+      </c>
+      <c r="G209" t="s">
+        <v>19</v>
+      </c>
+      <c r="H209" t="s">
+        <v>32</v>
+      </c>
+      <c r="I209">
+        <v>400</v>
+      </c>
+      <c r="J209" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="210" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B210">
+        <v>8</v>
+      </c>
+      <c r="C210" t="s">
+        <v>34</v>
+      </c>
+      <c r="D210">
+        <v>8</v>
+      </c>
+      <c r="E210" t="s">
+        <v>35</v>
+      </c>
+      <c r="F210">
+        <v>170</v>
+      </c>
+      <c r="G210" t="s">
+        <v>19</v>
+      </c>
+      <c r="H210" t="s">
+        <v>32</v>
+      </c>
+      <c r="I210">
+        <v>450</v>
+      </c>
+      <c r="J210" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="211" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B211">
+        <v>8</v>
+      </c>
+      <c r="C211" t="s">
+        <v>34</v>
+      </c>
+      <c r="D211">
+        <v>9</v>
+      </c>
+      <c r="E211" t="s">
+        <v>35</v>
+      </c>
+      <c r="F211">
+        <v>180</v>
+      </c>
+      <c r="G211" t="s">
+        <v>19</v>
+      </c>
+      <c r="H211" t="s">
+        <v>32</v>
+      </c>
+      <c r="I211">
+        <v>500</v>
+      </c>
+      <c r="J211" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="212" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B212">
+        <v>8</v>
+      </c>
+      <c r="C212" t="s">
+        <v>34</v>
+      </c>
+      <c r="D212">
+        <v>10</v>
+      </c>
+      <c r="E212" t="s">
+        <v>35</v>
+      </c>
+      <c r="F212">
+        <v>190</v>
+      </c>
+      <c r="G212" t="s">
+        <v>19</v>
+      </c>
+      <c r="H212" t="s">
+        <v>32</v>
+      </c>
+      <c r="I212">
+        <v>550</v>
+      </c>
+      <c r="J212" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="213" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B213">
+        <v>8</v>
+      </c>
+      <c r="C213" t="s">
+        <v>34</v>
+      </c>
+      <c r="D213">
+        <v>11</v>
+      </c>
+      <c r="E213" t="s">
+        <v>35</v>
+      </c>
+      <c r="F213">
+        <v>200</v>
+      </c>
+      <c r="G213" t="s">
+        <v>19</v>
+      </c>
+      <c r="H213" t="s">
+        <v>32</v>
+      </c>
+      <c r="I213">
+        <v>600</v>
+      </c>
+      <c r="J213" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="214" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B214">
+        <v>8</v>
+      </c>
+      <c r="C214" t="s">
+        <v>34</v>
+      </c>
+      <c r="D214">
+        <v>12</v>
+      </c>
+      <c r="E214" t="s">
+        <v>35</v>
+      </c>
+      <c r="F214">
+        <v>210</v>
+      </c>
+      <c r="G214" t="s">
+        <v>19</v>
+      </c>
+      <c r="H214" t="s">
+        <v>32</v>
+      </c>
+      <c r="I214">
+        <v>650</v>
+      </c>
+      <c r="J214" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="215" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B215">
+        <v>8</v>
+      </c>
+      <c r="C215" t="s">
+        <v>34</v>
+      </c>
+      <c r="D215">
+        <v>13</v>
+      </c>
+      <c r="E215" t="s">
+        <v>35</v>
+      </c>
+      <c r="F215">
+        <v>220</v>
+      </c>
+      <c r="G215" t="s">
+        <v>19</v>
+      </c>
+      <c r="H215" t="s">
+        <v>32</v>
+      </c>
+      <c r="I215">
+        <v>700</v>
+      </c>
+      <c r="J215" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="216" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B216">
+        <v>8</v>
+      </c>
+      <c r="C216" t="s">
+        <v>34</v>
+      </c>
+      <c r="D216">
+        <v>14</v>
+      </c>
+      <c r="E216" t="s">
+        <v>35</v>
+      </c>
+      <c r="F216">
+        <v>230</v>
+      </c>
+      <c r="G216" t="s">
+        <v>19</v>
+      </c>
+      <c r="H216" t="s">
+        <v>32</v>
+      </c>
+      <c r="I216">
+        <v>750</v>
+      </c>
+      <c r="J216" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="217" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B217">
+        <v>8</v>
+      </c>
+      <c r="C217" t="s">
+        <v>34</v>
+      </c>
+      <c r="D217">
+        <v>15</v>
+      </c>
+      <c r="E217" t="s">
+        <v>35</v>
+      </c>
+      <c r="F217">
+        <v>240</v>
+      </c>
+      <c r="G217" t="s">
+        <v>19</v>
+      </c>
+      <c r="H217" t="s">
+        <v>32</v>
+      </c>
+      <c r="I217">
+        <v>800</v>
+      </c>
+      <c r="J217" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="218" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B218">
+        <v>8</v>
+      </c>
+      <c r="C218" t="s">
+        <v>34</v>
+      </c>
+      <c r="D218">
+        <v>16</v>
+      </c>
+      <c r="E218" t="s">
+        <v>35</v>
+      </c>
+      <c r="F218">
+        <v>250</v>
+      </c>
+      <c r="G218" t="s">
+        <v>19</v>
+      </c>
+      <c r="H218" t="s">
+        <v>32</v>
+      </c>
+      <c r="I218">
+        <v>850</v>
+      </c>
+      <c r="J218" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="219" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B219">
+        <v>8</v>
+      </c>
+      <c r="C219" t="s">
+        <v>34</v>
+      </c>
+      <c r="D219">
+        <v>17</v>
+      </c>
+      <c r="E219" t="s">
+        <v>35</v>
+      </c>
+      <c r="F219">
+        <v>260</v>
+      </c>
+      <c r="G219" t="s">
+        <v>19</v>
+      </c>
+      <c r="H219" t="s">
+        <v>32</v>
+      </c>
+      <c r="I219">
+        <v>900</v>
+      </c>
+      <c r="J219" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="220" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B220">
+        <v>8</v>
+      </c>
+      <c r="C220" t="s">
+        <v>34</v>
+      </c>
+      <c r="D220">
+        <v>18</v>
+      </c>
+      <c r="E220" t="s">
+        <v>35</v>
+      </c>
+      <c r="F220">
+        <v>270</v>
+      </c>
+      <c r="G220" t="s">
+        <v>19</v>
+      </c>
+      <c r="H220" t="s">
+        <v>32</v>
+      </c>
+      <c r="I220">
+        <v>950</v>
+      </c>
+      <c r="J220" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="221" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B221">
+        <v>8</v>
+      </c>
+      <c r="C221" t="s">
+        <v>34</v>
+      </c>
+      <c r="D221">
+        <v>19</v>
+      </c>
+      <c r="E221" t="s">
+        <v>35</v>
+      </c>
+      <c r="F221">
+        <v>280</v>
+      </c>
+      <c r="G221" t="s">
+        <v>19</v>
+      </c>
+      <c r="H221" t="s">
+        <v>32</v>
+      </c>
+      <c r="I221">
+        <v>1000</v>
+      </c>
+      <c r="J221" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="222" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B222">
+        <v>8</v>
+      </c>
+      <c r="C222" t="s">
+        <v>34</v>
+      </c>
+      <c r="D222">
+        <v>20</v>
+      </c>
+      <c r="E222" t="s">
+        <v>35</v>
+      </c>
+      <c r="F222">
+        <v>290</v>
+      </c>
+      <c r="G222" t="s">
+        <v>19</v>
+      </c>
+      <c r="H222" t="s">
+        <v>32</v>
+      </c>
+      <c r="I222">
+        <v>1050</v>
+      </c>
+      <c r="J222" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="223" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B223">
+        <v>9</v>
+      </c>
+      <c r="C223" t="s">
+        <v>37</v>
+      </c>
+      <c r="D223">
+        <v>1</v>
+      </c>
+      <c r="E223" t="s">
+        <v>38</v>
+      </c>
+      <c r="F223">
+        <v>20</v>
+      </c>
+      <c r="G223" t="s">
+        <v>19</v>
+      </c>
+      <c r="H223" t="s">
+        <v>32</v>
+      </c>
+      <c r="I223">
+        <v>100</v>
+      </c>
+      <c r="J223" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="224" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B224">
+        <v>9</v>
+      </c>
+      <c r="C224" t="s">
+        <v>37</v>
+      </c>
+      <c r="D224">
+        <v>2</v>
+      </c>
+      <c r="E224" t="s">
+        <v>38</v>
+      </c>
+      <c r="F224">
+        <v>25</v>
+      </c>
+      <c r="G224" t="s">
+        <v>19</v>
+      </c>
+      <c r="H224" t="s">
+        <v>32</v>
+      </c>
+      <c r="I224">
+        <v>150</v>
+      </c>
+      <c r="J224" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="225" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B225">
+        <v>9</v>
+      </c>
+      <c r="C225" t="s">
+        <v>37</v>
+      </c>
+      <c r="D225">
+        <v>3</v>
+      </c>
+      <c r="E225" t="s">
+        <v>38</v>
+      </c>
+      <c r="F225">
+        <v>30</v>
+      </c>
+      <c r="G225" t="s">
+        <v>19</v>
+      </c>
+      <c r="H225" t="s">
+        <v>32</v>
+      </c>
+      <c r="I225">
+        <v>200</v>
+      </c>
+      <c r="J225" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="226" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B226">
+        <v>9</v>
+      </c>
+      <c r="C226" t="s">
+        <v>37</v>
+      </c>
+      <c r="D226">
+        <v>4</v>
+      </c>
+      <c r="E226" t="s">
+        <v>38</v>
+      </c>
+      <c r="F226">
+        <v>35</v>
+      </c>
+      <c r="G226" t="s">
+        <v>19</v>
+      </c>
+      <c r="H226" t="s">
+        <v>32</v>
+      </c>
+      <c r="I226">
+        <v>250</v>
+      </c>
+      <c r="J226" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="227" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B227">
+        <v>9</v>
+      </c>
+      <c r="C227" t="s">
+        <v>37</v>
+      </c>
+      <c r="D227">
+        <v>5</v>
+      </c>
+      <c r="E227" t="s">
+        <v>38</v>
+      </c>
+      <c r="F227">
+        <v>40</v>
+      </c>
+      <c r="G227" t="s">
+        <v>19</v>
+      </c>
+      <c r="H227" t="s">
+        <v>32</v>
+      </c>
+      <c r="I227">
+        <v>300</v>
+      </c>
+      <c r="J227" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="228" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B228">
+        <v>9</v>
+      </c>
+      <c r="C228" t="s">
+        <v>37</v>
+      </c>
+      <c r="D228">
+        <v>6</v>
+      </c>
+      <c r="E228" t="s">
+        <v>38</v>
+      </c>
+      <c r="F228">
+        <v>45</v>
+      </c>
+      <c r="G228" t="s">
+        <v>19</v>
+      </c>
+      <c r="H228" t="s">
+        <v>32</v>
+      </c>
+      <c r="I228">
+        <v>350</v>
+      </c>
+      <c r="J228" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="229" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B229">
+        <v>9</v>
+      </c>
+      <c r="C229" t="s">
+        <v>37</v>
+      </c>
+      <c r="D229">
+        <v>7</v>
+      </c>
+      <c r="E229" t="s">
+        <v>38</v>
+      </c>
+      <c r="F229">
+        <v>50</v>
+      </c>
+      <c r="G229" t="s">
+        <v>19</v>
+      </c>
+      <c r="H229" t="s">
+        <v>32</v>
+      </c>
+      <c r="I229">
+        <v>400</v>
+      </c>
+      <c r="J229" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="230" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B230">
+        <v>9</v>
+      </c>
+      <c r="C230" t="s">
+        <v>37</v>
+      </c>
+      <c r="D230">
+        <v>8</v>
+      </c>
+      <c r="E230" t="s">
+        <v>38</v>
+      </c>
+      <c r="F230">
+        <v>55</v>
+      </c>
+      <c r="G230" t="s">
+        <v>19</v>
+      </c>
+      <c r="H230" t="s">
+        <v>32</v>
+      </c>
+      <c r="I230">
+        <v>450</v>
+      </c>
+      <c r="J230" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="231" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B231">
+        <v>9</v>
+      </c>
+      <c r="C231" t="s">
+        <v>37</v>
+      </c>
+      <c r="D231">
+        <v>9</v>
+      </c>
+      <c r="E231" t="s">
+        <v>38</v>
+      </c>
+      <c r="F231">
+        <v>60</v>
+      </c>
+      <c r="G231" t="s">
+        <v>19</v>
+      </c>
+      <c r="H231" t="s">
+        <v>32</v>
+      </c>
+      <c r="I231">
+        <v>500</v>
+      </c>
+      <c r="J231" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="232" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B232">
+        <v>9</v>
+      </c>
+      <c r="C232" t="s">
+        <v>37</v>
+      </c>
+      <c r="D232">
+        <v>10</v>
+      </c>
+      <c r="E232" t="s">
+        <v>38</v>
+      </c>
+      <c r="F232">
+        <v>65</v>
+      </c>
+      <c r="G232" t="s">
+        <v>19</v>
+      </c>
+      <c r="H232" t="s">
+        <v>32</v>
+      </c>
+      <c r="I232">
+        <v>550</v>
+      </c>
+      <c r="J232" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="233" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B233">
+        <v>9</v>
+      </c>
+      <c r="C233" t="s">
+        <v>37</v>
+      </c>
+      <c r="D233">
+        <v>11</v>
+      </c>
+      <c r="E233" t="s">
+        <v>38</v>
+      </c>
+      <c r="F233">
+        <v>70</v>
+      </c>
+      <c r="G233" t="s">
+        <v>19</v>
+      </c>
+      <c r="H233" t="s">
+        <v>32</v>
+      </c>
+      <c r="I233">
+        <v>600</v>
+      </c>
+      <c r="J233" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="234" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B234">
+        <v>9</v>
+      </c>
+      <c r="C234" t="s">
+        <v>37</v>
+      </c>
+      <c r="D234">
+        <v>12</v>
+      </c>
+      <c r="E234" t="s">
+        <v>38</v>
+      </c>
+      <c r="F234">
+        <v>75</v>
+      </c>
+      <c r="G234" t="s">
+        <v>19</v>
+      </c>
+      <c r="H234" t="s">
+        <v>32</v>
+      </c>
+      <c r="I234">
+        <v>650</v>
+      </c>
+      <c r="J234" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="235" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B235">
+        <v>9</v>
+      </c>
+      <c r="C235" t="s">
+        <v>37</v>
+      </c>
+      <c r="D235">
+        <v>13</v>
+      </c>
+      <c r="E235" t="s">
+        <v>38</v>
+      </c>
+      <c r="F235">
+        <v>80</v>
+      </c>
+      <c r="G235" t="s">
+        <v>19</v>
+      </c>
+      <c r="H235" t="s">
+        <v>32</v>
+      </c>
+      <c r="I235">
+        <v>700</v>
+      </c>
+      <c r="J235" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="236" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B236">
+        <v>9</v>
+      </c>
+      <c r="C236" t="s">
+        <v>37</v>
+      </c>
+      <c r="D236">
+        <v>14</v>
+      </c>
+      <c r="E236" t="s">
+        <v>38</v>
+      </c>
+      <c r="F236">
+        <v>85</v>
+      </c>
+      <c r="G236" t="s">
+        <v>19</v>
+      </c>
+      <c r="H236" t="s">
+        <v>32</v>
+      </c>
+      <c r="I236">
+        <v>750</v>
+      </c>
+      <c r="J236" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="237" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B237">
+        <v>9</v>
+      </c>
+      <c r="C237" t="s">
+        <v>37</v>
+      </c>
+      <c r="D237">
+        <v>15</v>
+      </c>
+      <c r="E237" t="s">
+        <v>38</v>
+      </c>
+      <c r="F237">
+        <v>90</v>
+      </c>
+      <c r="G237" t="s">
+        <v>19</v>
+      </c>
+      <c r="H237" t="s">
+        <v>32</v>
+      </c>
+      <c r="I237">
+        <v>800</v>
+      </c>
+      <c r="J237" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="238" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B238">
+        <v>9</v>
+      </c>
+      <c r="C238" t="s">
+        <v>37</v>
+      </c>
+      <c r="D238">
+        <v>16</v>
+      </c>
+      <c r="E238" t="s">
+        <v>38</v>
+      </c>
+      <c r="F238">
+        <v>95</v>
+      </c>
+      <c r="G238" t="s">
+        <v>19</v>
+      </c>
+      <c r="H238" t="s">
+        <v>32</v>
+      </c>
+      <c r="I238">
+        <v>850</v>
+      </c>
+      <c r="J238" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="239" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B239">
+        <v>9</v>
+      </c>
+      <c r="C239" t="s">
+        <v>37</v>
+      </c>
+      <c r="D239">
+        <v>17</v>
+      </c>
+      <c r="E239" t="s">
+        <v>38</v>
+      </c>
+      <c r="F239">
+        <v>100</v>
+      </c>
+      <c r="G239" t="s">
+        <v>19</v>
+      </c>
+      <c r="H239" t="s">
+        <v>32</v>
+      </c>
+      <c r="I239">
+        <v>900</v>
+      </c>
+      <c r="J239" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="240" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B240">
+        <v>9</v>
+      </c>
+      <c r="C240" t="s">
+        <v>37</v>
+      </c>
+      <c r="D240">
+        <v>18</v>
+      </c>
+      <c r="E240" t="s">
+        <v>38</v>
+      </c>
+      <c r="F240">
+        <v>105</v>
+      </c>
+      <c r="G240" t="s">
+        <v>19</v>
+      </c>
+      <c r="H240" t="s">
+        <v>32</v>
+      </c>
+      <c r="I240">
+        <v>950</v>
+      </c>
+      <c r="J240" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="241" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B241">
+        <v>9</v>
+      </c>
+      <c r="C241" t="s">
+        <v>37</v>
+      </c>
+      <c r="D241">
+        <v>19</v>
+      </c>
+      <c r="E241" t="s">
+        <v>38</v>
+      </c>
+      <c r="F241">
+        <v>110</v>
+      </c>
+      <c r="G241" t="s">
+        <v>19</v>
+      </c>
+      <c r="H241" t="s">
+        <v>32</v>
+      </c>
+      <c r="I241">
+        <v>1000</v>
+      </c>
+      <c r="J241" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="242" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B242">
+        <v>9</v>
+      </c>
+      <c r="C242" t="s">
+        <v>37</v>
+      </c>
+      <c r="D242">
+        <v>20</v>
+      </c>
+      <c r="E242" t="s">
+        <v>38</v>
+      </c>
+      <c r="F242">
+        <v>115</v>
+      </c>
+      <c r="G242" t="s">
+        <v>19</v>
+      </c>
+      <c r="H242" t="s">
+        <v>32</v>
+      </c>
+      <c r="I242">
+        <v>1050</v>
+      </c>
+      <c r="J242" t="s">
         <v>39</v>
       </c>
     </row>
@@ -5758,11 +8368,12 @@
         <v>60</v>
       </c>
       <c r="K12" s="3">
-        <f t="shared" ref="K12:K17" si="0">K3*2</f>
-        <v>0.24</v>
+        <f>K3*3</f>
+        <v>0.36</v>
       </c>
       <c r="L12" s="3">
-        <v>0.36</v>
+        <f>K12*1.5</f>
+        <v>0.54</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
@@ -5782,11 +8393,12 @@
         <v>19</v>
       </c>
       <c r="K13" s="4">
-        <f t="shared" si="0"/>
-        <v>20</v>
+        <f t="shared" ref="K13:K17" si="0">K4*3</f>
+        <v>30</v>
       </c>
       <c r="L13" s="4">
-        <v>30</v>
+        <f t="shared" ref="L13:L17" si="1">K13*1.5</f>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
@@ -5807,11 +8419,11 @@
       </c>
       <c r="K14" s="6">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="L14" s="6">
-        <f>L5*2</f>
-        <v>28</v>
+        <f t="shared" si="1"/>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
@@ -5832,11 +8444,11 @@
       </c>
       <c r="K15" s="7">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="L15" s="7">
-        <f>L6*2</f>
-        <v>46</v>
+        <f>ROUND(K15*1.5,0)</f>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
@@ -5857,11 +8469,11 @@
       </c>
       <c r="K16" s="8">
         <f t="shared" si="0"/>
-        <v>0.24</v>
+        <v>0.36</v>
       </c>
       <c r="L16" s="8">
-        <f>L7*2</f>
-        <v>0.4</v>
+        <f t="shared" si="1"/>
+        <v>0.54</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
@@ -5882,11 +8494,11 @@
       </c>
       <c r="K17" s="9">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L17" s="9">
-        <f>L8*2</f>
-        <v>34</v>
+        <f t="shared" si="1"/>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
